--- a/documentacion/HISTORIAS-DE-USUARIO.xlsx
+++ b/documentacion/HISTORIAS-DE-USUARIO.xlsx
@@ -1,26 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sopio\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fran_\Gestor_De_Proyectos\documentacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0F172EB-5238-404A-A832-481705C64653}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96AD698A-DB60-4D8F-98A1-CAB7614A3D67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="16305" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="84">
   <si>
     <t>GRUPO 2</t>
   </si>
@@ -84,9 +97,6 @@
   </si>
   <si>
     <t>-Crear formulario registro.</t>
-  </si>
-  <si>
-    <t>-Crear endpont POST usuario.</t>
   </si>
   <si>
     <t>BACK</t>
@@ -154,9 +164,6 @@
     <t>-Crear formulario Login.</t>
   </si>
   <si>
-    <t>-Crear endpont para login de usuario.</t>
-  </si>
-  <si>
     <t>-Realizar tests unitarios.</t>
   </si>
   <si>
@@ -200,9 +207,6 @@
   </si>
   <si>
     <t>-Crear endpoint GET proyectos.</t>
-  </si>
-  <si>
-    <t>Solo los usarios admin tendrán acceso al panel.</t>
   </si>
   <si>
     <t>-Gestionar las autorizaciones.</t>
@@ -255,9 +259,6 @@
   </si>
   <si>
     <t>Si se intenta crear un proyecto con un nombre que ya existe, se debe mostrar un mensaje de error indicando que el nombre ya está en uso.</t>
-  </si>
-  <si>
-    <t>-Validar antes de enviar el formulario, que el producto no exista en la BDD.</t>
   </si>
   <si>
     <t>Se deben crear las tareas a partir del archivo .csv y asignarlas a los usuarios indicados.</t>
@@ -345,9 +346,6 @@
     <t>-Crear endpoint GET tareas por prioridad.</t>
   </si>
   <si>
-    <t>-Crear botón que perimita elegir el filtro.</t>
-  </si>
-  <si>
     <t>-Renderizar el listado filtrado.</t>
   </si>
   <si>
@@ -378,16 +376,10 @@
     </r>
   </si>
   <si>
-    <t>Se debe poder indicar dos variables de tiempo y que el sistema calcule la estimación.</t>
-  </si>
-  <si>
     <t>-Crear botón para calcular estimación.</t>
   </si>
   <si>
     <t>-Realizar lógica de cálculo para devolver el valor estimado.</t>
-  </si>
-  <si>
-    <t>-Crear endpoint PUT tarea para guardar la estimación.</t>
   </si>
   <si>
     <t>Se debe poder modificar la estimación inicial.</t>
@@ -429,22 +421,10 @@
     <t>-Mostrar estado actual.</t>
   </si>
   <si>
-    <t>-Crear menú desplegable para que el usuario eliga el estado.</t>
-  </si>
-  <si>
-    <t>-Crear endpoint PUT tarea para guardar el nuevo estado.</t>
-  </si>
-  <si>
     <t>Se debe poder registrar la fecha en que una tarea pasa a EN PROGRESO.</t>
   </si>
   <si>
-    <t>-Guardar el dato de fecha actual en el atributo startedAt.</t>
-  </si>
-  <si>
     <t>Se debe poder registrar la fecha en que una tarea pasa a FINALIZADA.</t>
-  </si>
-  <si>
-    <t>-Guardar el dato de fecha actual en el atributo finishedAt.</t>
   </si>
   <si>
     <r>
@@ -480,10 +460,46 @@
     <t>-Crear botón Generar Reporte.</t>
   </si>
   <si>
-    <t>-CONSULTA A LA BDD (POR DEFINIR)</t>
+    <t>Se deben mostrar las tareas separadas por estado, indicando fecha de inicio y finalización para las tareas finalizadas, y una comparación de la estimación con el tiempo real.</t>
   </si>
   <si>
-    <t>Se deben mostrar las tareas separadas por estado, indicando fecha de inicio y finalización para las tareas finalizadas, y una comparación de la estimación con el tiempo real.</t>
+    <t>-Crear endpoint POST usuario.</t>
+  </si>
+  <si>
+    <t>-Crear endpoint para login de usuario.</t>
+  </si>
+  <si>
+    <t>-Validar antes de enviar el formulario, que el proyecto no exista en la BDD.</t>
+  </si>
+  <si>
+    <t>-Crear botón que permita elegir el filtro.</t>
+  </si>
+  <si>
+    <t>Solo usuarios admin tendrán acceso al panel.</t>
+  </si>
+  <si>
+    <t>-Crear menú desplegable para que el usuario elija el estado.</t>
+  </si>
+  <si>
+    <t>Se debe poder indicar tres variables de tiempo (PERT) y que el sistema calcule la estimación.</t>
+  </si>
+  <si>
+    <t>-Guardar el dato de fecha actual en el atributo fechaAsignacion.</t>
+  </si>
+  <si>
+    <t>-Guardar el dato de fecha actual en el atributo fechaCierre.</t>
+  </si>
+  <si>
+    <t>-Crear endpoint PATCH tarea para guardar la estimación.</t>
+  </si>
+  <si>
+    <t>-Crear endpoint PATCH tarea para guardar el nuevo estado.</t>
+  </si>
+  <si>
+    <t>-CONSULTA A LA BDD</t>
+  </si>
+  <si>
+    <t>1H</t>
   </si>
 </sst>
 </file>
@@ -798,7 +814,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -875,16 +891,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -894,6 +900,25 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1113,24 +1138,24 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:X1012"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="32.77734375" customWidth="1"/>
-    <col min="2" max="2" width="55.109375" customWidth="1"/>
-    <col min="3" max="3" width="56.6640625" customWidth="1"/>
-    <col min="4" max="4" width="12.77734375" customWidth="1"/>
+    <col min="1" max="1" width="32.7109375" customWidth="1"/>
+    <col min="2" max="2" width="55.140625" customWidth="1"/>
+    <col min="3" max="3" width="56.7109375" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="26" t="s">
+      <c r="B1" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="28"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="36"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
@@ -1151,7 +1176,7 @@
       <c r="W1" s="2"/>
       <c r="X1" s="2"/>
     </row>
-    <row r="2" spans="1:24" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
@@ -1187,11 +1212,11 @@
       <c r="W2" s="2"/>
       <c r="X2" s="2"/>
     </row>
-    <row r="3" spans="1:24" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="29" t="s">
+    <row r="3" spans="1:24" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="26" t="s">
         <v>8</v>
       </c>
       <c r="C3" s="7" t="s">
@@ -1223,9 +1248,9 @@
       <c r="W3" s="2"/>
       <c r="X3" s="2"/>
     </row>
-    <row r="4" spans="1:24" ht="16.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="30"/>
-      <c r="B4" s="33"/>
+    <row r="4" spans="1:24" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="32"/>
+      <c r="B4" s="27"/>
       <c r="C4" s="10" t="s">
         <v>12</v>
       </c>
@@ -1255,14 +1280,14 @@
       <c r="W4" s="2"/>
       <c r="X4" s="2"/>
     </row>
-    <row r="5" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="30"/>
-      <c r="B5" s="33"/>
-      <c r="C5" s="10" t="s">
-        <v>13</v>
+    <row r="5" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="32"/>
+      <c r="B5" s="27"/>
+      <c r="C5" s="37" t="s">
+        <v>71</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E5" s="12" t="s">
         <v>11</v>
@@ -1287,14 +1312,14 @@
       <c r="W5" s="2"/>
       <c r="X5" s="2"/>
     </row>
-    <row r="6" spans="1:24" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="30"/>
-      <c r="B6" s="33"/>
+    <row r="6" spans="1:24" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="32"/>
+      <c r="B6" s="27"/>
       <c r="C6" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E6" s="12" t="s">
         <v>11</v>
@@ -1319,17 +1344,17 @@
       <c r="W6" s="2"/>
       <c r="X6" s="2"/>
     </row>
-    <row r="7" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="30"/>
-      <c r="B7" s="34"/>
+    <row r="7" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="32"/>
+      <c r="B7" s="28"/>
       <c r="C7" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="E7" s="12" t="s">
         <v>17</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>18</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
@@ -1351,13 +1376,13 @@
       <c r="W7" s="2"/>
       <c r="X7" s="2"/>
     </row>
-    <row r="8" spans="1:24" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A8" s="30"/>
+    <row r="8" spans="1:24" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A8" s="32"/>
       <c r="B8" s="13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D8" s="11" t="s">
         <v>10</v>
@@ -1385,19 +1410,19 @@
       <c r="W8" s="2"/>
       <c r="X8" s="2"/>
     </row>
-    <row r="9" spans="1:24" ht="28.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="31"/>
+    <row r="9" spans="1:24" ht="28.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="33"/>
       <c r="B9" s="14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D9" s="16" t="s">
         <v>10</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
@@ -1419,15 +1444,15 @@
       <c r="W9" s="2"/>
       <c r="X9" s="2"/>
     </row>
-    <row r="10" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="29" t="s">
+    <row r="10" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="32" t="s">
+      <c r="C10" s="7" t="s">
         <v>24</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>25</v>
       </c>
       <c r="D10" s="8" t="s">
         <v>10</v>
@@ -1455,11 +1480,11 @@
       <c r="W10" s="2"/>
       <c r="X10" s="2"/>
     </row>
-    <row r="11" spans="1:24" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="30"/>
-      <c r="B11" s="33"/>
+    <row r="11" spans="1:24" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="32"/>
+      <c r="B11" s="27"/>
       <c r="C11" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D11" s="11" t="s">
         <v>10</v>
@@ -1487,14 +1512,14 @@
       <c r="W11" s="2"/>
       <c r="X11" s="2"/>
     </row>
-    <row r="12" spans="1:24" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="30"/>
-      <c r="B12" s="33"/>
-      <c r="C12" s="10" t="s">
-        <v>27</v>
+    <row r="12" spans="1:24" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="32"/>
+      <c r="B12" s="27"/>
+      <c r="C12" s="37" t="s">
+        <v>72</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E12" s="12" t="s">
         <v>11</v>
@@ -1519,14 +1544,14 @@
       <c r="W12" s="2"/>
       <c r="X12" s="2"/>
     </row>
-    <row r="13" spans="1:24" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="30"/>
-      <c r="B13" s="34"/>
+    <row r="13" spans="1:24" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="32"/>
+      <c r="B13" s="28"/>
       <c r="C13" s="10" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E13" s="12" t="s">
         <v>11</v>
@@ -1551,19 +1576,19 @@
       <c r="W13" s="2"/>
       <c r="X13" s="2"/>
     </row>
-    <row r="14" spans="1:24" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A14" s="31"/>
+    <row r="14" spans="1:24" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A14" s="33"/>
       <c r="B14" s="14" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D14" s="16" t="s">
         <v>10</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
@@ -1585,15 +1610,15 @@
       <c r="W14" s="2"/>
       <c r="X14" s="2"/>
     </row>
-    <row r="15" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="29" t="s">
-        <v>30</v>
+    <row r="15" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="31" t="s">
+        <v>28</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D15" s="8" t="s">
         <v>10</v>
@@ -1621,19 +1646,19 @@
       <c r="W15" s="2"/>
       <c r="X15" s="2"/>
     </row>
-    <row r="16" spans="1:24" ht="19.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="30"/>
+    <row r="16" spans="1:24" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="32"/>
       <c r="B16" s="13" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
@@ -1655,19 +1680,19 @@
       <c r="W16" s="2"/>
       <c r="X16" s="2"/>
     </row>
-    <row r="17" spans="1:24" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="31"/>
+    <row r="17" spans="1:24" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="33"/>
       <c r="B17" s="14" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D17" s="16" t="s">
         <v>10</v>
       </c>
       <c r="E17" s="17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
@@ -1689,21 +1714,21 @@
       <c r="W17" s="2"/>
       <c r="X17" s="2"/>
     </row>
-    <row r="18" spans="1:24" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A18" s="29" t="s">
-        <v>37</v>
+    <row r="18" spans="1:24" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A18" s="31" t="s">
+        <v>34</v>
       </c>
       <c r="B18" s="18" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D18" s="8" t="s">
         <v>10</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
@@ -1725,13 +1750,13 @@
       <c r="W18" s="2"/>
       <c r="X18" s="2"/>
     </row>
-    <row r="19" spans="1:24" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A19" s="30"/>
-      <c r="B19" s="35" t="s">
-        <v>40</v>
+    <row r="19" spans="1:24" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A19" s="32"/>
+      <c r="B19" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D19" s="11" t="s">
         <v>10</v>
@@ -1759,14 +1784,14 @@
       <c r="W19" s="2"/>
       <c r="X19" s="2"/>
     </row>
-    <row r="20" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="30"/>
-      <c r="B20" s="33"/>
+    <row r="20" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="32"/>
+      <c r="B20" s="27"/>
       <c r="C20" s="10" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E20" s="12" t="s">
         <v>11</v>
@@ -1791,14 +1816,14 @@
       <c r="W20" s="2"/>
       <c r="X20" s="2"/>
     </row>
-    <row r="21" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="30"/>
-      <c r="B21" s="34"/>
+    <row r="21" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="32"/>
+      <c r="B21" s="28"/>
       <c r="C21" s="19" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E21" s="12" t="s">
         <v>11</v>
@@ -1823,19 +1848,19 @@
       <c r="W21" s="2"/>
       <c r="X21" s="2"/>
     </row>
-    <row r="22" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="30"/>
+    <row r="22" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="32"/>
       <c r="B22" s="13" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
@@ -1857,16 +1882,16 @@
       <c r="W22" s="2"/>
       <c r="X22" s="2"/>
     </row>
-    <row r="23" spans="1:24" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A23" s="30"/>
+    <row r="23" spans="1:24" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A23" s="32"/>
       <c r="B23" s="13" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
-      <c r="C23" s="10" t="s">
-        <v>47</v>
+      <c r="C23" s="37" t="s">
+        <v>73</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E23" s="12" t="s">
         <v>11</v>
@@ -1891,16 +1916,16 @@
       <c r="W23" s="2"/>
       <c r="X23" s="2"/>
     </row>
-    <row r="24" spans="1:24" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="30"/>
-      <c r="B24" s="35" t="s">
-        <v>48</v>
+    <row r="24" spans="1:24" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="32"/>
+      <c r="B24" s="29" t="s">
+        <v>44</v>
       </c>
       <c r="C24" s="20" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D24" s="21" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E24" s="12" t="s">
         <v>11</v>
@@ -1925,17 +1950,17 @@
       <c r="W24" s="2"/>
       <c r="X24" s="2"/>
     </row>
-    <row r="25" spans="1:24" ht="16.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="31"/>
-      <c r="B25" s="36"/>
+    <row r="25" spans="1:24" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="33"/>
+      <c r="B25" s="30"/>
       <c r="C25" s="22" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D25" s="23" t="s">
         <v>10</v>
       </c>
       <c r="E25" s="17" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
@@ -1957,15 +1982,15 @@
       <c r="W25" s="2"/>
       <c r="X25" s="2"/>
     </row>
-    <row r="26" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="29" t="s">
-        <v>52</v>
+    <row r="26" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="31" t="s">
+        <v>48</v>
       </c>
-      <c r="B26" s="32" t="s">
-        <v>53</v>
+      <c r="B26" s="26" t="s">
+        <v>49</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D26" s="8" t="s">
         <v>10</v>
@@ -1993,17 +2018,17 @@
       <c r="W26" s="2"/>
       <c r="X26" s="2"/>
     </row>
-    <row r="27" spans="1:24" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="30"/>
-      <c r="B27" s="33"/>
+    <row r="27" spans="1:24" ht="17.45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="32"/>
+      <c r="B27" s="27"/>
       <c r="C27" s="10" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D27" s="11" t="s">
         <v>10</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
@@ -2025,17 +2050,17 @@
       <c r="W27" s="2"/>
       <c r="X27" s="2"/>
     </row>
-    <row r="28" spans="1:24" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="31"/>
-      <c r="B28" s="36"/>
+    <row r="28" spans="1:24" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="33"/>
+      <c r="B28" s="30"/>
       <c r="C28" s="15" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E28" s="17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
@@ -2057,18 +2082,18 @@
       <c r="W28" s="2"/>
       <c r="X28" s="2"/>
     </row>
-    <row r="29" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="29" t="s">
-        <v>57</v>
+    <row r="29" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="31" t="s">
+        <v>53</v>
       </c>
-      <c r="B29" s="32" t="s">
-        <v>58</v>
+      <c r="B29" s="26" t="s">
+        <v>54</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>11</v>
@@ -2093,17 +2118,17 @@
       <c r="W29" s="2"/>
       <c r="X29" s="2"/>
     </row>
-    <row r="30" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="30"/>
-      <c r="B30" s="33"/>
-      <c r="C30" s="20" t="s">
-        <v>60</v>
+    <row r="30" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="32"/>
+      <c r="B30" s="27"/>
+      <c r="C30" s="38" t="s">
+        <v>74</v>
       </c>
       <c r="D30" s="21" t="s">
         <v>10</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
@@ -2125,11 +2150,11 @@
       <c r="W30" s="2"/>
       <c r="X30" s="2"/>
     </row>
-    <row r="31" spans="1:24" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="31"/>
-      <c r="B31" s="36"/>
+    <row r="31" spans="1:24" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="33"/>
+      <c r="B31" s="30"/>
       <c r="C31" s="22" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D31" s="23" t="s">
         <v>10</v>
@@ -2157,21 +2182,21 @@
       <c r="W31" s="2"/>
       <c r="X31" s="2"/>
     </row>
-    <row r="32" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="29" t="s">
-        <v>62</v>
+    <row r="32" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="31" t="s">
+        <v>57</v>
       </c>
-      <c r="B32" s="32" t="s">
-        <v>63</v>
+      <c r="B32" s="26" t="s">
+        <v>77</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D32" s="8" t="s">
         <v>10</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
@@ -2193,11 +2218,11 @@
       <c r="W32" s="2"/>
       <c r="X32" s="2"/>
     </row>
-    <row r="33" spans="1:24" ht="16.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="30"/>
-      <c r="B33" s="33"/>
+    <row r="33" spans="1:24" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="32"/>
+      <c r="B33" s="27"/>
       <c r="C33" s="10" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D33" s="11" t="s">
         <v>10</v>
@@ -2225,14 +2250,14 @@
       <c r="W33" s="2"/>
       <c r="X33" s="2"/>
     </row>
-    <row r="34" spans="1:24" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="30"/>
-      <c r="B34" s="34"/>
-      <c r="C34" s="10" t="s">
-        <v>66</v>
+    <row r="34" spans="1:24" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="32"/>
+      <c r="B34" s="28"/>
+      <c r="C34" s="37" t="s">
+        <v>80</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E34" s="12" t="s">
         <v>11</v>
@@ -2257,18 +2282,20 @@
       <c r="W34" s="2"/>
       <c r="X34" s="2"/>
     </row>
-    <row r="35" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="31"/>
+    <row r="35" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="33"/>
       <c r="B35" s="14" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D35" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="E35" s="17"/>
+      <c r="E35" s="17" t="s">
+        <v>83</v>
+      </c>
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
@@ -2289,21 +2316,21 @@
       <c r="W35" s="2"/>
       <c r="X35" s="2"/>
     </row>
-    <row r="36" spans="1:24" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="29" t="s">
-        <v>69</v>
+    <row r="36" spans="1:24" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="31" t="s">
+        <v>62</v>
       </c>
-      <c r="B36" s="32" t="s">
-        <v>70</v>
+      <c r="B36" s="26" t="s">
+        <v>63</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D36" s="8" t="s">
         <v>10</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
@@ -2325,17 +2352,17 @@
       <c r="W36" s="2"/>
       <c r="X36" s="2"/>
     </row>
-    <row r="37" spans="1:24" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="30"/>
-      <c r="B37" s="33"/>
-      <c r="C37" s="10" t="s">
-        <v>72</v>
+    <row r="37" spans="1:24" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="32"/>
+      <c r="B37" s="27"/>
+      <c r="C37" s="37" t="s">
+        <v>76</v>
       </c>
       <c r="D37" s="11" t="s">
         <v>10</v>
       </c>
       <c r="E37" s="12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F37" s="2"/>
       <c r="G37" s="2"/>
@@ -2357,14 +2384,14 @@
       <c r="W37" s="2"/>
       <c r="X37" s="2"/>
     </row>
-    <row r="38" spans="1:24" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="30"/>
-      <c r="B38" s="34"/>
-      <c r="C38" s="10" t="s">
-        <v>73</v>
+    <row r="38" spans="1:24" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="32"/>
+      <c r="B38" s="28"/>
+      <c r="C38" s="37" t="s">
+        <v>81</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E38" s="12" t="s">
         <v>11</v>
@@ -2389,19 +2416,19 @@
       <c r="W38" s="2"/>
       <c r="X38" s="2"/>
     </row>
-    <row r="39" spans="1:24" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A39" s="30"/>
+    <row r="39" spans="1:24" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A39" s="32"/>
       <c r="B39" s="13" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
-      <c r="C39" s="10" t="s">
-        <v>75</v>
+      <c r="C39" s="37" t="s">
+        <v>78</v>
       </c>
       <c r="D39" s="11" t="s">
         <v>10</v>
       </c>
       <c r="E39" s="12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F39" s="2"/>
       <c r="G39" s="2"/>
@@ -2423,19 +2450,19 @@
       <c r="W39" s="2"/>
       <c r="X39" s="2"/>
     </row>
-    <row r="40" spans="1:24" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A40" s="31"/>
+    <row r="40" spans="1:24" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A40" s="33"/>
       <c r="B40" s="14" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
-      <c r="C40" s="15" t="s">
-        <v>77</v>
+      <c r="C40" s="39" t="s">
+        <v>79</v>
       </c>
       <c r="D40" s="16" t="s">
         <v>10</v>
       </c>
       <c r="E40" s="17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
@@ -2457,21 +2484,21 @@
       <c r="W40" s="2"/>
       <c r="X40" s="2"/>
     </row>
-    <row r="41" spans="1:24" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="29" t="s">
-        <v>78</v>
+    <row r="41" spans="1:24" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="31" t="s">
+        <v>67</v>
       </c>
-      <c r="B41" s="32" t="s">
-        <v>79</v>
+      <c r="B41" s="26" t="s">
+        <v>68</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="D41" s="8" t="s">
         <v>10</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
@@ -2493,14 +2520,14 @@
       <c r="W41" s="2"/>
       <c r="X41" s="2"/>
     </row>
-    <row r="42" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A42" s="30"/>
-      <c r="B42" s="34"/>
-      <c r="C42" s="10" t="s">
-        <v>81</v>
+    <row r="42" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A42" s="32"/>
+      <c r="B42" s="28"/>
+      <c r="C42" s="37" t="s">
+        <v>82</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E42" s="12"/>
       <c r="F42" s="2"/>
@@ -2523,10 +2550,10 @@
       <c r="W42" s="2"/>
       <c r="X42" s="2"/>
     </row>
-    <row r="43" spans="1:24" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="31"/>
+    <row r="43" spans="1:24" ht="42.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="33"/>
       <c r="B43" s="14" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="C43" s="15"/>
       <c r="D43" s="16"/>
@@ -2551,7 +2578,7 @@
       <c r="W43" s="2"/>
       <c r="X43" s="2"/>
     </row>
-    <row r="44" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A44" s="24"/>
       <c r="B44" s="25"/>
       <c r="C44" s="25"/>
@@ -2577,7 +2604,7 @@
       <c r="W44" s="2"/>
       <c r="X44" s="2"/>
     </row>
-    <row r="45" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A45" s="24"/>
       <c r="B45" s="25"/>
       <c r="C45" s="25"/>
@@ -2603,7 +2630,7 @@
       <c r="W45" s="2"/>
       <c r="X45" s="2"/>
     </row>
-    <row r="46" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A46" s="24"/>
       <c r="B46" s="25"/>
       <c r="C46" s="25"/>
@@ -2629,7 +2656,7 @@
       <c r="W46" s="2"/>
       <c r="X46" s="2"/>
     </row>
-    <row r="47" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A47" s="24"/>
       <c r="B47" s="25"/>
       <c r="C47" s="25"/>
@@ -2655,7 +2682,7 @@
       <c r="W47" s="2"/>
       <c r="X47" s="2"/>
     </row>
-    <row r="48" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A48" s="24"/>
       <c r="B48" s="25"/>
       <c r="C48" s="25"/>
@@ -2681,7 +2708,7 @@
       <c r="W48" s="2"/>
       <c r="X48" s="2"/>
     </row>
-    <row r="49" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A49" s="24"/>
       <c r="B49" s="25"/>
       <c r="C49" s="25"/>
@@ -2707,7 +2734,7 @@
       <c r="W49" s="2"/>
       <c r="X49" s="2"/>
     </row>
-    <row r="50" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A50" s="24"/>
       <c r="B50" s="24"/>
       <c r="C50" s="24"/>
@@ -2733,7 +2760,7 @@
       <c r="W50" s="2"/>
       <c r="X50" s="2"/>
     </row>
-    <row r="51" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A51" s="24"/>
       <c r="B51" s="24"/>
       <c r="C51" s="24"/>
@@ -2759,7 +2786,7 @@
       <c r="W51" s="2"/>
       <c r="X51" s="2"/>
     </row>
-    <row r="52" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A52" s="24"/>
       <c r="B52" s="24"/>
       <c r="C52" s="24"/>
@@ -2785,7 +2812,7 @@
       <c r="W52" s="2"/>
       <c r="X52" s="2"/>
     </row>
-    <row r="53" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A53" s="24"/>
       <c r="B53" s="24"/>
       <c r="C53" s="24"/>
@@ -2811,7 +2838,7 @@
       <c r="W53" s="2"/>
       <c r="X53" s="2"/>
     </row>
-    <row r="54" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A54" s="24"/>
       <c r="B54" s="24"/>
       <c r="C54" s="24"/>
@@ -2837,7 +2864,7 @@
       <c r="W54" s="2"/>
       <c r="X54" s="2"/>
     </row>
-    <row r="55" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A55" s="24"/>
       <c r="B55" s="24"/>
       <c r="C55" s="24"/>
@@ -2863,7 +2890,7 @@
       <c r="W55" s="2"/>
       <c r="X55" s="2"/>
     </row>
-    <row r="56" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A56" s="24"/>
       <c r="B56" s="24"/>
       <c r="C56" s="24"/>
@@ -2889,7 +2916,7 @@
       <c r="W56" s="2"/>
       <c r="X56" s="2"/>
     </row>
-    <row r="57" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A57" s="24"/>
       <c r="B57" s="24"/>
       <c r="C57" s="24"/>
@@ -2915,7 +2942,7 @@
       <c r="W57" s="2"/>
       <c r="X57" s="2"/>
     </row>
-    <row r="58" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A58" s="24"/>
       <c r="B58" s="24"/>
       <c r="C58" s="24"/>
@@ -2941,7 +2968,7 @@
       <c r="W58" s="2"/>
       <c r="X58" s="2"/>
     </row>
-    <row r="59" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A59" s="24"/>
       <c r="B59" s="24"/>
       <c r="C59" s="24"/>
@@ -2967,7 +2994,7 @@
       <c r="W59" s="2"/>
       <c r="X59" s="2"/>
     </row>
-    <row r="60" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A60" s="24"/>
       <c r="B60" s="24"/>
       <c r="C60" s="24"/>
@@ -2993,7 +3020,7 @@
       <c r="W60" s="2"/>
       <c r="X60" s="2"/>
     </row>
-    <row r="61" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A61" s="24"/>
       <c r="B61" s="24"/>
       <c r="C61" s="24"/>
@@ -3019,7 +3046,7 @@
       <c r="W61" s="2"/>
       <c r="X61" s="2"/>
     </row>
-    <row r="62" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A62" s="24"/>
       <c r="B62" s="24"/>
       <c r="C62" s="24"/>
@@ -3045,7 +3072,7 @@
       <c r="W62" s="2"/>
       <c r="X62" s="2"/>
     </row>
-    <row r="63" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A63" s="24"/>
       <c r="B63" s="24"/>
       <c r="C63" s="24"/>
@@ -3071,7 +3098,7 @@
       <c r="W63" s="2"/>
       <c r="X63" s="2"/>
     </row>
-    <row r="64" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A64" s="24"/>
       <c r="B64" s="24"/>
       <c r="C64" s="24"/>
@@ -3097,7 +3124,7 @@
       <c r="W64" s="2"/>
       <c r="X64" s="2"/>
     </row>
-    <row r="65" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A65" s="24"/>
       <c r="B65" s="24"/>
       <c r="C65" s="24"/>
@@ -3123,7 +3150,7 @@
       <c r="W65" s="2"/>
       <c r="X65" s="2"/>
     </row>
-    <row r="66" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A66" s="24"/>
       <c r="B66" s="24"/>
       <c r="C66" s="24"/>
@@ -3149,7 +3176,7 @@
       <c r="W66" s="2"/>
       <c r="X66" s="2"/>
     </row>
-    <row r="67" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A67" s="24"/>
       <c r="B67" s="24"/>
       <c r="C67" s="24"/>
@@ -3175,7 +3202,7 @@
       <c r="W67" s="2"/>
       <c r="X67" s="2"/>
     </row>
-    <row r="68" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A68" s="24"/>
       <c r="B68" s="24"/>
       <c r="C68" s="24"/>
@@ -3201,7 +3228,7 @@
       <c r="W68" s="2"/>
       <c r="X68" s="2"/>
     </row>
-    <row r="69" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A69" s="24"/>
       <c r="B69" s="24"/>
       <c r="C69" s="24"/>
@@ -3227,7 +3254,7 @@
       <c r="W69" s="2"/>
       <c r="X69" s="2"/>
     </row>
-    <row r="70" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A70" s="24"/>
       <c r="B70" s="24"/>
       <c r="C70" s="24"/>
@@ -3253,7 +3280,7 @@
       <c r="W70" s="2"/>
       <c r="X70" s="2"/>
     </row>
-    <row r="71" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="24"/>
       <c r="B71" s="24"/>
       <c r="C71" s="24"/>
@@ -3279,7 +3306,7 @@
       <c r="W71" s="2"/>
       <c r="X71" s="2"/>
     </row>
-    <row r="72" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="24"/>
       <c r="B72" s="24"/>
       <c r="C72" s="24"/>
@@ -3305,7 +3332,7 @@
       <c r="W72" s="2"/>
       <c r="X72" s="2"/>
     </row>
-    <row r="73" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A73" s="24"/>
       <c r="B73" s="24"/>
       <c r="C73" s="24"/>
@@ -3331,7 +3358,7 @@
       <c r="W73" s="2"/>
       <c r="X73" s="2"/>
     </row>
-    <row r="74" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A74" s="24"/>
       <c r="B74" s="24"/>
       <c r="C74" s="24"/>
@@ -3357,7 +3384,7 @@
       <c r="W74" s="2"/>
       <c r="X74" s="2"/>
     </row>
-    <row r="75" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A75" s="24"/>
       <c r="B75" s="24"/>
       <c r="C75" s="24"/>
@@ -3383,7 +3410,7 @@
       <c r="W75" s="2"/>
       <c r="X75" s="2"/>
     </row>
-    <row r="76" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="24"/>
       <c r="B76" s="24"/>
       <c r="C76" s="24"/>
@@ -3409,7 +3436,7 @@
       <c r="W76" s="2"/>
       <c r="X76" s="2"/>
     </row>
-    <row r="77" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="24"/>
       <c r="B77" s="24"/>
       <c r="C77" s="24"/>
@@ -3435,7 +3462,7 @@
       <c r="W77" s="2"/>
       <c r="X77" s="2"/>
     </row>
-    <row r="78" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A78" s="24"/>
       <c r="B78" s="24"/>
       <c r="C78" s="24"/>
@@ -3461,7 +3488,7 @@
       <c r="W78" s="2"/>
       <c r="X78" s="2"/>
     </row>
-    <row r="79" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A79" s="24"/>
       <c r="B79" s="24"/>
       <c r="C79" s="24"/>
@@ -3487,7 +3514,7 @@
       <c r="W79" s="2"/>
       <c r="X79" s="2"/>
     </row>
-    <row r="80" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="24"/>
       <c r="B80" s="24"/>
       <c r="C80" s="24"/>
@@ -3513,7 +3540,7 @@
       <c r="W80" s="2"/>
       <c r="X80" s="2"/>
     </row>
-    <row r="81" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="24"/>
       <c r="B81" s="24"/>
       <c r="C81" s="24"/>
@@ -3539,7 +3566,7 @@
       <c r="W81" s="2"/>
       <c r="X81" s="2"/>
     </row>
-    <row r="82" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A82" s="24"/>
       <c r="B82" s="24"/>
       <c r="C82" s="24"/>
@@ -3565,7 +3592,7 @@
       <c r="W82" s="2"/>
       <c r="X82" s="2"/>
     </row>
-    <row r="83" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A83" s="24"/>
       <c r="B83" s="24"/>
       <c r="C83" s="24"/>
@@ -3591,7 +3618,7 @@
       <c r="W83" s="2"/>
       <c r="X83" s="2"/>
     </row>
-    <row r="84" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A84" s="24"/>
       <c r="B84" s="24"/>
       <c r="C84" s="24"/>
@@ -3617,7 +3644,7 @@
       <c r="W84" s="2"/>
       <c r="X84" s="2"/>
     </row>
-    <row r="85" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A85" s="24"/>
       <c r="B85" s="24"/>
       <c r="C85" s="24"/>
@@ -3643,7 +3670,7 @@
       <c r="W85" s="2"/>
       <c r="X85" s="2"/>
     </row>
-    <row r="86" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A86" s="24"/>
       <c r="B86" s="24"/>
       <c r="C86" s="24"/>
@@ -3669,7 +3696,7 @@
       <c r="W86" s="2"/>
       <c r="X86" s="2"/>
     </row>
-    <row r="87" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A87" s="24"/>
       <c r="B87" s="24"/>
       <c r="C87" s="24"/>
@@ -3695,7 +3722,7 @@
       <c r="W87" s="2"/>
       <c r="X87" s="2"/>
     </row>
-    <row r="88" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="24"/>
       <c r="B88" s="24"/>
       <c r="C88" s="24"/>
@@ -3721,7 +3748,7 @@
       <c r="W88" s="2"/>
       <c r="X88" s="2"/>
     </row>
-    <row r="89" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="24"/>
       <c r="B89" s="24"/>
       <c r="C89" s="24"/>
@@ -3747,7 +3774,7 @@
       <c r="W89" s="2"/>
       <c r="X89" s="2"/>
     </row>
-    <row r="90" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A90" s="24"/>
       <c r="B90" s="24"/>
       <c r="C90" s="24"/>
@@ -3773,7 +3800,7 @@
       <c r="W90" s="2"/>
       <c r="X90" s="2"/>
     </row>
-    <row r="91" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A91" s="24"/>
       <c r="B91" s="24"/>
       <c r="C91" s="24"/>
@@ -3799,7 +3826,7 @@
       <c r="W91" s="2"/>
       <c r="X91" s="2"/>
     </row>
-    <row r="92" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A92" s="24"/>
       <c r="B92" s="24"/>
       <c r="C92" s="24"/>
@@ -3825,7 +3852,7 @@
       <c r="W92" s="2"/>
       <c r="X92" s="2"/>
     </row>
-    <row r="93" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A93" s="24"/>
       <c r="B93" s="24"/>
       <c r="C93" s="24"/>
@@ -3851,7 +3878,7 @@
       <c r="W93" s="2"/>
       <c r="X93" s="2"/>
     </row>
-    <row r="94" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A94" s="24"/>
       <c r="B94" s="24"/>
       <c r="C94" s="24"/>
@@ -3877,7 +3904,7 @@
       <c r="W94" s="2"/>
       <c r="X94" s="2"/>
     </row>
-    <row r="95" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A95" s="24"/>
       <c r="B95" s="24"/>
       <c r="C95" s="24"/>
@@ -3903,7 +3930,7 @@
       <c r="W95" s="2"/>
       <c r="X95" s="2"/>
     </row>
-    <row r="96" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A96" s="24"/>
       <c r="B96" s="24"/>
       <c r="C96" s="24"/>
@@ -3929,7 +3956,7 @@
       <c r="W96" s="2"/>
       <c r="X96" s="2"/>
     </row>
-    <row r="97" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A97" s="24"/>
       <c r="B97" s="24"/>
       <c r="C97" s="24"/>
@@ -3955,7 +3982,7 @@
       <c r="W97" s="2"/>
       <c r="X97" s="2"/>
     </row>
-    <row r="98" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A98" s="24"/>
       <c r="B98" s="24"/>
       <c r="C98" s="24"/>
@@ -3981,7 +4008,7 @@
       <c r="W98" s="2"/>
       <c r="X98" s="2"/>
     </row>
-    <row r="99" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A99" s="24"/>
       <c r="B99" s="24"/>
       <c r="C99" s="24"/>
@@ -4007,7 +4034,7 @@
       <c r="W99" s="2"/>
       <c r="X99" s="2"/>
     </row>
-    <row r="100" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A100" s="24"/>
       <c r="B100" s="24"/>
       <c r="C100" s="24"/>
@@ -4033,7 +4060,7 @@
       <c r="W100" s="2"/>
       <c r="X100" s="2"/>
     </row>
-    <row r="101" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="24"/>
       <c r="B101" s="24"/>
       <c r="C101" s="24"/>
@@ -4059,7 +4086,7 @@
       <c r="W101" s="2"/>
       <c r="X101" s="2"/>
     </row>
-    <row r="102" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="24"/>
       <c r="B102" s="24"/>
       <c r="C102" s="24"/>
@@ -4085,7 +4112,7 @@
       <c r="W102" s="2"/>
       <c r="X102" s="2"/>
     </row>
-    <row r="103" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A103" s="24"/>
       <c r="B103" s="24"/>
       <c r="C103" s="24"/>
@@ -4111,7 +4138,7 @@
       <c r="W103" s="2"/>
       <c r="X103" s="2"/>
     </row>
-    <row r="104" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A104" s="24"/>
       <c r="B104" s="24"/>
       <c r="C104" s="24"/>
@@ -4137,7 +4164,7 @@
       <c r="W104" s="2"/>
       <c r="X104" s="2"/>
     </row>
-    <row r="105" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A105" s="24"/>
       <c r="B105" s="24"/>
       <c r="C105" s="24"/>
@@ -4163,7 +4190,7 @@
       <c r="W105" s="2"/>
       <c r="X105" s="2"/>
     </row>
-    <row r="106" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A106" s="24"/>
       <c r="B106" s="24"/>
       <c r="C106" s="24"/>
@@ -4189,7 +4216,7 @@
       <c r="W106" s="2"/>
       <c r="X106" s="2"/>
     </row>
-    <row r="107" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A107" s="24"/>
       <c r="B107" s="24"/>
       <c r="C107" s="24"/>
@@ -4215,7 +4242,7 @@
       <c r="W107" s="2"/>
       <c r="X107" s="2"/>
     </row>
-    <row r="108" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A108" s="24"/>
       <c r="B108" s="24"/>
       <c r="C108" s="24"/>
@@ -4241,7 +4268,7 @@
       <c r="W108" s="2"/>
       <c r="X108" s="2"/>
     </row>
-    <row r="109" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A109" s="24"/>
       <c r="B109" s="24"/>
       <c r="C109" s="24"/>
@@ -4267,7 +4294,7 @@
       <c r="W109" s="2"/>
       <c r="X109" s="2"/>
     </row>
-    <row r="110" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A110" s="24"/>
       <c r="B110" s="24"/>
       <c r="C110" s="24"/>
@@ -4293,7 +4320,7 @@
       <c r="W110" s="2"/>
       <c r="X110" s="2"/>
     </row>
-    <row r="111" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A111" s="24"/>
       <c r="B111" s="24"/>
       <c r="C111" s="24"/>
@@ -4319,7 +4346,7 @@
       <c r="W111" s="2"/>
       <c r="X111" s="2"/>
     </row>
-    <row r="112" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A112" s="24"/>
       <c r="B112" s="24"/>
       <c r="C112" s="24"/>
@@ -4345,7 +4372,7 @@
       <c r="W112" s="2"/>
       <c r="X112" s="2"/>
     </row>
-    <row r="113" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A113" s="24"/>
       <c r="B113" s="24"/>
       <c r="C113" s="24"/>
@@ -4371,7 +4398,7 @@
       <c r="W113" s="2"/>
       <c r="X113" s="2"/>
     </row>
-    <row r="114" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A114" s="24"/>
       <c r="B114" s="24"/>
       <c r="C114" s="24"/>
@@ -4397,7 +4424,7 @@
       <c r="W114" s="2"/>
       <c r="X114" s="2"/>
     </row>
-    <row r="115" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A115" s="24"/>
       <c r="B115" s="24"/>
       <c r="C115" s="24"/>
@@ -4423,7 +4450,7 @@
       <c r="W115" s="2"/>
       <c r="X115" s="2"/>
     </row>
-    <row r="116" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A116" s="24"/>
       <c r="B116" s="24"/>
       <c r="C116" s="24"/>
@@ -4449,7 +4476,7 @@
       <c r="W116" s="2"/>
       <c r="X116" s="2"/>
     </row>
-    <row r="117" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A117" s="24"/>
       <c r="B117" s="24"/>
       <c r="C117" s="24"/>
@@ -4475,7 +4502,7 @@
       <c r="W117" s="2"/>
       <c r="X117" s="2"/>
     </row>
-    <row r="118" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A118" s="24"/>
       <c r="B118" s="24"/>
       <c r="C118" s="24"/>
@@ -4501,7 +4528,7 @@
       <c r="W118" s="2"/>
       <c r="X118" s="2"/>
     </row>
-    <row r="119" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A119" s="24"/>
       <c r="B119" s="24"/>
       <c r="C119" s="24"/>
@@ -4527,7 +4554,7 @@
       <c r="W119" s="2"/>
       <c r="X119" s="2"/>
     </row>
-    <row r="120" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A120" s="24"/>
       <c r="B120" s="24"/>
       <c r="C120" s="24"/>
@@ -4553,7 +4580,7 @@
       <c r="W120" s="2"/>
       <c r="X120" s="2"/>
     </row>
-    <row r="121" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A121" s="24"/>
       <c r="B121" s="24"/>
       <c r="C121" s="24"/>
@@ -4579,7 +4606,7 @@
       <c r="W121" s="2"/>
       <c r="X121" s="2"/>
     </row>
-    <row r="122" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A122" s="24"/>
       <c r="B122" s="24"/>
       <c r="C122" s="24"/>
@@ -4605,7 +4632,7 @@
       <c r="W122" s="2"/>
       <c r="X122" s="2"/>
     </row>
-    <row r="123" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A123" s="24"/>
       <c r="B123" s="24"/>
       <c r="C123" s="24"/>
@@ -4631,7 +4658,7 @@
       <c r="W123" s="2"/>
       <c r="X123" s="2"/>
     </row>
-    <row r="124" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A124" s="24"/>
       <c r="B124" s="24"/>
       <c r="C124" s="24"/>
@@ -4657,7 +4684,7 @@
       <c r="W124" s="2"/>
       <c r="X124" s="2"/>
     </row>
-    <row r="125" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A125" s="24"/>
       <c r="B125" s="24"/>
       <c r="C125" s="24"/>
@@ -4683,7 +4710,7 @@
       <c r="W125" s="2"/>
       <c r="X125" s="2"/>
     </row>
-    <row r="126" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A126" s="24"/>
       <c r="B126" s="24"/>
       <c r="C126" s="24"/>
@@ -4709,7 +4736,7 @@
       <c r="W126" s="2"/>
       <c r="X126" s="2"/>
     </row>
-    <row r="127" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A127" s="24"/>
       <c r="B127" s="24"/>
       <c r="C127" s="24"/>
@@ -4735,7 +4762,7 @@
       <c r="W127" s="2"/>
       <c r="X127" s="2"/>
     </row>
-    <row r="128" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A128" s="24"/>
       <c r="B128" s="24"/>
       <c r="C128" s="24"/>
@@ -4761,7 +4788,7 @@
       <c r="W128" s="2"/>
       <c r="X128" s="2"/>
     </row>
-    <row r="129" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A129" s="24"/>
       <c r="B129" s="24"/>
       <c r="C129" s="24"/>
@@ -4787,7 +4814,7 @@
       <c r="W129" s="2"/>
       <c r="X129" s="2"/>
     </row>
-    <row r="130" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A130" s="24"/>
       <c r="B130" s="24"/>
       <c r="C130" s="24"/>
@@ -4813,7 +4840,7 @@
       <c r="W130" s="2"/>
       <c r="X130" s="2"/>
     </row>
-    <row r="131" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A131" s="24"/>
       <c r="B131" s="24"/>
       <c r="C131" s="24"/>
@@ -4839,7 +4866,7 @@
       <c r="W131" s="2"/>
       <c r="X131" s="2"/>
     </row>
-    <row r="132" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A132" s="24"/>
       <c r="B132" s="24"/>
       <c r="C132" s="24"/>
@@ -4865,7 +4892,7 @@
       <c r="W132" s="2"/>
       <c r="X132" s="2"/>
     </row>
-    <row r="133" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A133" s="24"/>
       <c r="B133" s="24"/>
       <c r="C133" s="24"/>
@@ -4891,7 +4918,7 @@
       <c r="W133" s="2"/>
       <c r="X133" s="2"/>
     </row>
-    <row r="134" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A134" s="24"/>
       <c r="B134" s="24"/>
       <c r="C134" s="24"/>
@@ -4917,7 +4944,7 @@
       <c r="W134" s="2"/>
       <c r="X134" s="2"/>
     </row>
-    <row r="135" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A135" s="24"/>
       <c r="B135" s="24"/>
       <c r="C135" s="24"/>
@@ -4943,7 +4970,7 @@
       <c r="W135" s="2"/>
       <c r="X135" s="2"/>
     </row>
-    <row r="136" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A136" s="24"/>
       <c r="B136" s="24"/>
       <c r="C136" s="24"/>
@@ -4969,7 +4996,7 @@
       <c r="W136" s="2"/>
       <c r="X136" s="2"/>
     </row>
-    <row r="137" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A137" s="24"/>
       <c r="B137" s="24"/>
       <c r="C137" s="24"/>
@@ -4995,7 +5022,7 @@
       <c r="W137" s="2"/>
       <c r="X137" s="2"/>
     </row>
-    <row r="138" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A138" s="24"/>
       <c r="B138" s="24"/>
       <c r="C138" s="24"/>
@@ -5021,7 +5048,7 @@
       <c r="W138" s="2"/>
       <c r="X138" s="2"/>
     </row>
-    <row r="139" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A139" s="24"/>
       <c r="B139" s="24"/>
       <c r="C139" s="24"/>
@@ -5047,7 +5074,7 @@
       <c r="W139" s="2"/>
       <c r="X139" s="2"/>
     </row>
-    <row r="140" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A140" s="24"/>
       <c r="B140" s="24"/>
       <c r="C140" s="24"/>
@@ -5073,7 +5100,7 @@
       <c r="W140" s="2"/>
       <c r="X140" s="2"/>
     </row>
-    <row r="141" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A141" s="24"/>
       <c r="B141" s="24"/>
       <c r="C141" s="24"/>
@@ -5099,7 +5126,7 @@
       <c r="W141" s="2"/>
       <c r="X141" s="2"/>
     </row>
-    <row r="142" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A142" s="24"/>
       <c r="B142" s="24"/>
       <c r="C142" s="24"/>
@@ -5125,7 +5152,7 @@
       <c r="W142" s="2"/>
       <c r="X142" s="2"/>
     </row>
-    <row r="143" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A143" s="24"/>
       <c r="B143" s="24"/>
       <c r="C143" s="24"/>
@@ -5151,7 +5178,7 @@
       <c r="W143" s="2"/>
       <c r="X143" s="2"/>
     </row>
-    <row r="144" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A144" s="24"/>
       <c r="B144" s="24"/>
       <c r="C144" s="24"/>
@@ -5177,7 +5204,7 @@
       <c r="W144" s="2"/>
       <c r="X144" s="2"/>
     </row>
-    <row r="145" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A145" s="24"/>
       <c r="B145" s="24"/>
       <c r="C145" s="24"/>
@@ -5203,7 +5230,7 @@
       <c r="W145" s="2"/>
       <c r="X145" s="2"/>
     </row>
-    <row r="146" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A146" s="24"/>
       <c r="B146" s="24"/>
       <c r="C146" s="24"/>
@@ -5229,7 +5256,7 @@
       <c r="W146" s="2"/>
       <c r="X146" s="2"/>
     </row>
-    <row r="147" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A147" s="24"/>
       <c r="B147" s="24"/>
       <c r="C147" s="24"/>
@@ -5255,7 +5282,7 @@
       <c r="W147" s="2"/>
       <c r="X147" s="2"/>
     </row>
-    <row r="148" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A148" s="24"/>
       <c r="B148" s="24"/>
       <c r="C148" s="24"/>
@@ -5281,7 +5308,7 @@
       <c r="W148" s="2"/>
       <c r="X148" s="2"/>
     </row>
-    <row r="149" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A149" s="24"/>
       <c r="B149" s="24"/>
       <c r="C149" s="24"/>
@@ -5307,7 +5334,7 @@
       <c r="W149" s="2"/>
       <c r="X149" s="2"/>
     </row>
-    <row r="150" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A150" s="24"/>
       <c r="B150" s="24"/>
       <c r="C150" s="24"/>
@@ -5333,7 +5360,7 @@
       <c r="W150" s="2"/>
       <c r="X150" s="2"/>
     </row>
-    <row r="151" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A151" s="24"/>
       <c r="B151" s="24"/>
       <c r="C151" s="24"/>
@@ -5359,7 +5386,7 @@
       <c r="W151" s="2"/>
       <c r="X151" s="2"/>
     </row>
-    <row r="152" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A152" s="24"/>
       <c r="B152" s="24"/>
       <c r="C152" s="24"/>
@@ -5385,7 +5412,7 @@
       <c r="W152" s="2"/>
       <c r="X152" s="2"/>
     </row>
-    <row r="153" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A153" s="24"/>
       <c r="B153" s="24"/>
       <c r="C153" s="24"/>
@@ -5411,7 +5438,7 @@
       <c r="W153" s="2"/>
       <c r="X153" s="2"/>
     </row>
-    <row r="154" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A154" s="24"/>
       <c r="B154" s="24"/>
       <c r="C154" s="24"/>
@@ -5437,7 +5464,7 @@
       <c r="W154" s="2"/>
       <c r="X154" s="2"/>
     </row>
-    <row r="155" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A155" s="24"/>
       <c r="B155" s="24"/>
       <c r="C155" s="24"/>
@@ -5463,7 +5490,7 @@
       <c r="W155" s="2"/>
       <c r="X155" s="2"/>
     </row>
-    <row r="156" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A156" s="24"/>
       <c r="B156" s="24"/>
       <c r="C156" s="24"/>
@@ -5489,7 +5516,7 @@
       <c r="W156" s="2"/>
       <c r="X156" s="2"/>
     </row>
-    <row r="157" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A157" s="24"/>
       <c r="B157" s="24"/>
       <c r="C157" s="24"/>
@@ -5515,7 +5542,7 @@
       <c r="W157" s="2"/>
       <c r="X157" s="2"/>
     </row>
-    <row r="158" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A158" s="24"/>
       <c r="B158" s="24"/>
       <c r="C158" s="24"/>
@@ -5541,7 +5568,7 @@
       <c r="W158" s="2"/>
       <c r="X158" s="2"/>
     </row>
-    <row r="159" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A159" s="24"/>
       <c r="B159" s="24"/>
       <c r="C159" s="24"/>
@@ -5567,7 +5594,7 @@
       <c r="W159" s="2"/>
       <c r="X159" s="2"/>
     </row>
-    <row r="160" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A160" s="24"/>
       <c r="B160" s="24"/>
       <c r="C160" s="24"/>
@@ -5593,7 +5620,7 @@
       <c r="W160" s="2"/>
       <c r="X160" s="2"/>
     </row>
-    <row r="161" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A161" s="24"/>
       <c r="B161" s="24"/>
       <c r="C161" s="24"/>
@@ -5619,7 +5646,7 @@
       <c r="W161" s="2"/>
       <c r="X161" s="2"/>
     </row>
-    <row r="162" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A162" s="24"/>
       <c r="B162" s="24"/>
       <c r="C162" s="24"/>
@@ -5645,7 +5672,7 @@
       <c r="W162" s="2"/>
       <c r="X162" s="2"/>
     </row>
-    <row r="163" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A163" s="24"/>
       <c r="B163" s="24"/>
       <c r="C163" s="24"/>
@@ -5671,7 +5698,7 @@
       <c r="W163" s="2"/>
       <c r="X163" s="2"/>
     </row>
-    <row r="164" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A164" s="24"/>
       <c r="B164" s="24"/>
       <c r="C164" s="24"/>
@@ -5697,7 +5724,7 @@
       <c r="W164" s="2"/>
       <c r="X164" s="2"/>
     </row>
-    <row r="165" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A165" s="24"/>
       <c r="B165" s="24"/>
       <c r="C165" s="24"/>
@@ -5723,7 +5750,7 @@
       <c r="W165" s="2"/>
       <c r="X165" s="2"/>
     </row>
-    <row r="166" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A166" s="24"/>
       <c r="B166" s="24"/>
       <c r="C166" s="24"/>
@@ -5749,7 +5776,7 @@
       <c r="W166" s="2"/>
       <c r="X166" s="2"/>
     </row>
-    <row r="167" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A167" s="24"/>
       <c r="B167" s="24"/>
       <c r="C167" s="24"/>
@@ -5775,7 +5802,7 @@
       <c r="W167" s="2"/>
       <c r="X167" s="2"/>
     </row>
-    <row r="168" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A168" s="24"/>
       <c r="B168" s="24"/>
       <c r="C168" s="24"/>
@@ -5801,7 +5828,7 @@
       <c r="W168" s="2"/>
       <c r="X168" s="2"/>
     </row>
-    <row r="169" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A169" s="24"/>
       <c r="B169" s="24"/>
       <c r="C169" s="24"/>
@@ -5827,7 +5854,7 @@
       <c r="W169" s="2"/>
       <c r="X169" s="2"/>
     </row>
-    <row r="170" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A170" s="24"/>
       <c r="B170" s="24"/>
       <c r="C170" s="24"/>
@@ -5853,7 +5880,7 @@
       <c r="W170" s="2"/>
       <c r="X170" s="2"/>
     </row>
-    <row r="171" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A171" s="24"/>
       <c r="B171" s="24"/>
       <c r="C171" s="24"/>
@@ -5879,7 +5906,7 @@
       <c r="W171" s="2"/>
       <c r="X171" s="2"/>
     </row>
-    <row r="172" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A172" s="24"/>
       <c r="B172" s="24"/>
       <c r="C172" s="24"/>
@@ -5905,7 +5932,7 @@
       <c r="W172" s="2"/>
       <c r="X172" s="2"/>
     </row>
-    <row r="173" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A173" s="24"/>
       <c r="B173" s="24"/>
       <c r="C173" s="24"/>
@@ -5931,7 +5958,7 @@
       <c r="W173" s="2"/>
       <c r="X173" s="2"/>
     </row>
-    <row r="174" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A174" s="24"/>
       <c r="B174" s="24"/>
       <c r="C174" s="24"/>
@@ -5957,7 +5984,7 @@
       <c r="W174" s="2"/>
       <c r="X174" s="2"/>
     </row>
-    <row r="175" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A175" s="24"/>
       <c r="B175" s="24"/>
       <c r="C175" s="24"/>
@@ -5983,7 +6010,7 @@
       <c r="W175" s="2"/>
       <c r="X175" s="2"/>
     </row>
-    <row r="176" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A176" s="24"/>
       <c r="B176" s="24"/>
       <c r="C176" s="24"/>
@@ -6009,7 +6036,7 @@
       <c r="W176" s="2"/>
       <c r="X176" s="2"/>
     </row>
-    <row r="177" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A177" s="24"/>
       <c r="B177" s="24"/>
       <c r="C177" s="24"/>
@@ -6035,7 +6062,7 @@
       <c r="W177" s="2"/>
       <c r="X177" s="2"/>
     </row>
-    <row r="178" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A178" s="24"/>
       <c r="B178" s="24"/>
       <c r="C178" s="24"/>
@@ -6061,7 +6088,7 @@
       <c r="W178" s="2"/>
       <c r="X178" s="2"/>
     </row>
-    <row r="179" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A179" s="24"/>
       <c r="B179" s="24"/>
       <c r="C179" s="24"/>
@@ -6087,7 +6114,7 @@
       <c r="W179" s="2"/>
       <c r="X179" s="2"/>
     </row>
-    <row r="180" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A180" s="24"/>
       <c r="B180" s="24"/>
       <c r="C180" s="24"/>
@@ -6113,7 +6140,7 @@
       <c r="W180" s="2"/>
       <c r="X180" s="2"/>
     </row>
-    <row r="181" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A181" s="24"/>
       <c r="B181" s="24"/>
       <c r="C181" s="24"/>
@@ -6139,7 +6166,7 @@
       <c r="W181" s="2"/>
       <c r="X181" s="2"/>
     </row>
-    <row r="182" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A182" s="24"/>
       <c r="B182" s="24"/>
       <c r="C182" s="24"/>
@@ -6165,7 +6192,7 @@
       <c r="W182" s="2"/>
       <c r="X182" s="2"/>
     </row>
-    <row r="183" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A183" s="24"/>
       <c r="B183" s="24"/>
       <c r="C183" s="24"/>
@@ -6191,7 +6218,7 @@
       <c r="W183" s="2"/>
       <c r="X183" s="2"/>
     </row>
-    <row r="184" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A184" s="24"/>
       <c r="B184" s="24"/>
       <c r="C184" s="24"/>
@@ -6217,7 +6244,7 @@
       <c r="W184" s="2"/>
       <c r="X184" s="2"/>
     </row>
-    <row r="185" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A185" s="24"/>
       <c r="B185" s="24"/>
       <c r="C185" s="24"/>
@@ -6243,7 +6270,7 @@
       <c r="W185" s="2"/>
       <c r="X185" s="2"/>
     </row>
-    <row r="186" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A186" s="24"/>
       <c r="B186" s="24"/>
       <c r="C186" s="24"/>
@@ -6269,7 +6296,7 @@
       <c r="W186" s="2"/>
       <c r="X186" s="2"/>
     </row>
-    <row r="187" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A187" s="24"/>
       <c r="B187" s="24"/>
       <c r="C187" s="24"/>
@@ -6295,7 +6322,7 @@
       <c r="W187" s="2"/>
       <c r="X187" s="2"/>
     </row>
-    <row r="188" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A188" s="24"/>
       <c r="B188" s="24"/>
       <c r="C188" s="24"/>
@@ -6321,7 +6348,7 @@
       <c r="W188" s="2"/>
       <c r="X188" s="2"/>
     </row>
-    <row r="189" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A189" s="24"/>
       <c r="B189" s="24"/>
       <c r="C189" s="24"/>
@@ -6347,7 +6374,7 @@
       <c r="W189" s="2"/>
       <c r="X189" s="2"/>
     </row>
-    <row r="190" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A190" s="24"/>
       <c r="B190" s="24"/>
       <c r="C190" s="24"/>
@@ -6373,7 +6400,7 @@
       <c r="W190" s="2"/>
       <c r="X190" s="2"/>
     </row>
-    <row r="191" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A191" s="24"/>
       <c r="B191" s="24"/>
       <c r="C191" s="24"/>
@@ -6399,7 +6426,7 @@
       <c r="W191" s="2"/>
       <c r="X191" s="2"/>
     </row>
-    <row r="192" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A192" s="24"/>
       <c r="B192" s="24"/>
       <c r="C192" s="24"/>
@@ -6425,7 +6452,7 @@
       <c r="W192" s="2"/>
       <c r="X192" s="2"/>
     </row>
-    <row r="193" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A193" s="24"/>
       <c r="B193" s="24"/>
       <c r="C193" s="24"/>
@@ -6451,7 +6478,7 @@
       <c r="W193" s="2"/>
       <c r="X193" s="2"/>
     </row>
-    <row r="194" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A194" s="24"/>
       <c r="B194" s="24"/>
       <c r="C194" s="24"/>
@@ -6477,7 +6504,7 @@
       <c r="W194" s="2"/>
       <c r="X194" s="2"/>
     </row>
-    <row r="195" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A195" s="24"/>
       <c r="B195" s="24"/>
       <c r="C195" s="24"/>
@@ -6503,7 +6530,7 @@
       <c r="W195" s="2"/>
       <c r="X195" s="2"/>
     </row>
-    <row r="196" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A196" s="24"/>
       <c r="B196" s="24"/>
       <c r="C196" s="24"/>
@@ -6529,7 +6556,7 @@
       <c r="W196" s="2"/>
       <c r="X196" s="2"/>
     </row>
-    <row r="197" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A197" s="24"/>
       <c r="B197" s="24"/>
       <c r="C197" s="24"/>
@@ -6555,7 +6582,7 @@
       <c r="W197" s="2"/>
       <c r="X197" s="2"/>
     </row>
-    <row r="198" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A198" s="24"/>
       <c r="B198" s="24"/>
       <c r="C198" s="24"/>
@@ -6581,7 +6608,7 @@
       <c r="W198" s="2"/>
       <c r="X198" s="2"/>
     </row>
-    <row r="199" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A199" s="24"/>
       <c r="B199" s="24"/>
       <c r="C199" s="24"/>
@@ -6607,7 +6634,7 @@
       <c r="W199" s="2"/>
       <c r="X199" s="2"/>
     </row>
-    <row r="200" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A200" s="24"/>
       <c r="B200" s="24"/>
       <c r="C200" s="24"/>
@@ -6633,7 +6660,7 @@
       <c r="W200" s="2"/>
       <c r="X200" s="2"/>
     </row>
-    <row r="201" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A201" s="24"/>
       <c r="B201" s="24"/>
       <c r="C201" s="24"/>
@@ -6659,7 +6686,7 @@
       <c r="W201" s="2"/>
       <c r="X201" s="2"/>
     </row>
-    <row r="202" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A202" s="24"/>
       <c r="B202" s="24"/>
       <c r="C202" s="24"/>
@@ -6685,7 +6712,7 @@
       <c r="W202" s="2"/>
       <c r="X202" s="2"/>
     </row>
-    <row r="203" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A203" s="24"/>
       <c r="B203" s="24"/>
       <c r="C203" s="24"/>
@@ -6711,7 +6738,7 @@
       <c r="W203" s="2"/>
       <c r="X203" s="2"/>
     </row>
-    <row r="204" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A204" s="24"/>
       <c r="B204" s="24"/>
       <c r="C204" s="24"/>
@@ -6737,7 +6764,7 @@
       <c r="W204" s="2"/>
       <c r="X204" s="2"/>
     </row>
-    <row r="205" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A205" s="24"/>
       <c r="B205" s="24"/>
       <c r="C205" s="24"/>
@@ -6763,7 +6790,7 @@
       <c r="W205" s="2"/>
       <c r="X205" s="2"/>
     </row>
-    <row r="206" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A206" s="24"/>
       <c r="B206" s="24"/>
       <c r="C206" s="24"/>
@@ -6789,7 +6816,7 @@
       <c r="W206" s="2"/>
       <c r="X206" s="2"/>
     </row>
-    <row r="207" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A207" s="24"/>
       <c r="B207" s="24"/>
       <c r="C207" s="24"/>
@@ -6815,7 +6842,7 @@
       <c r="W207" s="2"/>
       <c r="X207" s="2"/>
     </row>
-    <row r="208" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A208" s="24"/>
       <c r="B208" s="24"/>
       <c r="C208" s="24"/>
@@ -6841,7 +6868,7 @@
       <c r="W208" s="2"/>
       <c r="X208" s="2"/>
     </row>
-    <row r="209" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A209" s="24"/>
       <c r="B209" s="24"/>
       <c r="C209" s="24"/>
@@ -6867,7 +6894,7 @@
       <c r="W209" s="2"/>
       <c r="X209" s="2"/>
     </row>
-    <row r="210" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A210" s="24"/>
       <c r="B210" s="24"/>
       <c r="C210" s="24"/>
@@ -6893,7 +6920,7 @@
       <c r="W210" s="2"/>
       <c r="X210" s="2"/>
     </row>
-    <row r="211" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A211" s="24"/>
       <c r="B211" s="24"/>
       <c r="C211" s="24"/>
@@ -6919,7 +6946,7 @@
       <c r="W211" s="2"/>
       <c r="X211" s="2"/>
     </row>
-    <row r="212" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A212" s="24"/>
       <c r="B212" s="24"/>
       <c r="C212" s="24"/>
@@ -6945,7 +6972,7 @@
       <c r="W212" s="2"/>
       <c r="X212" s="2"/>
     </row>
-    <row r="213" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A213" s="24"/>
       <c r="B213" s="24"/>
       <c r="C213" s="24"/>
@@ -6971,7 +6998,7 @@
       <c r="W213" s="2"/>
       <c r="X213" s="2"/>
     </row>
-    <row r="214" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A214" s="24"/>
       <c r="B214" s="24"/>
       <c r="C214" s="24"/>
@@ -6997,7 +7024,7 @@
       <c r="W214" s="2"/>
       <c r="X214" s="2"/>
     </row>
-    <row r="215" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A215" s="24"/>
       <c r="B215" s="24"/>
       <c r="C215" s="24"/>
@@ -7023,7 +7050,7 @@
       <c r="W215" s="2"/>
       <c r="X215" s="2"/>
     </row>
-    <row r="216" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A216" s="24"/>
       <c r="B216" s="24"/>
       <c r="C216" s="24"/>
@@ -7049,7 +7076,7 @@
       <c r="W216" s="2"/>
       <c r="X216" s="2"/>
     </row>
-    <row r="217" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A217" s="24"/>
       <c r="B217" s="24"/>
       <c r="C217" s="24"/>
@@ -7075,7 +7102,7 @@
       <c r="W217" s="2"/>
       <c r="X217" s="2"/>
     </row>
-    <row r="218" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A218" s="24"/>
       <c r="B218" s="24"/>
       <c r="C218" s="24"/>
@@ -7101,7 +7128,7 @@
       <c r="W218" s="2"/>
       <c r="X218" s="2"/>
     </row>
-    <row r="219" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A219" s="24"/>
       <c r="B219" s="24"/>
       <c r="C219" s="24"/>
@@ -7127,7 +7154,7 @@
       <c r="W219" s="2"/>
       <c r="X219" s="2"/>
     </row>
-    <row r="220" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A220" s="24"/>
       <c r="B220" s="24"/>
       <c r="C220" s="24"/>
@@ -7153,7 +7180,7 @@
       <c r="W220" s="2"/>
       <c r="X220" s="2"/>
     </row>
-    <row r="221" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A221" s="24"/>
       <c r="B221" s="24"/>
       <c r="C221" s="24"/>
@@ -7179,7 +7206,7 @@
       <c r="W221" s="2"/>
       <c r="X221" s="2"/>
     </row>
-    <row r="222" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A222" s="24"/>
       <c r="B222" s="24"/>
       <c r="C222" s="24"/>
@@ -7205,7 +7232,7 @@
       <c r="W222" s="2"/>
       <c r="X222" s="2"/>
     </row>
-    <row r="223" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A223" s="24"/>
       <c r="B223" s="24"/>
       <c r="C223" s="24"/>
@@ -7231,7 +7258,7 @@
       <c r="W223" s="2"/>
       <c r="X223" s="2"/>
     </row>
-    <row r="224" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A224" s="24"/>
       <c r="B224" s="24"/>
       <c r="C224" s="24"/>
@@ -7257,7 +7284,7 @@
       <c r="W224" s="2"/>
       <c r="X224" s="2"/>
     </row>
-    <row r="225" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A225" s="24"/>
       <c r="B225" s="24"/>
       <c r="C225" s="24"/>
@@ -7283,7 +7310,7 @@
       <c r="W225" s="2"/>
       <c r="X225" s="2"/>
     </row>
-    <row r="226" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A226" s="24"/>
       <c r="B226" s="24"/>
       <c r="C226" s="24"/>
@@ -7309,7 +7336,7 @@
       <c r="W226" s="2"/>
       <c r="X226" s="2"/>
     </row>
-    <row r="227" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A227" s="24"/>
       <c r="B227" s="24"/>
       <c r="C227" s="24"/>
@@ -7335,7 +7362,7 @@
       <c r="W227" s="2"/>
       <c r="X227" s="2"/>
     </row>
-    <row r="228" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A228" s="24"/>
       <c r="B228" s="24"/>
       <c r="C228" s="24"/>
@@ -7361,7 +7388,7 @@
       <c r="W228" s="2"/>
       <c r="X228" s="2"/>
     </row>
-    <row r="229" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A229" s="24"/>
       <c r="B229" s="24"/>
       <c r="C229" s="24"/>
@@ -7387,7 +7414,7 @@
       <c r="W229" s="2"/>
       <c r="X229" s="2"/>
     </row>
-    <row r="230" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A230" s="24"/>
       <c r="B230" s="24"/>
       <c r="C230" s="24"/>
@@ -7413,7 +7440,7 @@
       <c r="W230" s="2"/>
       <c r="X230" s="2"/>
     </row>
-    <row r="231" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A231" s="24"/>
       <c r="B231" s="24"/>
       <c r="C231" s="24"/>
@@ -7439,7 +7466,7 @@
       <c r="W231" s="2"/>
       <c r="X231" s="2"/>
     </row>
-    <row r="232" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A232" s="24"/>
       <c r="B232" s="24"/>
       <c r="C232" s="24"/>
@@ -7465,7 +7492,7 @@
       <c r="W232" s="2"/>
       <c r="X232" s="2"/>
     </row>
-    <row r="233" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A233" s="24"/>
       <c r="B233" s="24"/>
       <c r="C233" s="24"/>
@@ -7491,7 +7518,7 @@
       <c r="W233" s="2"/>
       <c r="X233" s="2"/>
     </row>
-    <row r="234" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A234" s="24"/>
       <c r="B234" s="24"/>
       <c r="C234" s="24"/>
@@ -7517,7 +7544,7 @@
       <c r="W234" s="2"/>
       <c r="X234" s="2"/>
     </row>
-    <row r="235" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A235" s="24"/>
       <c r="B235" s="24"/>
       <c r="C235" s="24"/>
@@ -7543,7 +7570,7 @@
       <c r="W235" s="2"/>
       <c r="X235" s="2"/>
     </row>
-    <row r="236" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A236" s="24"/>
       <c r="B236" s="24"/>
       <c r="C236" s="24"/>
@@ -7569,7 +7596,7 @@
       <c r="W236" s="2"/>
       <c r="X236" s="2"/>
     </row>
-    <row r="237" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A237" s="24"/>
       <c r="B237" s="24"/>
       <c r="C237" s="24"/>
@@ -7595,7 +7622,7 @@
       <c r="W237" s="2"/>
       <c r="X237" s="2"/>
     </row>
-    <row r="238" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A238" s="24"/>
       <c r="B238" s="24"/>
       <c r="C238" s="24"/>
@@ -7621,7 +7648,7 @@
       <c r="W238" s="2"/>
       <c r="X238" s="2"/>
     </row>
-    <row r="239" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A239" s="24"/>
       <c r="B239" s="24"/>
       <c r="C239" s="24"/>
@@ -7647,7 +7674,7 @@
       <c r="W239" s="2"/>
       <c r="X239" s="2"/>
     </row>
-    <row r="240" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A240" s="24"/>
       <c r="B240" s="24"/>
       <c r="C240" s="24"/>
@@ -7673,7 +7700,7 @@
       <c r="W240" s="2"/>
       <c r="X240" s="2"/>
     </row>
-    <row r="241" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A241" s="24"/>
       <c r="B241" s="24"/>
       <c r="C241" s="24"/>
@@ -7699,7 +7726,7 @@
       <c r="W241" s="2"/>
       <c r="X241" s="2"/>
     </row>
-    <row r="242" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A242" s="24"/>
       <c r="B242" s="24"/>
       <c r="C242" s="24"/>
@@ -7725,7 +7752,7 @@
       <c r="W242" s="2"/>
       <c r="X242" s="2"/>
     </row>
-    <row r="243" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A243" s="24"/>
       <c r="B243" s="24"/>
       <c r="C243" s="24"/>
@@ -7751,7 +7778,7 @@
       <c r="W243" s="2"/>
       <c r="X243" s="2"/>
     </row>
-    <row r="244" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A244" s="24"/>
       <c r="B244" s="24"/>
       <c r="C244" s="24"/>
@@ -7777,7 +7804,7 @@
       <c r="W244" s="2"/>
       <c r="X244" s="2"/>
     </row>
-    <row r="245" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A245" s="24"/>
       <c r="B245" s="24"/>
       <c r="C245" s="24"/>
@@ -7803,7 +7830,7 @@
       <c r="W245" s="2"/>
       <c r="X245" s="2"/>
     </row>
-    <row r="246" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A246" s="24"/>
       <c r="B246" s="24"/>
       <c r="C246" s="24"/>
@@ -7829,7 +7856,7 @@
       <c r="W246" s="2"/>
       <c r="X246" s="2"/>
     </row>
-    <row r="247" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A247" s="24"/>
       <c r="B247" s="24"/>
       <c r="C247" s="24"/>
@@ -7855,7 +7882,7 @@
       <c r="W247" s="2"/>
       <c r="X247" s="2"/>
     </row>
-    <row r="248" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A248" s="24"/>
       <c r="B248" s="24"/>
       <c r="C248" s="24"/>
@@ -7881,7 +7908,7 @@
       <c r="W248" s="2"/>
       <c r="X248" s="2"/>
     </row>
-    <row r="249" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A249" s="24"/>
       <c r="B249" s="24"/>
       <c r="C249" s="24"/>
@@ -7907,7 +7934,7 @@
       <c r="W249" s="2"/>
       <c r="X249" s="2"/>
     </row>
-    <row r="250" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A250" s="24"/>
       <c r="B250" s="24"/>
       <c r="C250" s="24"/>
@@ -7933,7 +7960,7 @@
       <c r="W250" s="2"/>
       <c r="X250" s="2"/>
     </row>
-    <row r="251" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A251" s="24"/>
       <c r="B251" s="24"/>
       <c r="C251" s="24"/>
@@ -7959,7 +7986,7 @@
       <c r="W251" s="2"/>
       <c r="X251" s="2"/>
     </row>
-    <row r="252" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A252" s="24"/>
       <c r="B252" s="24"/>
       <c r="C252" s="24"/>
@@ -7985,7 +8012,7 @@
       <c r="W252" s="2"/>
       <c r="X252" s="2"/>
     </row>
-    <row r="253" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A253" s="24"/>
       <c r="B253" s="24"/>
       <c r="C253" s="24"/>
@@ -8011,7 +8038,7 @@
       <c r="W253" s="2"/>
       <c r="X253" s="2"/>
     </row>
-    <row r="254" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A254" s="24"/>
       <c r="B254" s="24"/>
       <c r="C254" s="24"/>
@@ -8037,7 +8064,7 @@
       <c r="W254" s="2"/>
       <c r="X254" s="2"/>
     </row>
-    <row r="255" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A255" s="24"/>
       <c r="B255" s="24"/>
       <c r="C255" s="24"/>
@@ -8063,7 +8090,7 @@
       <c r="W255" s="2"/>
       <c r="X255" s="2"/>
     </row>
-    <row r="256" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A256" s="24"/>
       <c r="B256" s="24"/>
       <c r="C256" s="24"/>
@@ -8089,7 +8116,7 @@
       <c r="W256" s="2"/>
       <c r="X256" s="2"/>
     </row>
-    <row r="257" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A257" s="24"/>
       <c r="B257" s="24"/>
       <c r="C257" s="24"/>
@@ -8115,7 +8142,7 @@
       <c r="W257" s="2"/>
       <c r="X257" s="2"/>
     </row>
-    <row r="258" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A258" s="24"/>
       <c r="B258" s="24"/>
       <c r="C258" s="24"/>
@@ -8141,7 +8168,7 @@
       <c r="W258" s="2"/>
       <c r="X258" s="2"/>
     </row>
-    <row r="259" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A259" s="24"/>
       <c r="B259" s="24"/>
       <c r="C259" s="24"/>
@@ -8167,7 +8194,7 @@
       <c r="W259" s="2"/>
       <c r="X259" s="2"/>
     </row>
-    <row r="260" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A260" s="24"/>
       <c r="B260" s="24"/>
       <c r="C260" s="24"/>
@@ -8193,7 +8220,7 @@
       <c r="W260" s="2"/>
       <c r="X260" s="2"/>
     </row>
-    <row r="261" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A261" s="24"/>
       <c r="B261" s="24"/>
       <c r="C261" s="24"/>
@@ -8219,7 +8246,7 @@
       <c r="W261" s="2"/>
       <c r="X261" s="2"/>
     </row>
-    <row r="262" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A262" s="24"/>
       <c r="B262" s="24"/>
       <c r="C262" s="24"/>
@@ -8245,7 +8272,7 @@
       <c r="W262" s="2"/>
       <c r="X262" s="2"/>
     </row>
-    <row r="263" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A263" s="24"/>
       <c r="B263" s="24"/>
       <c r="C263" s="24"/>
@@ -8271,7 +8298,7 @@
       <c r="W263" s="2"/>
       <c r="X263" s="2"/>
     </row>
-    <row r="264" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A264" s="24"/>
       <c r="B264" s="24"/>
       <c r="C264" s="24"/>
@@ -8297,7 +8324,7 @@
       <c r="W264" s="2"/>
       <c r="X264" s="2"/>
     </row>
-    <row r="265" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A265" s="24"/>
       <c r="B265" s="24"/>
       <c r="C265" s="24"/>
@@ -8323,7 +8350,7 @@
       <c r="W265" s="2"/>
       <c r="X265" s="2"/>
     </row>
-    <row r="266" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A266" s="24"/>
       <c r="B266" s="24"/>
       <c r="C266" s="24"/>
@@ -8349,7 +8376,7 @@
       <c r="W266" s="2"/>
       <c r="X266" s="2"/>
     </row>
-    <row r="267" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A267" s="24"/>
       <c r="B267" s="24"/>
       <c r="C267" s="24"/>
@@ -8375,7 +8402,7 @@
       <c r="W267" s="2"/>
       <c r="X267" s="2"/>
     </row>
-    <row r="268" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A268" s="24"/>
       <c r="B268" s="24"/>
       <c r="C268" s="24"/>
@@ -8401,7 +8428,7 @@
       <c r="W268" s="2"/>
       <c r="X268" s="2"/>
     </row>
-    <row r="269" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A269" s="24"/>
       <c r="B269" s="24"/>
       <c r="C269" s="24"/>
@@ -8427,7 +8454,7 @@
       <c r="W269" s="2"/>
       <c r="X269" s="2"/>
     </row>
-    <row r="270" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A270" s="24"/>
       <c r="B270" s="24"/>
       <c r="C270" s="24"/>
@@ -8453,7 +8480,7 @@
       <c r="W270" s="2"/>
       <c r="X270" s="2"/>
     </row>
-    <row r="271" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A271" s="24"/>
       <c r="B271" s="24"/>
       <c r="C271" s="24"/>
@@ -8479,7 +8506,7 @@
       <c r="W271" s="2"/>
       <c r="X271" s="2"/>
     </row>
-    <row r="272" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A272" s="24"/>
       <c r="B272" s="24"/>
       <c r="C272" s="24"/>
@@ -8505,7 +8532,7 @@
       <c r="W272" s="2"/>
       <c r="X272" s="2"/>
     </row>
-    <row r="273" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A273" s="24"/>
       <c r="B273" s="24"/>
       <c r="C273" s="24"/>
@@ -8531,7 +8558,7 @@
       <c r="W273" s="2"/>
       <c r="X273" s="2"/>
     </row>
-    <row r="274" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A274" s="24"/>
       <c r="B274" s="24"/>
       <c r="C274" s="24"/>
@@ -8557,7 +8584,7 @@
       <c r="W274" s="2"/>
       <c r="X274" s="2"/>
     </row>
-    <row r="275" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A275" s="24"/>
       <c r="B275" s="24"/>
       <c r="C275" s="24"/>
@@ -8583,7 +8610,7 @@
       <c r="W275" s="2"/>
       <c r="X275" s="2"/>
     </row>
-    <row r="276" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A276" s="24"/>
       <c r="B276" s="24"/>
       <c r="C276" s="24"/>
@@ -8609,7 +8636,7 @@
       <c r="W276" s="2"/>
       <c r="X276" s="2"/>
     </row>
-    <row r="277" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A277" s="24"/>
       <c r="B277" s="24"/>
       <c r="C277" s="24"/>
@@ -8635,7 +8662,7 @@
       <c r="W277" s="2"/>
       <c r="X277" s="2"/>
     </row>
-    <row r="278" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A278" s="24"/>
       <c r="B278" s="24"/>
       <c r="C278" s="24"/>
@@ -8661,7 +8688,7 @@
       <c r="W278" s="2"/>
       <c r="X278" s="2"/>
     </row>
-    <row r="279" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A279" s="24"/>
       <c r="B279" s="24"/>
       <c r="C279" s="24"/>
@@ -8687,7 +8714,7 @@
       <c r="W279" s="2"/>
       <c r="X279" s="2"/>
     </row>
-    <row r="280" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A280" s="24"/>
       <c r="B280" s="24"/>
       <c r="C280" s="24"/>
@@ -8713,7 +8740,7 @@
       <c r="W280" s="2"/>
       <c r="X280" s="2"/>
     </row>
-    <row r="281" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A281" s="24"/>
       <c r="B281" s="24"/>
       <c r="C281" s="24"/>
@@ -8739,7 +8766,7 @@
       <c r="W281" s="2"/>
       <c r="X281" s="2"/>
     </row>
-    <row r="282" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A282" s="24"/>
       <c r="B282" s="24"/>
       <c r="C282" s="24"/>
@@ -8765,7 +8792,7 @@
       <c r="W282" s="2"/>
       <c r="X282" s="2"/>
     </row>
-    <row r="283" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A283" s="24"/>
       <c r="B283" s="24"/>
       <c r="C283" s="24"/>
@@ -8791,7 +8818,7 @@
       <c r="W283" s="2"/>
       <c r="X283" s="2"/>
     </row>
-    <row r="284" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A284" s="24"/>
       <c r="B284" s="24"/>
       <c r="C284" s="24"/>
@@ -8817,7 +8844,7 @@
       <c r="W284" s="2"/>
       <c r="X284" s="2"/>
     </row>
-    <row r="285" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A285" s="24"/>
       <c r="B285" s="24"/>
       <c r="C285" s="24"/>
@@ -8843,7 +8870,7 @@
       <c r="W285" s="2"/>
       <c r="X285" s="2"/>
     </row>
-    <row r="286" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A286" s="24"/>
       <c r="B286" s="24"/>
       <c r="C286" s="24"/>
@@ -8869,7 +8896,7 @@
       <c r="W286" s="2"/>
       <c r="X286" s="2"/>
     </row>
-    <row r="287" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A287" s="24"/>
       <c r="B287" s="24"/>
       <c r="C287" s="24"/>
@@ -8895,7 +8922,7 @@
       <c r="W287" s="2"/>
       <c r="X287" s="2"/>
     </row>
-    <row r="288" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A288" s="24"/>
       <c r="B288" s="24"/>
       <c r="C288" s="24"/>
@@ -8921,7 +8948,7 @@
       <c r="W288" s="2"/>
       <c r="X288" s="2"/>
     </row>
-    <row r="289" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A289" s="24"/>
       <c r="B289" s="24"/>
       <c r="C289" s="24"/>
@@ -8947,7 +8974,7 @@
       <c r="W289" s="2"/>
       <c r="X289" s="2"/>
     </row>
-    <row r="290" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A290" s="24"/>
       <c r="B290" s="24"/>
       <c r="C290" s="24"/>
@@ -8973,7 +9000,7 @@
       <c r="W290" s="2"/>
       <c r="X290" s="2"/>
     </row>
-    <row r="291" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A291" s="24"/>
       <c r="B291" s="24"/>
       <c r="C291" s="24"/>
@@ -8999,7 +9026,7 @@
       <c r="W291" s="2"/>
       <c r="X291" s="2"/>
     </row>
-    <row r="292" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A292" s="24"/>
       <c r="B292" s="24"/>
       <c r="C292" s="24"/>
@@ -9025,7 +9052,7 @@
       <c r="W292" s="2"/>
       <c r="X292" s="2"/>
     </row>
-    <row r="293" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A293" s="24"/>
       <c r="B293" s="24"/>
       <c r="C293" s="24"/>
@@ -9051,7 +9078,7 @@
       <c r="W293" s="2"/>
       <c r="X293" s="2"/>
     </row>
-    <row r="294" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A294" s="24"/>
       <c r="B294" s="24"/>
       <c r="C294" s="24"/>
@@ -9077,7 +9104,7 @@
       <c r="W294" s="2"/>
       <c r="X294" s="2"/>
     </row>
-    <row r="295" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A295" s="24"/>
       <c r="B295" s="24"/>
       <c r="C295" s="24"/>
@@ -9103,7 +9130,7 @@
       <c r="W295" s="2"/>
       <c r="X295" s="2"/>
     </row>
-    <row r="296" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A296" s="24"/>
       <c r="B296" s="24"/>
       <c r="C296" s="24"/>
@@ -9129,7 +9156,7 @@
       <c r="W296" s="2"/>
       <c r="X296" s="2"/>
     </row>
-    <row r="297" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A297" s="24"/>
       <c r="B297" s="24"/>
       <c r="C297" s="24"/>
@@ -9155,7 +9182,7 @@
       <c r="W297" s="2"/>
       <c r="X297" s="2"/>
     </row>
-    <row r="298" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A298" s="24"/>
       <c r="B298" s="24"/>
       <c r="C298" s="24"/>
@@ -9181,7 +9208,7 @@
       <c r="W298" s="2"/>
       <c r="X298" s="2"/>
     </row>
-    <row r="299" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A299" s="24"/>
       <c r="B299" s="24"/>
       <c r="C299" s="24"/>
@@ -9207,7 +9234,7 @@
       <c r="W299" s="2"/>
       <c r="X299" s="2"/>
     </row>
-    <row r="300" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A300" s="24"/>
       <c r="B300" s="24"/>
       <c r="C300" s="24"/>
@@ -9233,7 +9260,7 @@
       <c r="W300" s="2"/>
       <c r="X300" s="2"/>
     </row>
-    <row r="301" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A301" s="24"/>
       <c r="B301" s="24"/>
       <c r="C301" s="24"/>
@@ -9259,7 +9286,7 @@
       <c r="W301" s="2"/>
       <c r="X301" s="2"/>
     </row>
-    <row r="302" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A302" s="24"/>
       <c r="B302" s="24"/>
       <c r="C302" s="24"/>
@@ -9285,7 +9312,7 @@
       <c r="W302" s="2"/>
       <c r="X302" s="2"/>
     </row>
-    <row r="303" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A303" s="24"/>
       <c r="B303" s="24"/>
       <c r="C303" s="24"/>
@@ -9311,7 +9338,7 @@
       <c r="W303" s="2"/>
       <c r="X303" s="2"/>
     </row>
-    <row r="304" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A304" s="24"/>
       <c r="B304" s="24"/>
       <c r="C304" s="24"/>
@@ -9337,7 +9364,7 @@
       <c r="W304" s="2"/>
       <c r="X304" s="2"/>
     </row>
-    <row r="305" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A305" s="24"/>
       <c r="B305" s="24"/>
       <c r="C305" s="24"/>
@@ -9363,7 +9390,7 @@
       <c r="W305" s="2"/>
       <c r="X305" s="2"/>
     </row>
-    <row r="306" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A306" s="24"/>
       <c r="B306" s="24"/>
       <c r="C306" s="24"/>
@@ -9389,7 +9416,7 @@
       <c r="W306" s="2"/>
       <c r="X306" s="2"/>
     </row>
-    <row r="307" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A307" s="24"/>
       <c r="B307" s="24"/>
       <c r="C307" s="24"/>
@@ -9415,7 +9442,7 @@
       <c r="W307" s="2"/>
       <c r="X307" s="2"/>
     </row>
-    <row r="308" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A308" s="24"/>
       <c r="B308" s="24"/>
       <c r="C308" s="24"/>
@@ -9441,7 +9468,7 @@
       <c r="W308" s="2"/>
       <c r="X308" s="2"/>
     </row>
-    <row r="309" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A309" s="24"/>
       <c r="B309" s="24"/>
       <c r="C309" s="24"/>
@@ -9467,7 +9494,7 @@
       <c r="W309" s="2"/>
       <c r="X309" s="2"/>
     </row>
-    <row r="310" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A310" s="24"/>
       <c r="B310" s="24"/>
       <c r="C310" s="24"/>
@@ -9493,7 +9520,7 @@
       <c r="W310" s="2"/>
       <c r="X310" s="2"/>
     </row>
-    <row r="311" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A311" s="24"/>
       <c r="B311" s="24"/>
       <c r="C311" s="24"/>
@@ -9519,7 +9546,7 @@
       <c r="W311" s="2"/>
       <c r="X311" s="2"/>
     </row>
-    <row r="312" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A312" s="24"/>
       <c r="B312" s="24"/>
       <c r="C312" s="24"/>
@@ -9545,7 +9572,7 @@
       <c r="W312" s="2"/>
       <c r="X312" s="2"/>
     </row>
-    <row r="313" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A313" s="24"/>
       <c r="B313" s="24"/>
       <c r="C313" s="24"/>
@@ -9571,7 +9598,7 @@
       <c r="W313" s="2"/>
       <c r="X313" s="2"/>
     </row>
-    <row r="314" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A314" s="24"/>
       <c r="B314" s="24"/>
       <c r="C314" s="24"/>
@@ -9597,7 +9624,7 @@
       <c r="W314" s="2"/>
       <c r="X314" s="2"/>
     </row>
-    <row r="315" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A315" s="24"/>
       <c r="B315" s="24"/>
       <c r="C315" s="24"/>
@@ -9623,7 +9650,7 @@
       <c r="W315" s="2"/>
       <c r="X315" s="2"/>
     </row>
-    <row r="316" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A316" s="24"/>
       <c r="B316" s="24"/>
       <c r="C316" s="24"/>
@@ -9649,7 +9676,7 @@
       <c r="W316" s="2"/>
       <c r="X316" s="2"/>
     </row>
-    <row r="317" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A317" s="24"/>
       <c r="B317" s="24"/>
       <c r="C317" s="24"/>
@@ -9675,7 +9702,7 @@
       <c r="W317" s="2"/>
       <c r="X317" s="2"/>
     </row>
-    <row r="318" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A318" s="24"/>
       <c r="B318" s="24"/>
       <c r="C318" s="24"/>
@@ -9701,7 +9728,7 @@
       <c r="W318" s="2"/>
       <c r="X318" s="2"/>
     </row>
-    <row r="319" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A319" s="24"/>
       <c r="B319" s="24"/>
       <c r="C319" s="24"/>
@@ -9727,7 +9754,7 @@
       <c r="W319" s="2"/>
       <c r="X319" s="2"/>
     </row>
-    <row r="320" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A320" s="24"/>
       <c r="B320" s="24"/>
       <c r="C320" s="24"/>
@@ -9753,7 +9780,7 @@
       <c r="W320" s="2"/>
       <c r="X320" s="2"/>
     </row>
-    <row r="321" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A321" s="24"/>
       <c r="B321" s="24"/>
       <c r="C321" s="24"/>
@@ -9779,7 +9806,7 @@
       <c r="W321" s="2"/>
       <c r="X321" s="2"/>
     </row>
-    <row r="322" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A322" s="24"/>
       <c r="B322" s="24"/>
       <c r="C322" s="24"/>
@@ -9805,7 +9832,7 @@
       <c r="W322" s="2"/>
       <c r="X322" s="2"/>
     </row>
-    <row r="323" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A323" s="24"/>
       <c r="B323" s="24"/>
       <c r="C323" s="24"/>
@@ -9831,7 +9858,7 @@
       <c r="W323" s="2"/>
       <c r="X323" s="2"/>
     </row>
-    <row r="324" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A324" s="24"/>
       <c r="B324" s="24"/>
       <c r="C324" s="24"/>
@@ -9857,7 +9884,7 @@
       <c r="W324" s="2"/>
       <c r="X324" s="2"/>
     </row>
-    <row r="325" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A325" s="24"/>
       <c r="B325" s="24"/>
       <c r="C325" s="24"/>
@@ -9883,7 +9910,7 @@
       <c r="W325" s="2"/>
       <c r="X325" s="2"/>
     </row>
-    <row r="326" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A326" s="24"/>
       <c r="B326" s="24"/>
       <c r="C326" s="24"/>
@@ -9909,7 +9936,7 @@
       <c r="W326" s="2"/>
       <c r="X326" s="2"/>
     </row>
-    <row r="327" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A327" s="24"/>
       <c r="B327" s="24"/>
       <c r="C327" s="24"/>
@@ -9935,7 +9962,7 @@
       <c r="W327" s="2"/>
       <c r="X327" s="2"/>
     </row>
-    <row r="328" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A328" s="24"/>
       <c r="B328" s="24"/>
       <c r="C328" s="24"/>
@@ -9961,7 +9988,7 @@
       <c r="W328" s="2"/>
       <c r="X328" s="2"/>
     </row>
-    <row r="329" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A329" s="24"/>
       <c r="B329" s="24"/>
       <c r="C329" s="24"/>
@@ -9987,7 +10014,7 @@
       <c r="W329" s="2"/>
       <c r="X329" s="2"/>
     </row>
-    <row r="330" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A330" s="24"/>
       <c r="B330" s="24"/>
       <c r="C330" s="24"/>
@@ -10013,7 +10040,7 @@
       <c r="W330" s="2"/>
       <c r="X330" s="2"/>
     </row>
-    <row r="331" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A331" s="24"/>
       <c r="B331" s="24"/>
       <c r="C331" s="24"/>
@@ -10039,7 +10066,7 @@
       <c r="W331" s="2"/>
       <c r="X331" s="2"/>
     </row>
-    <row r="332" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A332" s="24"/>
       <c r="B332" s="24"/>
       <c r="C332" s="24"/>
@@ -10065,7 +10092,7 @@
       <c r="W332" s="2"/>
       <c r="X332" s="2"/>
     </row>
-    <row r="333" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A333" s="24"/>
       <c r="B333" s="24"/>
       <c r="C333" s="24"/>
@@ -10091,7 +10118,7 @@
       <c r="W333" s="2"/>
       <c r="X333" s="2"/>
     </row>
-    <row r="334" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A334" s="24"/>
       <c r="B334" s="24"/>
       <c r="C334" s="24"/>
@@ -10117,7 +10144,7 @@
       <c r="W334" s="2"/>
       <c r="X334" s="2"/>
     </row>
-    <row r="335" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A335" s="24"/>
       <c r="B335" s="24"/>
       <c r="C335" s="24"/>
@@ -10143,7 +10170,7 @@
       <c r="W335" s="2"/>
       <c r="X335" s="2"/>
     </row>
-    <row r="336" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A336" s="24"/>
       <c r="B336" s="24"/>
       <c r="C336" s="24"/>
@@ -10169,7 +10196,7 @@
       <c r="W336" s="2"/>
       <c r="X336" s="2"/>
     </row>
-    <row r="337" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A337" s="24"/>
       <c r="B337" s="24"/>
       <c r="C337" s="24"/>
@@ -10195,7 +10222,7 @@
       <c r="W337" s="2"/>
       <c r="X337" s="2"/>
     </row>
-    <row r="338" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A338" s="24"/>
       <c r="B338" s="24"/>
       <c r="C338" s="24"/>
@@ -10221,7 +10248,7 @@
       <c r="W338" s="2"/>
       <c r="X338" s="2"/>
     </row>
-    <row r="339" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A339" s="24"/>
       <c r="B339" s="24"/>
       <c r="C339" s="24"/>
@@ -10247,7 +10274,7 @@
       <c r="W339" s="2"/>
       <c r="X339" s="2"/>
     </row>
-    <row r="340" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A340" s="24"/>
       <c r="B340" s="24"/>
       <c r="C340" s="24"/>
@@ -10273,7 +10300,7 @@
       <c r="W340" s="2"/>
       <c r="X340" s="2"/>
     </row>
-    <row r="341" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A341" s="24"/>
       <c r="B341" s="24"/>
       <c r="C341" s="24"/>
@@ -10299,7 +10326,7 @@
       <c r="W341" s="2"/>
       <c r="X341" s="2"/>
     </row>
-    <row r="342" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A342" s="24"/>
       <c r="B342" s="24"/>
       <c r="C342" s="24"/>
@@ -10325,7 +10352,7 @@
       <c r="W342" s="2"/>
       <c r="X342" s="2"/>
     </row>
-    <row r="343" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A343" s="24"/>
       <c r="B343" s="24"/>
       <c r="C343" s="24"/>
@@ -10351,7 +10378,7 @@
       <c r="W343" s="2"/>
       <c r="X343" s="2"/>
     </row>
-    <row r="344" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A344" s="24"/>
       <c r="B344" s="24"/>
       <c r="C344" s="24"/>
@@ -10377,7 +10404,7 @@
       <c r="W344" s="2"/>
       <c r="X344" s="2"/>
     </row>
-    <row r="345" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A345" s="24"/>
       <c r="B345" s="24"/>
       <c r="C345" s="24"/>
@@ -10403,7 +10430,7 @@
       <c r="W345" s="2"/>
       <c r="X345" s="2"/>
     </row>
-    <row r="346" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A346" s="24"/>
       <c r="B346" s="24"/>
       <c r="C346" s="24"/>
@@ -10429,7 +10456,7 @@
       <c r="W346" s="2"/>
       <c r="X346" s="2"/>
     </row>
-    <row r="347" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A347" s="24"/>
       <c r="B347" s="24"/>
       <c r="C347" s="24"/>
@@ -10455,7 +10482,7 @@
       <c r="W347" s="2"/>
       <c r="X347" s="2"/>
     </row>
-    <row r="348" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A348" s="24"/>
       <c r="B348" s="24"/>
       <c r="C348" s="24"/>
@@ -10481,7 +10508,7 @@
       <c r="W348" s="2"/>
       <c r="X348" s="2"/>
     </row>
-    <row r="349" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A349" s="24"/>
       <c r="B349" s="24"/>
       <c r="C349" s="24"/>
@@ -10507,7 +10534,7 @@
       <c r="W349" s="2"/>
       <c r="X349" s="2"/>
     </row>
-    <row r="350" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A350" s="24"/>
       <c r="B350" s="24"/>
       <c r="C350" s="24"/>
@@ -10533,7 +10560,7 @@
       <c r="W350" s="2"/>
       <c r="X350" s="2"/>
     </row>
-    <row r="351" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A351" s="24"/>
       <c r="B351" s="24"/>
       <c r="C351" s="24"/>
@@ -10559,7 +10586,7 @@
       <c r="W351" s="2"/>
       <c r="X351" s="2"/>
     </row>
-    <row r="352" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A352" s="24"/>
       <c r="B352" s="24"/>
       <c r="C352" s="24"/>
@@ -10585,7 +10612,7 @@
       <c r="W352" s="2"/>
       <c r="X352" s="2"/>
     </row>
-    <row r="353" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A353" s="24"/>
       <c r="B353" s="24"/>
       <c r="C353" s="24"/>
@@ -10611,7 +10638,7 @@
       <c r="W353" s="2"/>
       <c r="X353" s="2"/>
     </row>
-    <row r="354" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A354" s="24"/>
       <c r="B354" s="24"/>
       <c r="C354" s="24"/>
@@ -10637,7 +10664,7 @@
       <c r="W354" s="2"/>
       <c r="X354" s="2"/>
     </row>
-    <row r="355" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A355" s="24"/>
       <c r="B355" s="24"/>
       <c r="C355" s="24"/>
@@ -10663,7 +10690,7 @@
       <c r="W355" s="2"/>
       <c r="X355" s="2"/>
     </row>
-    <row r="356" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A356" s="24"/>
       <c r="B356" s="24"/>
       <c r="C356" s="24"/>
@@ -10689,7 +10716,7 @@
       <c r="W356" s="2"/>
       <c r="X356" s="2"/>
     </row>
-    <row r="357" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A357" s="24"/>
       <c r="B357" s="24"/>
       <c r="C357" s="24"/>
@@ -10715,7 +10742,7 @@
       <c r="W357" s="2"/>
       <c r="X357" s="2"/>
     </row>
-    <row r="358" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A358" s="24"/>
       <c r="B358" s="24"/>
       <c r="C358" s="24"/>
@@ -10741,7 +10768,7 @@
       <c r="W358" s="2"/>
       <c r="X358" s="2"/>
     </row>
-    <row r="359" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A359" s="24"/>
       <c r="B359" s="24"/>
       <c r="C359" s="24"/>
@@ -10767,7 +10794,7 @@
       <c r="W359" s="2"/>
       <c r="X359" s="2"/>
     </row>
-    <row r="360" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A360" s="24"/>
       <c r="B360" s="24"/>
       <c r="C360" s="24"/>
@@ -10793,7 +10820,7 @@
       <c r="W360" s="2"/>
       <c r="X360" s="2"/>
     </row>
-    <row r="361" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A361" s="24"/>
       <c r="B361" s="24"/>
       <c r="C361" s="24"/>
@@ -10819,7 +10846,7 @@
       <c r="W361" s="2"/>
       <c r="X361" s="2"/>
     </row>
-    <row r="362" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A362" s="24"/>
       <c r="B362" s="24"/>
       <c r="C362" s="24"/>
@@ -10845,7 +10872,7 @@
       <c r="W362" s="2"/>
       <c r="X362" s="2"/>
     </row>
-    <row r="363" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A363" s="24"/>
       <c r="B363" s="24"/>
       <c r="C363" s="24"/>
@@ -10871,7 +10898,7 @@
       <c r="W363" s="2"/>
       <c r="X363" s="2"/>
     </row>
-    <row r="364" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A364" s="24"/>
       <c r="B364" s="24"/>
       <c r="C364" s="24"/>
@@ -10897,7 +10924,7 @@
       <c r="W364" s="2"/>
       <c r="X364" s="2"/>
     </row>
-    <row r="365" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A365" s="24"/>
       <c r="B365" s="24"/>
       <c r="C365" s="24"/>
@@ -10923,7 +10950,7 @@
       <c r="W365" s="2"/>
       <c r="X365" s="2"/>
     </row>
-    <row r="366" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A366" s="24"/>
       <c r="B366" s="24"/>
       <c r="C366" s="24"/>
@@ -10949,7 +10976,7 @@
       <c r="W366" s="2"/>
       <c r="X366" s="2"/>
     </row>
-    <row r="367" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A367" s="24"/>
       <c r="B367" s="24"/>
       <c r="C367" s="24"/>
@@ -10975,7 +11002,7 @@
       <c r="W367" s="2"/>
       <c r="X367" s="2"/>
     </row>
-    <row r="368" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A368" s="24"/>
       <c r="B368" s="24"/>
       <c r="C368" s="24"/>
@@ -11001,7 +11028,7 @@
       <c r="W368" s="2"/>
       <c r="X368" s="2"/>
     </row>
-    <row r="369" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A369" s="24"/>
       <c r="B369" s="24"/>
       <c r="C369" s="24"/>
@@ -11027,7 +11054,7 @@
       <c r="W369" s="2"/>
       <c r="X369" s="2"/>
     </row>
-    <row r="370" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A370" s="24"/>
       <c r="B370" s="24"/>
       <c r="C370" s="24"/>
@@ -11053,7 +11080,7 @@
       <c r="W370" s="2"/>
       <c r="X370" s="2"/>
     </row>
-    <row r="371" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A371" s="24"/>
       <c r="B371" s="24"/>
       <c r="C371" s="24"/>
@@ -11079,7 +11106,7 @@
       <c r="W371" s="2"/>
       <c r="X371" s="2"/>
     </row>
-    <row r="372" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A372" s="24"/>
       <c r="B372" s="24"/>
       <c r="C372" s="24"/>
@@ -11105,7 +11132,7 @@
       <c r="W372" s="2"/>
       <c r="X372" s="2"/>
     </row>
-    <row r="373" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A373" s="24"/>
       <c r="B373" s="24"/>
       <c r="C373" s="24"/>
@@ -11131,7 +11158,7 @@
       <c r="W373" s="2"/>
       <c r="X373" s="2"/>
     </row>
-    <row r="374" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A374" s="24"/>
       <c r="B374" s="24"/>
       <c r="C374" s="24"/>
@@ -11157,7 +11184,7 @@
       <c r="W374" s="2"/>
       <c r="X374" s="2"/>
     </row>
-    <row r="375" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A375" s="24"/>
       <c r="B375" s="24"/>
       <c r="C375" s="24"/>
@@ -11183,7 +11210,7 @@
       <c r="W375" s="2"/>
       <c r="X375" s="2"/>
     </row>
-    <row r="376" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A376" s="24"/>
       <c r="B376" s="24"/>
       <c r="C376" s="24"/>
@@ -11209,7 +11236,7 @@
       <c r="W376" s="2"/>
       <c r="X376" s="2"/>
     </row>
-    <row r="377" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A377" s="24"/>
       <c r="B377" s="24"/>
       <c r="C377" s="24"/>
@@ -11235,7 +11262,7 @@
       <c r="W377" s="2"/>
       <c r="X377" s="2"/>
     </row>
-    <row r="378" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A378" s="24"/>
       <c r="B378" s="24"/>
       <c r="C378" s="24"/>
@@ -11261,7 +11288,7 @@
       <c r="W378" s="2"/>
       <c r="X378" s="2"/>
     </row>
-    <row r="379" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A379" s="24"/>
       <c r="B379" s="24"/>
       <c r="C379" s="24"/>
@@ -11287,7 +11314,7 @@
       <c r="W379" s="2"/>
       <c r="X379" s="2"/>
     </row>
-    <row r="380" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A380" s="24"/>
       <c r="B380" s="24"/>
       <c r="C380" s="24"/>
@@ -11313,7 +11340,7 @@
       <c r="W380" s="2"/>
       <c r="X380" s="2"/>
     </row>
-    <row r="381" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A381" s="24"/>
       <c r="B381" s="24"/>
       <c r="C381" s="24"/>
@@ -11339,7 +11366,7 @@
       <c r="W381" s="2"/>
       <c r="X381" s="2"/>
     </row>
-    <row r="382" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A382" s="24"/>
       <c r="B382" s="24"/>
       <c r="C382" s="24"/>
@@ -11365,7 +11392,7 @@
       <c r="W382" s="2"/>
       <c r="X382" s="2"/>
     </row>
-    <row r="383" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A383" s="24"/>
       <c r="B383" s="24"/>
       <c r="C383" s="24"/>
@@ -11391,7 +11418,7 @@
       <c r="W383" s="2"/>
       <c r="X383" s="2"/>
     </row>
-    <row r="384" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A384" s="24"/>
       <c r="B384" s="24"/>
       <c r="C384" s="24"/>
@@ -11417,7 +11444,7 @@
       <c r="W384" s="2"/>
       <c r="X384" s="2"/>
     </row>
-    <row r="385" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A385" s="24"/>
       <c r="B385" s="24"/>
       <c r="C385" s="24"/>
@@ -11443,7 +11470,7 @@
       <c r="W385" s="2"/>
       <c r="X385" s="2"/>
     </row>
-    <row r="386" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A386" s="24"/>
       <c r="B386" s="24"/>
       <c r="C386" s="24"/>
@@ -11469,7 +11496,7 @@
       <c r="W386" s="2"/>
       <c r="X386" s="2"/>
     </row>
-    <row r="387" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A387" s="24"/>
       <c r="B387" s="24"/>
       <c r="C387" s="24"/>
@@ -11495,7 +11522,7 @@
       <c r="W387" s="2"/>
       <c r="X387" s="2"/>
     </row>
-    <row r="388" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A388" s="24"/>
       <c r="B388" s="24"/>
       <c r="C388" s="24"/>
@@ -11521,7 +11548,7 @@
       <c r="W388" s="2"/>
       <c r="X388" s="2"/>
     </row>
-    <row r="389" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A389" s="24"/>
       <c r="B389" s="24"/>
       <c r="C389" s="24"/>
@@ -11547,7 +11574,7 @@
       <c r="W389" s="2"/>
       <c r="X389" s="2"/>
     </row>
-    <row r="390" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A390" s="24"/>
       <c r="B390" s="24"/>
       <c r="C390" s="24"/>
@@ -11573,7 +11600,7 @@
       <c r="W390" s="2"/>
       <c r="X390" s="2"/>
     </row>
-    <row r="391" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A391" s="24"/>
       <c r="B391" s="24"/>
       <c r="C391" s="24"/>
@@ -11599,7 +11626,7 @@
       <c r="W391" s="2"/>
       <c r="X391" s="2"/>
     </row>
-    <row r="392" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A392" s="24"/>
       <c r="B392" s="24"/>
       <c r="C392" s="24"/>
@@ -11625,7 +11652,7 @@
       <c r="W392" s="2"/>
       <c r="X392" s="2"/>
     </row>
-    <row r="393" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A393" s="24"/>
       <c r="B393" s="24"/>
       <c r="C393" s="24"/>
@@ -11651,7 +11678,7 @@
       <c r="W393" s="2"/>
       <c r="X393" s="2"/>
     </row>
-    <row r="394" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A394" s="24"/>
       <c r="B394" s="24"/>
       <c r="C394" s="24"/>
@@ -11677,7 +11704,7 @@
       <c r="W394" s="2"/>
       <c r="X394" s="2"/>
     </row>
-    <row r="395" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A395" s="24"/>
       <c r="B395" s="24"/>
       <c r="C395" s="24"/>
@@ -11703,7 +11730,7 @@
       <c r="W395" s="2"/>
       <c r="X395" s="2"/>
     </row>
-    <row r="396" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A396" s="24"/>
       <c r="B396" s="24"/>
       <c r="C396" s="24"/>
@@ -11729,7 +11756,7 @@
       <c r="W396" s="2"/>
       <c r="X396" s="2"/>
     </row>
-    <row r="397" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A397" s="24"/>
       <c r="B397" s="24"/>
       <c r="C397" s="24"/>
@@ -11755,7 +11782,7 @@
       <c r="W397" s="2"/>
       <c r="X397" s="2"/>
     </row>
-    <row r="398" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A398" s="24"/>
       <c r="B398" s="24"/>
       <c r="C398" s="24"/>
@@ -11781,7 +11808,7 @@
       <c r="W398" s="2"/>
       <c r="X398" s="2"/>
     </row>
-    <row r="399" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A399" s="24"/>
       <c r="B399" s="24"/>
       <c r="C399" s="24"/>
@@ -11807,7 +11834,7 @@
       <c r="W399" s="2"/>
       <c r="X399" s="2"/>
     </row>
-    <row r="400" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A400" s="24"/>
       <c r="B400" s="24"/>
       <c r="C400" s="24"/>
@@ -11833,7 +11860,7 @@
       <c r="W400" s="2"/>
       <c r="X400" s="2"/>
     </row>
-    <row r="401" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A401" s="24"/>
       <c r="B401" s="24"/>
       <c r="C401" s="24"/>
@@ -11859,7 +11886,7 @@
       <c r="W401" s="2"/>
       <c r="X401" s="2"/>
     </row>
-    <row r="402" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A402" s="24"/>
       <c r="B402" s="24"/>
       <c r="C402" s="24"/>
@@ -11885,7 +11912,7 @@
       <c r="W402" s="2"/>
       <c r="X402" s="2"/>
     </row>
-    <row r="403" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A403" s="24"/>
       <c r="B403" s="24"/>
       <c r="C403" s="24"/>
@@ -11911,7 +11938,7 @@
       <c r="W403" s="2"/>
       <c r="X403" s="2"/>
     </row>
-    <row r="404" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A404" s="24"/>
       <c r="B404" s="24"/>
       <c r="C404" s="24"/>
@@ -11937,7 +11964,7 @@
       <c r="W404" s="2"/>
       <c r="X404" s="2"/>
     </row>
-    <row r="405" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A405" s="24"/>
       <c r="B405" s="24"/>
       <c r="C405" s="24"/>
@@ -11963,7 +11990,7 @@
       <c r="W405" s="2"/>
       <c r="X405" s="2"/>
     </row>
-    <row r="406" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A406" s="24"/>
       <c r="B406" s="24"/>
       <c r="C406" s="24"/>
@@ -11989,7 +12016,7 @@
       <c r="W406" s="2"/>
       <c r="X406" s="2"/>
     </row>
-    <row r="407" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A407" s="24"/>
       <c r="B407" s="24"/>
       <c r="C407" s="24"/>
@@ -12015,7 +12042,7 @@
       <c r="W407" s="2"/>
       <c r="X407" s="2"/>
     </row>
-    <row r="408" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A408" s="24"/>
       <c r="B408" s="24"/>
       <c r="C408" s="24"/>
@@ -12041,7 +12068,7 @@
       <c r="W408" s="2"/>
       <c r="X408" s="2"/>
     </row>
-    <row r="409" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A409" s="24"/>
       <c r="B409" s="24"/>
       <c r="C409" s="24"/>
@@ -12067,7 +12094,7 @@
       <c r="W409" s="2"/>
       <c r="X409" s="2"/>
     </row>
-    <row r="410" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A410" s="24"/>
       <c r="B410" s="24"/>
       <c r="C410" s="24"/>
@@ -12093,7 +12120,7 @@
       <c r="W410" s="2"/>
       <c r="X410" s="2"/>
     </row>
-    <row r="411" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A411" s="24"/>
       <c r="B411" s="24"/>
       <c r="C411" s="24"/>
@@ -12119,7 +12146,7 @@
       <c r="W411" s="2"/>
       <c r="X411" s="2"/>
     </row>
-    <row r="412" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A412" s="24"/>
       <c r="B412" s="24"/>
       <c r="C412" s="24"/>
@@ -12145,7 +12172,7 @@
       <c r="W412" s="2"/>
       <c r="X412" s="2"/>
     </row>
-    <row r="413" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A413" s="24"/>
       <c r="B413" s="24"/>
       <c r="C413" s="24"/>
@@ -12171,7 +12198,7 @@
       <c r="W413" s="2"/>
       <c r="X413" s="2"/>
     </row>
-    <row r="414" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A414" s="24"/>
       <c r="B414" s="24"/>
       <c r="C414" s="24"/>
@@ -12197,7 +12224,7 @@
       <c r="W414" s="2"/>
       <c r="X414" s="2"/>
     </row>
-    <row r="415" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A415" s="24"/>
       <c r="B415" s="24"/>
       <c r="C415" s="24"/>
@@ -12223,7 +12250,7 @@
       <c r="W415" s="2"/>
       <c r="X415" s="2"/>
     </row>
-    <row r="416" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A416" s="24"/>
       <c r="B416" s="24"/>
       <c r="C416" s="24"/>
@@ -12249,7 +12276,7 @@
       <c r="W416" s="2"/>
       <c r="X416" s="2"/>
     </row>
-    <row r="417" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A417" s="24"/>
       <c r="B417" s="24"/>
       <c r="C417" s="24"/>
@@ -12275,7 +12302,7 @@
       <c r="W417" s="2"/>
       <c r="X417" s="2"/>
     </row>
-    <row r="418" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A418" s="24"/>
       <c r="B418" s="24"/>
       <c r="C418" s="24"/>
@@ -12301,7 +12328,7 @@
       <c r="W418" s="2"/>
       <c r="X418" s="2"/>
     </row>
-    <row r="419" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A419" s="24"/>
       <c r="B419" s="24"/>
       <c r="C419" s="24"/>
@@ -12327,7 +12354,7 @@
       <c r="W419" s="2"/>
       <c r="X419" s="2"/>
     </row>
-    <row r="420" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A420" s="24"/>
       <c r="B420" s="24"/>
       <c r="C420" s="24"/>
@@ -12353,7 +12380,7 @@
       <c r="W420" s="2"/>
       <c r="X420" s="2"/>
     </row>
-    <row r="421" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A421" s="24"/>
       <c r="B421" s="24"/>
       <c r="C421" s="24"/>
@@ -12379,7 +12406,7 @@
       <c r="W421" s="2"/>
       <c r="X421" s="2"/>
     </row>
-    <row r="422" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A422" s="24"/>
       <c r="B422" s="24"/>
       <c r="C422" s="24"/>
@@ -12405,7 +12432,7 @@
       <c r="W422" s="2"/>
       <c r="X422" s="2"/>
     </row>
-    <row r="423" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A423" s="24"/>
       <c r="B423" s="24"/>
       <c r="C423" s="24"/>
@@ -12431,7 +12458,7 @@
       <c r="W423" s="2"/>
       <c r="X423" s="2"/>
     </row>
-    <row r="424" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A424" s="24"/>
       <c r="B424" s="24"/>
       <c r="C424" s="24"/>
@@ -12457,7 +12484,7 @@
       <c r="W424" s="2"/>
       <c r="X424" s="2"/>
     </row>
-    <row r="425" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A425" s="24"/>
       <c r="B425" s="24"/>
       <c r="C425" s="24"/>
@@ -12483,7 +12510,7 @@
       <c r="W425" s="2"/>
       <c r="X425" s="2"/>
     </row>
-    <row r="426" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A426" s="24"/>
       <c r="B426" s="24"/>
       <c r="C426" s="24"/>
@@ -12509,7 +12536,7 @@
       <c r="W426" s="2"/>
       <c r="X426" s="2"/>
     </row>
-    <row r="427" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A427" s="24"/>
       <c r="B427" s="24"/>
       <c r="C427" s="24"/>
@@ -12535,7 +12562,7 @@
       <c r="W427" s="2"/>
       <c r="X427" s="2"/>
     </row>
-    <row r="428" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A428" s="24"/>
       <c r="B428" s="24"/>
       <c r="C428" s="24"/>
@@ -12561,7 +12588,7 @@
       <c r="W428" s="2"/>
       <c r="X428" s="2"/>
     </row>
-    <row r="429" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A429" s="24"/>
       <c r="B429" s="24"/>
       <c r="C429" s="24"/>
@@ -12587,7 +12614,7 @@
       <c r="W429" s="2"/>
       <c r="X429" s="2"/>
     </row>
-    <row r="430" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A430" s="24"/>
       <c r="B430" s="24"/>
       <c r="C430" s="24"/>
@@ -12613,7 +12640,7 @@
       <c r="W430" s="2"/>
       <c r="X430" s="2"/>
     </row>
-    <row r="431" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A431" s="24"/>
       <c r="B431" s="24"/>
       <c r="C431" s="24"/>
@@ -12639,7 +12666,7 @@
       <c r="W431" s="2"/>
       <c r="X431" s="2"/>
     </row>
-    <row r="432" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A432" s="24"/>
       <c r="B432" s="24"/>
       <c r="C432" s="24"/>
@@ -12665,7 +12692,7 @@
       <c r="W432" s="2"/>
       <c r="X432" s="2"/>
     </row>
-    <row r="433" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A433" s="24"/>
       <c r="B433" s="24"/>
       <c r="C433" s="24"/>
@@ -12691,7 +12718,7 @@
       <c r="W433" s="2"/>
       <c r="X433" s="2"/>
     </row>
-    <row r="434" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A434" s="24"/>
       <c r="B434" s="24"/>
       <c r="C434" s="24"/>
@@ -12717,7 +12744,7 @@
       <c r="W434" s="2"/>
       <c r="X434" s="2"/>
     </row>
-    <row r="435" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A435" s="24"/>
       <c r="B435" s="24"/>
       <c r="C435" s="24"/>
@@ -12743,7 +12770,7 @@
       <c r="W435" s="2"/>
       <c r="X435" s="2"/>
     </row>
-    <row r="436" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A436" s="24"/>
       <c r="B436" s="24"/>
       <c r="C436" s="24"/>
@@ -12769,7 +12796,7 @@
       <c r="W436" s="2"/>
       <c r="X436" s="2"/>
     </row>
-    <row r="437" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A437" s="24"/>
       <c r="B437" s="24"/>
       <c r="C437" s="24"/>
@@ -12795,7 +12822,7 @@
       <c r="W437" s="2"/>
       <c r="X437" s="2"/>
     </row>
-    <row r="438" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A438" s="24"/>
       <c r="B438" s="24"/>
       <c r="C438" s="24"/>
@@ -12821,7 +12848,7 @@
       <c r="W438" s="2"/>
       <c r="X438" s="2"/>
     </row>
-    <row r="439" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A439" s="24"/>
       <c r="B439" s="24"/>
       <c r="C439" s="24"/>
@@ -12847,7 +12874,7 @@
       <c r="W439" s="2"/>
       <c r="X439" s="2"/>
     </row>
-    <row r="440" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A440" s="24"/>
       <c r="B440" s="24"/>
       <c r="C440" s="24"/>
@@ -12873,7 +12900,7 @@
       <c r="W440" s="2"/>
       <c r="X440" s="2"/>
     </row>
-    <row r="441" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A441" s="24"/>
       <c r="B441" s="24"/>
       <c r="C441" s="24"/>
@@ -12899,7 +12926,7 @@
       <c r="W441" s="2"/>
       <c r="X441" s="2"/>
     </row>
-    <row r="442" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A442" s="24"/>
       <c r="B442" s="24"/>
       <c r="C442" s="24"/>
@@ -12925,7 +12952,7 @@
       <c r="W442" s="2"/>
       <c r="X442" s="2"/>
     </row>
-    <row r="443" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A443" s="24"/>
       <c r="B443" s="24"/>
       <c r="C443" s="24"/>
@@ -12951,7 +12978,7 @@
       <c r="W443" s="2"/>
       <c r="X443" s="2"/>
     </row>
-    <row r="444" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A444" s="24"/>
       <c r="B444" s="24"/>
       <c r="C444" s="24"/>
@@ -12977,7 +13004,7 @@
       <c r="W444" s="2"/>
       <c r="X444" s="2"/>
     </row>
-    <row r="445" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A445" s="24"/>
       <c r="B445" s="24"/>
       <c r="C445" s="24"/>
@@ -13003,7 +13030,7 @@
       <c r="W445" s="2"/>
       <c r="X445" s="2"/>
     </row>
-    <row r="446" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A446" s="24"/>
       <c r="B446" s="24"/>
       <c r="C446" s="24"/>
@@ -13029,7 +13056,7 @@
       <c r="W446" s="2"/>
       <c r="X446" s="2"/>
     </row>
-    <row r="447" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A447" s="24"/>
       <c r="B447" s="24"/>
       <c r="C447" s="24"/>
@@ -13055,7 +13082,7 @@
       <c r="W447" s="2"/>
       <c r="X447" s="2"/>
     </row>
-    <row r="448" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A448" s="24"/>
       <c r="B448" s="24"/>
       <c r="C448" s="24"/>
@@ -13081,7 +13108,7 @@
       <c r="W448" s="2"/>
       <c r="X448" s="2"/>
     </row>
-    <row r="449" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A449" s="24"/>
       <c r="B449" s="24"/>
       <c r="C449" s="24"/>
@@ -13107,7 +13134,7 @@
       <c r="W449" s="2"/>
       <c r="X449" s="2"/>
     </row>
-    <row r="450" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A450" s="24"/>
       <c r="B450" s="24"/>
       <c r="C450" s="24"/>
@@ -13133,7 +13160,7 @@
       <c r="W450" s="2"/>
       <c r="X450" s="2"/>
     </row>
-    <row r="451" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A451" s="24"/>
       <c r="B451" s="24"/>
       <c r="C451" s="24"/>
@@ -13159,7 +13186,7 @@
       <c r="W451" s="2"/>
       <c r="X451" s="2"/>
     </row>
-    <row r="452" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A452" s="24"/>
       <c r="B452" s="24"/>
       <c r="C452" s="24"/>
@@ -13185,7 +13212,7 @@
       <c r="W452" s="2"/>
       <c r="X452" s="2"/>
     </row>
-    <row r="453" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A453" s="24"/>
       <c r="B453" s="24"/>
       <c r="C453" s="24"/>
@@ -13211,7 +13238,7 @@
       <c r="W453" s="2"/>
       <c r="X453" s="2"/>
     </row>
-    <row r="454" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A454" s="24"/>
       <c r="B454" s="24"/>
       <c r="C454" s="24"/>
@@ -13237,7 +13264,7 @@
       <c r="W454" s="2"/>
       <c r="X454" s="2"/>
     </row>
-    <row r="455" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A455" s="24"/>
       <c r="B455" s="24"/>
       <c r="C455" s="24"/>
@@ -13263,7 +13290,7 @@
       <c r="W455" s="2"/>
       <c r="X455" s="2"/>
     </row>
-    <row r="456" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A456" s="24"/>
       <c r="B456" s="24"/>
       <c r="C456" s="24"/>
@@ -13289,7 +13316,7 @@
       <c r="W456" s="2"/>
       <c r="X456" s="2"/>
     </row>
-    <row r="457" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A457" s="24"/>
       <c r="B457" s="24"/>
       <c r="C457" s="24"/>
@@ -13315,7 +13342,7 @@
       <c r="W457" s="2"/>
       <c r="X457" s="2"/>
     </row>
-    <row r="458" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A458" s="24"/>
       <c r="B458" s="24"/>
       <c r="C458" s="24"/>
@@ -13341,7 +13368,7 @@
       <c r="W458" s="2"/>
       <c r="X458" s="2"/>
     </row>
-    <row r="459" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A459" s="24"/>
       <c r="B459" s="24"/>
       <c r="C459" s="24"/>
@@ -13367,7 +13394,7 @@
       <c r="W459" s="2"/>
       <c r="X459" s="2"/>
     </row>
-    <row r="460" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A460" s="24"/>
       <c r="B460" s="24"/>
       <c r="C460" s="24"/>
@@ -13393,7 +13420,7 @@
       <c r="W460" s="2"/>
       <c r="X460" s="2"/>
     </row>
-    <row r="461" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A461" s="24"/>
       <c r="B461" s="24"/>
       <c r="C461" s="24"/>
@@ -13419,7 +13446,7 @@
       <c r="W461" s="2"/>
       <c r="X461" s="2"/>
     </row>
-    <row r="462" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A462" s="24"/>
       <c r="B462" s="24"/>
       <c r="C462" s="24"/>
@@ -13445,7 +13472,7 @@
       <c r="W462" s="2"/>
       <c r="X462" s="2"/>
     </row>
-    <row r="463" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A463" s="24"/>
       <c r="B463" s="24"/>
       <c r="C463" s="24"/>
@@ -13471,7 +13498,7 @@
       <c r="W463" s="2"/>
       <c r="X463" s="2"/>
     </row>
-    <row r="464" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A464" s="24"/>
       <c r="B464" s="24"/>
       <c r="C464" s="24"/>
@@ -13497,7 +13524,7 @@
       <c r="W464" s="2"/>
       <c r="X464" s="2"/>
     </row>
-    <row r="465" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A465" s="24"/>
       <c r="B465" s="24"/>
       <c r="C465" s="24"/>
@@ -13523,7 +13550,7 @@
       <c r="W465" s="2"/>
       <c r="X465" s="2"/>
     </row>
-    <row r="466" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A466" s="24"/>
       <c r="B466" s="24"/>
       <c r="C466" s="24"/>
@@ -13549,7 +13576,7 @@
       <c r="W466" s="2"/>
       <c r="X466" s="2"/>
     </row>
-    <row r="467" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A467" s="24"/>
       <c r="B467" s="24"/>
       <c r="C467" s="24"/>
@@ -13575,7 +13602,7 @@
       <c r="W467" s="2"/>
       <c r="X467" s="2"/>
     </row>
-    <row r="468" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A468" s="24"/>
       <c r="B468" s="24"/>
       <c r="C468" s="24"/>
@@ -13601,7 +13628,7 @@
       <c r="W468" s="2"/>
       <c r="X468" s="2"/>
     </row>
-    <row r="469" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A469" s="24"/>
       <c r="B469" s="24"/>
       <c r="C469" s="24"/>
@@ -13627,7 +13654,7 @@
       <c r="W469" s="2"/>
       <c r="X469" s="2"/>
     </row>
-    <row r="470" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A470" s="24"/>
       <c r="B470" s="24"/>
       <c r="C470" s="24"/>
@@ -13653,7 +13680,7 @@
       <c r="W470" s="2"/>
       <c r="X470" s="2"/>
     </row>
-    <row r="471" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A471" s="24"/>
       <c r="B471" s="24"/>
       <c r="C471" s="24"/>
@@ -13679,7 +13706,7 @@
       <c r="W471" s="2"/>
       <c r="X471" s="2"/>
     </row>
-    <row r="472" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A472" s="24"/>
       <c r="B472" s="24"/>
       <c r="C472" s="24"/>
@@ -13705,7 +13732,7 @@
       <c r="W472" s="2"/>
       <c r="X472" s="2"/>
     </row>
-    <row r="473" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A473" s="24"/>
       <c r="B473" s="24"/>
       <c r="C473" s="24"/>
@@ -13731,7 +13758,7 @@
       <c r="W473" s="2"/>
       <c r="X473" s="2"/>
     </row>
-    <row r="474" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A474" s="24"/>
       <c r="B474" s="24"/>
       <c r="C474" s="24"/>
@@ -13757,7 +13784,7 @@
       <c r="W474" s="2"/>
       <c r="X474" s="2"/>
     </row>
-    <row r="475" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A475" s="24"/>
       <c r="B475" s="24"/>
       <c r="C475" s="24"/>
@@ -13783,7 +13810,7 @@
       <c r="W475" s="2"/>
       <c r="X475" s="2"/>
     </row>
-    <row r="476" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A476" s="24"/>
       <c r="B476" s="24"/>
       <c r="C476" s="24"/>
@@ -13809,7 +13836,7 @@
       <c r="W476" s="2"/>
       <c r="X476" s="2"/>
     </row>
-    <row r="477" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A477" s="24"/>
       <c r="B477" s="24"/>
       <c r="C477" s="24"/>
@@ -13835,7 +13862,7 @@
       <c r="W477" s="2"/>
       <c r="X477" s="2"/>
     </row>
-    <row r="478" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A478" s="24"/>
       <c r="B478" s="24"/>
       <c r="C478" s="24"/>
@@ -13861,7 +13888,7 @@
       <c r="W478" s="2"/>
       <c r="X478" s="2"/>
     </row>
-    <row r="479" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A479" s="24"/>
       <c r="B479" s="24"/>
       <c r="C479" s="24"/>
@@ -13887,7 +13914,7 @@
       <c r="W479" s="2"/>
       <c r="X479" s="2"/>
     </row>
-    <row r="480" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A480" s="24"/>
       <c r="B480" s="24"/>
       <c r="C480" s="24"/>
@@ -13913,7 +13940,7 @@
       <c r="W480" s="2"/>
       <c r="X480" s="2"/>
     </row>
-    <row r="481" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A481" s="24"/>
       <c r="B481" s="24"/>
       <c r="C481" s="24"/>
@@ -13939,7 +13966,7 @@
       <c r="W481" s="2"/>
       <c r="X481" s="2"/>
     </row>
-    <row r="482" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A482" s="24"/>
       <c r="B482" s="24"/>
       <c r="C482" s="24"/>
@@ -13965,7 +13992,7 @@
       <c r="W482" s="2"/>
       <c r="X482" s="2"/>
     </row>
-    <row r="483" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A483" s="24"/>
       <c r="B483" s="24"/>
       <c r="C483" s="24"/>
@@ -13991,7 +14018,7 @@
       <c r="W483" s="2"/>
       <c r="X483" s="2"/>
     </row>
-    <row r="484" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A484" s="24"/>
       <c r="B484" s="24"/>
       <c r="C484" s="24"/>
@@ -14017,7 +14044,7 @@
       <c r="W484" s="2"/>
       <c r="X484" s="2"/>
     </row>
-    <row r="485" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A485" s="24"/>
       <c r="B485" s="24"/>
       <c r="C485" s="24"/>
@@ -14043,7 +14070,7 @@
       <c r="W485" s="2"/>
       <c r="X485" s="2"/>
     </row>
-    <row r="486" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A486" s="24"/>
       <c r="B486" s="24"/>
       <c r="C486" s="24"/>
@@ -14069,7 +14096,7 @@
       <c r="W486" s="2"/>
       <c r="X486" s="2"/>
     </row>
-    <row r="487" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A487" s="24"/>
       <c r="B487" s="24"/>
       <c r="C487" s="24"/>
@@ -14095,7 +14122,7 @@
       <c r="W487" s="2"/>
       <c r="X487" s="2"/>
     </row>
-    <row r="488" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A488" s="24"/>
       <c r="B488" s="24"/>
       <c r="C488" s="24"/>
@@ -14121,7 +14148,7 @@
       <c r="W488" s="2"/>
       <c r="X488" s="2"/>
     </row>
-    <row r="489" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A489" s="24"/>
       <c r="B489" s="24"/>
       <c r="C489" s="24"/>
@@ -14147,7 +14174,7 @@
       <c r="W489" s="2"/>
       <c r="X489" s="2"/>
     </row>
-    <row r="490" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A490" s="24"/>
       <c r="B490" s="24"/>
       <c r="C490" s="24"/>
@@ -14173,7 +14200,7 @@
       <c r="W490" s="2"/>
       <c r="X490" s="2"/>
     </row>
-    <row r="491" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A491" s="24"/>
       <c r="B491" s="24"/>
       <c r="C491" s="24"/>
@@ -14199,7 +14226,7 @@
       <c r="W491" s="2"/>
       <c r="X491" s="2"/>
     </row>
-    <row r="492" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A492" s="24"/>
       <c r="B492" s="24"/>
       <c r="C492" s="24"/>
@@ -14225,7 +14252,7 @@
       <c r="W492" s="2"/>
       <c r="X492" s="2"/>
     </row>
-    <row r="493" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A493" s="24"/>
       <c r="B493" s="24"/>
       <c r="C493" s="24"/>
@@ -14251,7 +14278,7 @@
       <c r="W493" s="2"/>
       <c r="X493" s="2"/>
     </row>
-    <row r="494" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A494" s="24"/>
       <c r="B494" s="24"/>
       <c r="C494" s="24"/>
@@ -14277,7 +14304,7 @@
       <c r="W494" s="2"/>
       <c r="X494" s="2"/>
     </row>
-    <row r="495" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A495" s="24"/>
       <c r="B495" s="24"/>
       <c r="C495" s="24"/>
@@ -14303,7 +14330,7 @@
       <c r="W495" s="2"/>
       <c r="X495" s="2"/>
     </row>
-    <row r="496" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A496" s="24"/>
       <c r="B496" s="24"/>
       <c r="C496" s="24"/>
@@ -14329,7 +14356,7 @@
       <c r="W496" s="2"/>
       <c r="X496" s="2"/>
     </row>
-    <row r="497" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A497" s="24"/>
       <c r="B497" s="24"/>
       <c r="C497" s="24"/>
@@ -14355,7 +14382,7 @@
       <c r="W497" s="2"/>
       <c r="X497" s="2"/>
     </row>
-    <row r="498" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A498" s="24"/>
       <c r="B498" s="24"/>
       <c r="C498" s="24"/>
@@ -14381,7 +14408,7 @@
       <c r="W498" s="2"/>
       <c r="X498" s="2"/>
     </row>
-    <row r="499" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A499" s="24"/>
       <c r="B499" s="24"/>
       <c r="C499" s="24"/>
@@ -14407,7 +14434,7 @@
       <c r="W499" s="2"/>
       <c r="X499" s="2"/>
     </row>
-    <row r="500" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A500" s="24"/>
       <c r="B500" s="24"/>
       <c r="C500" s="24"/>
@@ -14433,7 +14460,7 @@
       <c r="W500" s="2"/>
       <c r="X500" s="2"/>
     </row>
-    <row r="501" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A501" s="24"/>
       <c r="B501" s="24"/>
       <c r="C501" s="24"/>
@@ -14459,7 +14486,7 @@
       <c r="W501" s="2"/>
       <c r="X501" s="2"/>
     </row>
-    <row r="502" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A502" s="24"/>
       <c r="B502" s="24"/>
       <c r="C502" s="24"/>
@@ -14485,7 +14512,7 @@
       <c r="W502" s="2"/>
       <c r="X502" s="2"/>
     </row>
-    <row r="503" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A503" s="24"/>
       <c r="B503" s="24"/>
       <c r="C503" s="24"/>
@@ -14511,7 +14538,7 @@
       <c r="W503" s="2"/>
       <c r="X503" s="2"/>
     </row>
-    <row r="504" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A504" s="24"/>
       <c r="B504" s="24"/>
       <c r="C504" s="24"/>
@@ -14537,7 +14564,7 @@
       <c r="W504" s="2"/>
       <c r="X504" s="2"/>
     </row>
-    <row r="505" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A505" s="24"/>
       <c r="B505" s="24"/>
       <c r="C505" s="24"/>
@@ -14563,7 +14590,7 @@
       <c r="W505" s="2"/>
       <c r="X505" s="2"/>
     </row>
-    <row r="506" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A506" s="24"/>
       <c r="B506" s="24"/>
       <c r="C506" s="24"/>
@@ -14589,7 +14616,7 @@
       <c r="W506" s="2"/>
       <c r="X506" s="2"/>
     </row>
-    <row r="507" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A507" s="24"/>
       <c r="B507" s="24"/>
       <c r="C507" s="24"/>
@@ -14615,7 +14642,7 @@
       <c r="W507" s="2"/>
       <c r="X507" s="2"/>
     </row>
-    <row r="508" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A508" s="24"/>
       <c r="B508" s="24"/>
       <c r="C508" s="24"/>
@@ -14641,7 +14668,7 @@
       <c r="W508" s="2"/>
       <c r="X508" s="2"/>
     </row>
-    <row r="509" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A509" s="24"/>
       <c r="B509" s="24"/>
       <c r="C509" s="24"/>
@@ -14667,7 +14694,7 @@
       <c r="W509" s="2"/>
       <c r="X509" s="2"/>
     </row>
-    <row r="510" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A510" s="24"/>
       <c r="B510" s="24"/>
       <c r="C510" s="24"/>
@@ -14693,7 +14720,7 @@
       <c r="W510" s="2"/>
       <c r="X510" s="2"/>
     </row>
-    <row r="511" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A511" s="24"/>
       <c r="B511" s="24"/>
       <c r="C511" s="24"/>
@@ -14719,7 +14746,7 @@
       <c r="W511" s="2"/>
       <c r="X511" s="2"/>
     </row>
-    <row r="512" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A512" s="24"/>
       <c r="B512" s="24"/>
       <c r="C512" s="24"/>
@@ -14745,7 +14772,7 @@
       <c r="W512" s="2"/>
       <c r="X512" s="2"/>
     </row>
-    <row r="513" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A513" s="24"/>
       <c r="B513" s="24"/>
       <c r="C513" s="24"/>
@@ -14771,7 +14798,7 @@
       <c r="W513" s="2"/>
       <c r="X513" s="2"/>
     </row>
-    <row r="514" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A514" s="24"/>
       <c r="B514" s="24"/>
       <c r="C514" s="24"/>
@@ -14797,7 +14824,7 @@
       <c r="W514" s="2"/>
       <c r="X514" s="2"/>
     </row>
-    <row r="515" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A515" s="24"/>
       <c r="B515" s="24"/>
       <c r="C515" s="24"/>
@@ -14823,7 +14850,7 @@
       <c r="W515" s="2"/>
       <c r="X515" s="2"/>
     </row>
-    <row r="516" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A516" s="24"/>
       <c r="B516" s="24"/>
       <c r="C516" s="24"/>
@@ -14849,7 +14876,7 @@
       <c r="W516" s="2"/>
       <c r="X516" s="2"/>
     </row>
-    <row r="517" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A517" s="24"/>
       <c r="B517" s="24"/>
       <c r="C517" s="24"/>
@@ -14875,7 +14902,7 @@
       <c r="W517" s="2"/>
       <c r="X517" s="2"/>
     </row>
-    <row r="518" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A518" s="24"/>
       <c r="B518" s="24"/>
       <c r="C518" s="24"/>
@@ -14901,7 +14928,7 @@
       <c r="W518" s="2"/>
       <c r="X518" s="2"/>
     </row>
-    <row r="519" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A519" s="24"/>
       <c r="B519" s="24"/>
       <c r="C519" s="24"/>
@@ -14927,7 +14954,7 @@
       <c r="W519" s="2"/>
       <c r="X519" s="2"/>
     </row>
-    <row r="520" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A520" s="24"/>
       <c r="B520" s="24"/>
       <c r="C520" s="24"/>
@@ -14953,7 +14980,7 @@
       <c r="W520" s="2"/>
       <c r="X520" s="2"/>
     </row>
-    <row r="521" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A521" s="24"/>
       <c r="B521" s="24"/>
       <c r="C521" s="24"/>
@@ -14979,7 +15006,7 @@
       <c r="W521" s="2"/>
       <c r="X521" s="2"/>
     </row>
-    <row r="522" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A522" s="24"/>
       <c r="B522" s="24"/>
       <c r="C522" s="24"/>
@@ -15005,7 +15032,7 @@
       <c r="W522" s="2"/>
       <c r="X522" s="2"/>
     </row>
-    <row r="523" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A523" s="24"/>
       <c r="B523" s="24"/>
       <c r="C523" s="24"/>
@@ -15031,7 +15058,7 @@
       <c r="W523" s="2"/>
       <c r="X523" s="2"/>
     </row>
-    <row r="524" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A524" s="24"/>
       <c r="B524" s="24"/>
       <c r="C524" s="24"/>
@@ -15057,7 +15084,7 @@
       <c r="W524" s="2"/>
       <c r="X524" s="2"/>
     </row>
-    <row r="525" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A525" s="24"/>
       <c r="B525" s="24"/>
       <c r="C525" s="24"/>
@@ -15083,7 +15110,7 @@
       <c r="W525" s="2"/>
       <c r="X525" s="2"/>
     </row>
-    <row r="526" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A526" s="24"/>
       <c r="B526" s="24"/>
       <c r="C526" s="24"/>
@@ -15109,7 +15136,7 @@
       <c r="W526" s="2"/>
       <c r="X526" s="2"/>
     </row>
-    <row r="527" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A527" s="24"/>
       <c r="B527" s="24"/>
       <c r="C527" s="24"/>
@@ -15135,7 +15162,7 @@
       <c r="W527" s="2"/>
       <c r="X527" s="2"/>
     </row>
-    <row r="528" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A528" s="24"/>
       <c r="B528" s="24"/>
       <c r="C528" s="24"/>
@@ -15161,7 +15188,7 @@
       <c r="W528" s="2"/>
       <c r="X528" s="2"/>
     </row>
-    <row r="529" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A529" s="24"/>
       <c r="B529" s="24"/>
       <c r="C529" s="24"/>
@@ -15187,7 +15214,7 @@
       <c r="W529" s="2"/>
       <c r="X529" s="2"/>
     </row>
-    <row r="530" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A530" s="24"/>
       <c r="B530" s="24"/>
       <c r="C530" s="24"/>
@@ -15213,7 +15240,7 @@
       <c r="W530" s="2"/>
       <c r="X530" s="2"/>
     </row>
-    <row r="531" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A531" s="24"/>
       <c r="B531" s="24"/>
       <c r="C531" s="24"/>
@@ -15239,7 +15266,7 @@
       <c r="W531" s="2"/>
       <c r="X531" s="2"/>
     </row>
-    <row r="532" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A532" s="24"/>
       <c r="B532" s="24"/>
       <c r="C532" s="24"/>
@@ -15265,7 +15292,7 @@
       <c r="W532" s="2"/>
       <c r="X532" s="2"/>
     </row>
-    <row r="533" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A533" s="24"/>
       <c r="B533" s="24"/>
       <c r="C533" s="24"/>
@@ -15291,7 +15318,7 @@
       <c r="W533" s="2"/>
       <c r="X533" s="2"/>
     </row>
-    <row r="534" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A534" s="24"/>
       <c r="B534" s="24"/>
       <c r="C534" s="24"/>
@@ -15317,7 +15344,7 @@
       <c r="W534" s="2"/>
       <c r="X534" s="2"/>
     </row>
-    <row r="535" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A535" s="24"/>
       <c r="B535" s="24"/>
       <c r="C535" s="24"/>
@@ -15343,7 +15370,7 @@
       <c r="W535" s="2"/>
       <c r="X535" s="2"/>
     </row>
-    <row r="536" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A536" s="24"/>
       <c r="B536" s="24"/>
       <c r="C536" s="24"/>
@@ -15369,7 +15396,7 @@
       <c r="W536" s="2"/>
       <c r="X536" s="2"/>
     </row>
-    <row r="537" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A537" s="24"/>
       <c r="B537" s="24"/>
       <c r="C537" s="24"/>
@@ -15395,7 +15422,7 @@
       <c r="W537" s="2"/>
       <c r="X537" s="2"/>
     </row>
-    <row r="538" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A538" s="24"/>
       <c r="B538" s="24"/>
       <c r="C538" s="24"/>
@@ -15421,7 +15448,7 @@
       <c r="W538" s="2"/>
       <c r="X538" s="2"/>
     </row>
-    <row r="539" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A539" s="24"/>
       <c r="B539" s="24"/>
       <c r="C539" s="24"/>
@@ -15447,7 +15474,7 @@
       <c r="W539" s="2"/>
       <c r="X539" s="2"/>
     </row>
-    <row r="540" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A540" s="24"/>
       <c r="B540" s="24"/>
       <c r="C540" s="24"/>
@@ -15473,7 +15500,7 @@
       <c r="W540" s="2"/>
       <c r="X540" s="2"/>
     </row>
-    <row r="541" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A541" s="24"/>
       <c r="B541" s="24"/>
       <c r="C541" s="24"/>
@@ -15499,7 +15526,7 @@
       <c r="W541" s="2"/>
       <c r="X541" s="2"/>
     </row>
-    <row r="542" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A542" s="24"/>
       <c r="B542" s="24"/>
       <c r="C542" s="24"/>
@@ -15525,7 +15552,7 @@
       <c r="W542" s="2"/>
       <c r="X542" s="2"/>
     </row>
-    <row r="543" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A543" s="24"/>
       <c r="B543" s="24"/>
       <c r="C543" s="24"/>
@@ -15551,7 +15578,7 @@
       <c r="W543" s="2"/>
       <c r="X543" s="2"/>
     </row>
-    <row r="544" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A544" s="24"/>
       <c r="B544" s="24"/>
       <c r="C544" s="24"/>
@@ -15577,7 +15604,7 @@
       <c r="W544" s="2"/>
       <c r="X544" s="2"/>
     </row>
-    <row r="545" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A545" s="24"/>
       <c r="B545" s="24"/>
       <c r="C545" s="24"/>
@@ -15603,7 +15630,7 @@
       <c r="W545" s="2"/>
       <c r="X545" s="2"/>
     </row>
-    <row r="546" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A546" s="24"/>
       <c r="B546" s="24"/>
       <c r="C546" s="24"/>
@@ -15629,7 +15656,7 @@
       <c r="W546" s="2"/>
       <c r="X546" s="2"/>
     </row>
-    <row r="547" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A547" s="24"/>
       <c r="B547" s="24"/>
       <c r="C547" s="24"/>
@@ -15655,7 +15682,7 @@
       <c r="W547" s="2"/>
       <c r="X547" s="2"/>
     </row>
-    <row r="548" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A548" s="24"/>
       <c r="B548" s="24"/>
       <c r="C548" s="24"/>
@@ -15681,7 +15708,7 @@
       <c r="W548" s="2"/>
       <c r="X548" s="2"/>
     </row>
-    <row r="549" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A549" s="24"/>
       <c r="B549" s="24"/>
       <c r="C549" s="24"/>
@@ -15707,7 +15734,7 @@
       <c r="W549" s="2"/>
       <c r="X549" s="2"/>
     </row>
-    <row r="550" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A550" s="24"/>
       <c r="B550" s="24"/>
       <c r="C550" s="24"/>
@@ -15733,7 +15760,7 @@
       <c r="W550" s="2"/>
       <c r="X550" s="2"/>
     </row>
-    <row r="551" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A551" s="24"/>
       <c r="B551" s="24"/>
       <c r="C551" s="24"/>
@@ -15759,7 +15786,7 @@
       <c r="W551" s="2"/>
       <c r="X551" s="2"/>
     </row>
-    <row r="552" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A552" s="24"/>
       <c r="B552" s="24"/>
       <c r="C552" s="24"/>
@@ -15785,7 +15812,7 @@
       <c r="W552" s="2"/>
       <c r="X552" s="2"/>
     </row>
-    <row r="553" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A553" s="24"/>
       <c r="B553" s="24"/>
       <c r="C553" s="24"/>
@@ -15811,7 +15838,7 @@
       <c r="W553" s="2"/>
       <c r="X553" s="2"/>
     </row>
-    <row r="554" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A554" s="24"/>
       <c r="B554" s="24"/>
       <c r="C554" s="24"/>
@@ -15837,7 +15864,7 @@
       <c r="W554" s="2"/>
       <c r="X554" s="2"/>
     </row>
-    <row r="555" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A555" s="24"/>
       <c r="B555" s="24"/>
       <c r="C555" s="24"/>
@@ -15863,7 +15890,7 @@
       <c r="W555" s="2"/>
       <c r="X555" s="2"/>
     </row>
-    <row r="556" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A556" s="24"/>
       <c r="B556" s="24"/>
       <c r="C556" s="24"/>
@@ -15889,7 +15916,7 @@
       <c r="W556" s="2"/>
       <c r="X556" s="2"/>
     </row>
-    <row r="557" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A557" s="24"/>
       <c r="B557" s="24"/>
       <c r="C557" s="24"/>
@@ -15915,7 +15942,7 @@
       <c r="W557" s="2"/>
       <c r="X557" s="2"/>
     </row>
-    <row r="558" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A558" s="24"/>
       <c r="B558" s="24"/>
       <c r="C558" s="24"/>
@@ -15941,7 +15968,7 @@
       <c r="W558" s="2"/>
       <c r="X558" s="2"/>
     </row>
-    <row r="559" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A559" s="24"/>
       <c r="B559" s="24"/>
       <c r="C559" s="24"/>
@@ -15967,7 +15994,7 @@
       <c r="W559" s="2"/>
       <c r="X559" s="2"/>
     </row>
-    <row r="560" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A560" s="24"/>
       <c r="B560" s="24"/>
       <c r="C560" s="24"/>
@@ -15993,7 +16020,7 @@
       <c r="W560" s="2"/>
       <c r="X560" s="2"/>
     </row>
-    <row r="561" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A561" s="24"/>
       <c r="B561" s="24"/>
       <c r="C561" s="24"/>
@@ -16019,7 +16046,7 @@
       <c r="W561" s="2"/>
       <c r="X561" s="2"/>
     </row>
-    <row r="562" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A562" s="24"/>
       <c r="B562" s="24"/>
       <c r="C562" s="24"/>
@@ -16045,7 +16072,7 @@
       <c r="W562" s="2"/>
       <c r="X562" s="2"/>
     </row>
-    <row r="563" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A563" s="24"/>
       <c r="B563" s="24"/>
       <c r="C563" s="24"/>
@@ -16071,7 +16098,7 @@
       <c r="W563" s="2"/>
       <c r="X563" s="2"/>
     </row>
-    <row r="564" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A564" s="24"/>
       <c r="B564" s="24"/>
       <c r="C564" s="24"/>
@@ -16097,7 +16124,7 @@
       <c r="W564" s="2"/>
       <c r="X564" s="2"/>
     </row>
-    <row r="565" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A565" s="24"/>
       <c r="B565" s="24"/>
       <c r="C565" s="24"/>
@@ -16123,7 +16150,7 @@
       <c r="W565" s="2"/>
       <c r="X565" s="2"/>
     </row>
-    <row r="566" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A566" s="24"/>
       <c r="B566" s="24"/>
       <c r="C566" s="24"/>
@@ -16149,7 +16176,7 @@
       <c r="W566" s="2"/>
       <c r="X566" s="2"/>
     </row>
-    <row r="567" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A567" s="24"/>
       <c r="B567" s="24"/>
       <c r="C567" s="24"/>
@@ -16175,7 +16202,7 @@
       <c r="W567" s="2"/>
       <c r="X567" s="2"/>
     </row>
-    <row r="568" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A568" s="24"/>
       <c r="B568" s="24"/>
       <c r="C568" s="24"/>
@@ -16201,7 +16228,7 @@
       <c r="W568" s="2"/>
       <c r="X568" s="2"/>
     </row>
-    <row r="569" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A569" s="24"/>
       <c r="B569" s="24"/>
       <c r="C569" s="24"/>
@@ -16227,7 +16254,7 @@
       <c r="W569" s="2"/>
       <c r="X569" s="2"/>
     </row>
-    <row r="570" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A570" s="24"/>
       <c r="B570" s="24"/>
       <c r="C570" s="24"/>
@@ -16253,7 +16280,7 @@
       <c r="W570" s="2"/>
       <c r="X570" s="2"/>
     </row>
-    <row r="571" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A571" s="24"/>
       <c r="B571" s="24"/>
       <c r="C571" s="24"/>
@@ -16279,7 +16306,7 @@
       <c r="W571" s="2"/>
       <c r="X571" s="2"/>
     </row>
-    <row r="572" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A572" s="24"/>
       <c r="B572" s="24"/>
       <c r="C572" s="24"/>
@@ -16305,7 +16332,7 @@
       <c r="W572" s="2"/>
       <c r="X572" s="2"/>
     </row>
-    <row r="573" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A573" s="24"/>
       <c r="B573" s="24"/>
       <c r="C573" s="24"/>
@@ -16331,7 +16358,7 @@
       <c r="W573" s="2"/>
       <c r="X573" s="2"/>
     </row>
-    <row r="574" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A574" s="24"/>
       <c r="B574" s="24"/>
       <c r="C574" s="24"/>
@@ -16357,7 +16384,7 @@
       <c r="W574" s="2"/>
       <c r="X574" s="2"/>
     </row>
-    <row r="575" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A575" s="24"/>
       <c r="B575" s="24"/>
       <c r="C575" s="24"/>
@@ -16383,7 +16410,7 @@
       <c r="W575" s="2"/>
       <c r="X575" s="2"/>
     </row>
-    <row r="576" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A576" s="24"/>
       <c r="B576" s="24"/>
       <c r="C576" s="24"/>
@@ -16409,7 +16436,7 @@
       <c r="W576" s="2"/>
       <c r="X576" s="2"/>
     </row>
-    <row r="577" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A577" s="24"/>
       <c r="B577" s="24"/>
       <c r="C577" s="24"/>
@@ -16435,7 +16462,7 @@
       <c r="W577" s="2"/>
       <c r="X577" s="2"/>
     </row>
-    <row r="578" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A578" s="24"/>
       <c r="B578" s="24"/>
       <c r="C578" s="24"/>
@@ -16461,7 +16488,7 @@
       <c r="W578" s="2"/>
       <c r="X578" s="2"/>
     </row>
-    <row r="579" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A579" s="24"/>
       <c r="B579" s="24"/>
       <c r="C579" s="24"/>
@@ -16487,7 +16514,7 @@
       <c r="W579" s="2"/>
       <c r="X579" s="2"/>
     </row>
-    <row r="580" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A580" s="24"/>
       <c r="B580" s="24"/>
       <c r="C580" s="24"/>
@@ -16513,7 +16540,7 @@
       <c r="W580" s="2"/>
       <c r="X580" s="2"/>
     </row>
-    <row r="581" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A581" s="24"/>
       <c r="B581" s="24"/>
       <c r="C581" s="24"/>
@@ -16539,7 +16566,7 @@
       <c r="W581" s="2"/>
       <c r="X581" s="2"/>
     </row>
-    <row r="582" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A582" s="24"/>
       <c r="B582" s="24"/>
       <c r="C582" s="24"/>
@@ -16565,7 +16592,7 @@
       <c r="W582" s="2"/>
       <c r="X582" s="2"/>
     </row>
-    <row r="583" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A583" s="24"/>
       <c r="B583" s="24"/>
       <c r="C583" s="24"/>
@@ -16591,7 +16618,7 @@
       <c r="W583" s="2"/>
       <c r="X583" s="2"/>
     </row>
-    <row r="584" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A584" s="24"/>
       <c r="B584" s="24"/>
       <c r="C584" s="24"/>
@@ -16617,7 +16644,7 @@
       <c r="W584" s="2"/>
       <c r="X584" s="2"/>
     </row>
-    <row r="585" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A585" s="24"/>
       <c r="B585" s="24"/>
       <c r="C585" s="24"/>
@@ -16643,7 +16670,7 @@
       <c r="W585" s="2"/>
       <c r="X585" s="2"/>
     </row>
-    <row r="586" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A586" s="24"/>
       <c r="B586" s="24"/>
       <c r="C586" s="24"/>
@@ -16669,7 +16696,7 @@
       <c r="W586" s="2"/>
       <c r="X586" s="2"/>
     </row>
-    <row r="587" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A587" s="24"/>
       <c r="B587" s="24"/>
       <c r="C587" s="24"/>
@@ -16695,7 +16722,7 @@
       <c r="W587" s="2"/>
       <c r="X587" s="2"/>
     </row>
-    <row r="588" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A588" s="24"/>
       <c r="B588" s="24"/>
       <c r="C588" s="24"/>
@@ -16721,7 +16748,7 @@
       <c r="W588" s="2"/>
       <c r="X588" s="2"/>
     </row>
-    <row r="589" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A589" s="24"/>
       <c r="B589" s="24"/>
       <c r="C589" s="24"/>
@@ -16747,7 +16774,7 @@
       <c r="W589" s="2"/>
       <c r="X589" s="2"/>
     </row>
-    <row r="590" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A590" s="24"/>
       <c r="B590" s="24"/>
       <c r="C590" s="24"/>
@@ -16773,7 +16800,7 @@
       <c r="W590" s="2"/>
       <c r="X590" s="2"/>
     </row>
-    <row r="591" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A591" s="24"/>
       <c r="B591" s="24"/>
       <c r="C591" s="24"/>
@@ -16799,7 +16826,7 @@
       <c r="W591" s="2"/>
       <c r="X591" s="2"/>
     </row>
-    <row r="592" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A592" s="24"/>
       <c r="B592" s="24"/>
       <c r="C592" s="24"/>
@@ -16825,7 +16852,7 @@
       <c r="W592" s="2"/>
       <c r="X592" s="2"/>
     </row>
-    <row r="593" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A593" s="24"/>
       <c r="B593" s="24"/>
       <c r="C593" s="24"/>
@@ -16851,7 +16878,7 @@
       <c r="W593" s="2"/>
       <c r="X593" s="2"/>
     </row>
-    <row r="594" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A594" s="24"/>
       <c r="B594" s="24"/>
       <c r="C594" s="24"/>
@@ -16877,7 +16904,7 @@
       <c r="W594" s="2"/>
       <c r="X594" s="2"/>
     </row>
-    <row r="595" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A595" s="24"/>
       <c r="B595" s="24"/>
       <c r="C595" s="24"/>
@@ -16903,7 +16930,7 @@
       <c r="W595" s="2"/>
       <c r="X595" s="2"/>
     </row>
-    <row r="596" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A596" s="24"/>
       <c r="B596" s="24"/>
       <c r="C596" s="24"/>
@@ -16929,7 +16956,7 @@
       <c r="W596" s="2"/>
       <c r="X596" s="2"/>
     </row>
-    <row r="597" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A597" s="24"/>
       <c r="B597" s="24"/>
       <c r="C597" s="24"/>
@@ -16955,7 +16982,7 @@
       <c r="W597" s="2"/>
       <c r="X597" s="2"/>
     </row>
-    <row r="598" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A598" s="24"/>
       <c r="B598" s="24"/>
       <c r="C598" s="24"/>
@@ -16981,7 +17008,7 @@
       <c r="W598" s="2"/>
       <c r="X598" s="2"/>
     </row>
-    <row r="599" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A599" s="24"/>
       <c r="B599" s="24"/>
       <c r="C599" s="24"/>
@@ -17007,7 +17034,7 @@
       <c r="W599" s="2"/>
       <c r="X599" s="2"/>
     </row>
-    <row r="600" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A600" s="24"/>
       <c r="B600" s="24"/>
       <c r="C600" s="24"/>
@@ -17033,7 +17060,7 @@
       <c r="W600" s="2"/>
       <c r="X600" s="2"/>
     </row>
-    <row r="601" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A601" s="24"/>
       <c r="B601" s="24"/>
       <c r="C601" s="24"/>
@@ -17059,7 +17086,7 @@
       <c r="W601" s="2"/>
       <c r="X601" s="2"/>
     </row>
-    <row r="602" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A602" s="24"/>
       <c r="B602" s="24"/>
       <c r="C602" s="24"/>
@@ -17085,7 +17112,7 @@
       <c r="W602" s="2"/>
       <c r="X602" s="2"/>
     </row>
-    <row r="603" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A603" s="24"/>
       <c r="B603" s="24"/>
       <c r="C603" s="24"/>
@@ -17111,7 +17138,7 @@
       <c r="W603" s="2"/>
       <c r="X603" s="2"/>
     </row>
-    <row r="604" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A604" s="24"/>
       <c r="B604" s="24"/>
       <c r="C604" s="24"/>
@@ -17137,7 +17164,7 @@
       <c r="W604" s="2"/>
       <c r="X604" s="2"/>
     </row>
-    <row r="605" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A605" s="24"/>
       <c r="B605" s="24"/>
       <c r="C605" s="24"/>
@@ -17163,7 +17190,7 @@
       <c r="W605" s="2"/>
       <c r="X605" s="2"/>
     </row>
-    <row r="606" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A606" s="24"/>
       <c r="B606" s="24"/>
       <c r="C606" s="24"/>
@@ -17189,7 +17216,7 @@
       <c r="W606" s="2"/>
       <c r="X606" s="2"/>
     </row>
-    <row r="607" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A607" s="24"/>
       <c r="B607" s="24"/>
       <c r="C607" s="24"/>
@@ -17215,7 +17242,7 @@
       <c r="W607" s="2"/>
       <c r="X607" s="2"/>
     </row>
-    <row r="608" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A608" s="24"/>
       <c r="B608" s="24"/>
       <c r="C608" s="24"/>
@@ -17241,7 +17268,7 @@
       <c r="W608" s="2"/>
       <c r="X608" s="2"/>
     </row>
-    <row r="609" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A609" s="24"/>
       <c r="B609" s="24"/>
       <c r="C609" s="24"/>
@@ -17267,7 +17294,7 @@
       <c r="W609" s="2"/>
       <c r="X609" s="2"/>
     </row>
-    <row r="610" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A610" s="24"/>
       <c r="B610" s="24"/>
       <c r="C610" s="24"/>
@@ -17293,7 +17320,7 @@
       <c r="W610" s="2"/>
       <c r="X610" s="2"/>
     </row>
-    <row r="611" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A611" s="24"/>
       <c r="B611" s="24"/>
       <c r="C611" s="24"/>
@@ -17319,7 +17346,7 @@
       <c r="W611" s="2"/>
       <c r="X611" s="2"/>
     </row>
-    <row r="612" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A612" s="24"/>
       <c r="B612" s="24"/>
       <c r="C612" s="24"/>
@@ -17345,7 +17372,7 @@
       <c r="W612" s="2"/>
       <c r="X612" s="2"/>
     </row>
-    <row r="613" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A613" s="24"/>
       <c r="B613" s="24"/>
       <c r="C613" s="24"/>
@@ -17371,7 +17398,7 @@
       <c r="W613" s="2"/>
       <c r="X613" s="2"/>
     </row>
-    <row r="614" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A614" s="24"/>
       <c r="B614" s="24"/>
       <c r="C614" s="24"/>
@@ -17397,7 +17424,7 @@
       <c r="W614" s="2"/>
       <c r="X614" s="2"/>
     </row>
-    <row r="615" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A615" s="24"/>
       <c r="B615" s="24"/>
       <c r="C615" s="24"/>
@@ -17423,7 +17450,7 @@
       <c r="W615" s="2"/>
       <c r="X615" s="2"/>
     </row>
-    <row r="616" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A616" s="24"/>
       <c r="B616" s="24"/>
       <c r="C616" s="24"/>
@@ -17449,7 +17476,7 @@
       <c r="W616" s="2"/>
       <c r="X616" s="2"/>
     </row>
-    <row r="617" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A617" s="24"/>
       <c r="B617" s="24"/>
       <c r="C617" s="24"/>
@@ -17475,7 +17502,7 @@
       <c r="W617" s="2"/>
       <c r="X617" s="2"/>
     </row>
-    <row r="618" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A618" s="24"/>
       <c r="B618" s="24"/>
       <c r="C618" s="24"/>
@@ -17501,7 +17528,7 @@
       <c r="W618" s="2"/>
       <c r="X618" s="2"/>
     </row>
-    <row r="619" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A619" s="24"/>
       <c r="B619" s="24"/>
       <c r="C619" s="24"/>
@@ -17527,7 +17554,7 @@
       <c r="W619" s="2"/>
       <c r="X619" s="2"/>
     </row>
-    <row r="620" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A620" s="24"/>
       <c r="B620" s="24"/>
       <c r="C620" s="24"/>
@@ -17553,7 +17580,7 @@
       <c r="W620" s="2"/>
       <c r="X620" s="2"/>
     </row>
-    <row r="621" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A621" s="24"/>
       <c r="B621" s="24"/>
       <c r="C621" s="24"/>
@@ -17579,7 +17606,7 @@
       <c r="W621" s="2"/>
       <c r="X621" s="2"/>
     </row>
-    <row r="622" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A622" s="24"/>
       <c r="B622" s="24"/>
       <c r="C622" s="24"/>
@@ -17605,7 +17632,7 @@
       <c r="W622" s="2"/>
       <c r="X622" s="2"/>
     </row>
-    <row r="623" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A623" s="24"/>
       <c r="B623" s="24"/>
       <c r="C623" s="24"/>
@@ -17631,7 +17658,7 @@
       <c r="W623" s="2"/>
       <c r="X623" s="2"/>
     </row>
-    <row r="624" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A624" s="24"/>
       <c r="B624" s="24"/>
       <c r="C624" s="24"/>
@@ -17657,7 +17684,7 @@
       <c r="W624" s="2"/>
       <c r="X624" s="2"/>
     </row>
-    <row r="625" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A625" s="24"/>
       <c r="B625" s="24"/>
       <c r="C625" s="24"/>
@@ -17683,7 +17710,7 @@
       <c r="W625" s="2"/>
       <c r="X625" s="2"/>
     </row>
-    <row r="626" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A626" s="24"/>
       <c r="B626" s="24"/>
       <c r="C626" s="24"/>
@@ -17709,7 +17736,7 @@
       <c r="W626" s="2"/>
       <c r="X626" s="2"/>
     </row>
-    <row r="627" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A627" s="24"/>
       <c r="B627" s="24"/>
       <c r="C627" s="24"/>
@@ -17735,7 +17762,7 @@
       <c r="W627" s="2"/>
       <c r="X627" s="2"/>
     </row>
-    <row r="628" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A628" s="24"/>
       <c r="B628" s="24"/>
       <c r="C628" s="24"/>
@@ -17761,7 +17788,7 @@
       <c r="W628" s="2"/>
       <c r="X628" s="2"/>
     </row>
-    <row r="629" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A629" s="24"/>
       <c r="B629" s="24"/>
       <c r="C629" s="24"/>
@@ -17787,7 +17814,7 @@
       <c r="W629" s="2"/>
       <c r="X629" s="2"/>
     </row>
-    <row r="630" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A630" s="24"/>
       <c r="B630" s="24"/>
       <c r="C630" s="24"/>
@@ -17813,7 +17840,7 @@
       <c r="W630" s="2"/>
       <c r="X630" s="2"/>
     </row>
-    <row r="631" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A631" s="24"/>
       <c r="B631" s="24"/>
       <c r="C631" s="24"/>
@@ -17839,7 +17866,7 @@
       <c r="W631" s="2"/>
       <c r="X631" s="2"/>
     </row>
-    <row r="632" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A632" s="24"/>
       <c r="B632" s="24"/>
       <c r="C632" s="24"/>
@@ -17865,7 +17892,7 @@
       <c r="W632" s="2"/>
       <c r="X632" s="2"/>
     </row>
-    <row r="633" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A633" s="24"/>
       <c r="B633" s="24"/>
       <c r="C633" s="24"/>
@@ -17891,7 +17918,7 @@
       <c r="W633" s="2"/>
       <c r="X633" s="2"/>
     </row>
-    <row r="634" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A634" s="24"/>
       <c r="B634" s="24"/>
       <c r="C634" s="24"/>
@@ -17917,7 +17944,7 @@
       <c r="W634" s="2"/>
       <c r="X634" s="2"/>
     </row>
-    <row r="635" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A635" s="24"/>
       <c r="B635" s="24"/>
       <c r="C635" s="24"/>
@@ -17943,7 +17970,7 @@
       <c r="W635" s="2"/>
       <c r="X635" s="2"/>
     </row>
-    <row r="636" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A636" s="24"/>
       <c r="B636" s="24"/>
       <c r="C636" s="24"/>
@@ -17969,7 +17996,7 @@
       <c r="W636" s="2"/>
       <c r="X636" s="2"/>
     </row>
-    <row r="637" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A637" s="24"/>
       <c r="B637" s="24"/>
       <c r="C637" s="24"/>
@@ -17995,7 +18022,7 @@
       <c r="W637" s="2"/>
       <c r="X637" s="2"/>
     </row>
-    <row r="638" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A638" s="24"/>
       <c r="B638" s="24"/>
       <c r="C638" s="24"/>
@@ -18021,7 +18048,7 @@
       <c r="W638" s="2"/>
       <c r="X638" s="2"/>
     </row>
-    <row r="639" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A639" s="24"/>
       <c r="B639" s="24"/>
       <c r="C639" s="24"/>
@@ -18047,7 +18074,7 @@
       <c r="W639" s="2"/>
       <c r="X639" s="2"/>
     </row>
-    <row r="640" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A640" s="24"/>
       <c r="B640" s="24"/>
       <c r="C640" s="24"/>
@@ -18073,7 +18100,7 @@
       <c r="W640" s="2"/>
       <c r="X640" s="2"/>
     </row>
-    <row r="641" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A641" s="24"/>
       <c r="B641" s="24"/>
       <c r="C641" s="24"/>
@@ -18099,7 +18126,7 @@
       <c r="W641" s="2"/>
       <c r="X641" s="2"/>
     </row>
-    <row r="642" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A642" s="24"/>
       <c r="B642" s="24"/>
       <c r="C642" s="24"/>
@@ -18125,7 +18152,7 @@
       <c r="W642" s="2"/>
       <c r="X642" s="2"/>
     </row>
-    <row r="643" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A643" s="24"/>
       <c r="B643" s="24"/>
       <c r="C643" s="24"/>
@@ -18151,7 +18178,7 @@
       <c r="W643" s="2"/>
       <c r="X643" s="2"/>
     </row>
-    <row r="644" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A644" s="24"/>
       <c r="B644" s="24"/>
       <c r="C644" s="24"/>
@@ -18177,7 +18204,7 @@
       <c r="W644" s="2"/>
       <c r="X644" s="2"/>
     </row>
-    <row r="645" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A645" s="24"/>
       <c r="B645" s="24"/>
       <c r="C645" s="24"/>
@@ -18203,7 +18230,7 @@
       <c r="W645" s="2"/>
       <c r="X645" s="2"/>
     </row>
-    <row r="646" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A646" s="24"/>
       <c r="B646" s="24"/>
       <c r="C646" s="24"/>
@@ -18229,7 +18256,7 @@
       <c r="W646" s="2"/>
       <c r="X646" s="2"/>
     </row>
-    <row r="647" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A647" s="24"/>
       <c r="B647" s="24"/>
       <c r="C647" s="24"/>
@@ -18255,7 +18282,7 @@
       <c r="W647" s="2"/>
       <c r="X647" s="2"/>
     </row>
-    <row r="648" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A648" s="24"/>
       <c r="B648" s="24"/>
       <c r="C648" s="24"/>
@@ -18281,7 +18308,7 @@
       <c r="W648" s="2"/>
       <c r="X648" s="2"/>
     </row>
-    <row r="649" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A649" s="24"/>
       <c r="B649" s="24"/>
       <c r="C649" s="24"/>
@@ -18307,7 +18334,7 @@
       <c r="W649" s="2"/>
       <c r="X649" s="2"/>
     </row>
-    <row r="650" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A650" s="24"/>
       <c r="B650" s="24"/>
       <c r="C650" s="24"/>
@@ -18333,7 +18360,7 @@
       <c r="W650" s="2"/>
       <c r="X650" s="2"/>
     </row>
-    <row r="651" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A651" s="24"/>
       <c r="B651" s="24"/>
       <c r="C651" s="24"/>
@@ -18359,7 +18386,7 @@
       <c r="W651" s="2"/>
       <c r="X651" s="2"/>
     </row>
-    <row r="652" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A652" s="24"/>
       <c r="B652" s="24"/>
       <c r="C652" s="24"/>
@@ -18385,7 +18412,7 @@
       <c r="W652" s="2"/>
       <c r="X652" s="2"/>
     </row>
-    <row r="653" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A653" s="24"/>
       <c r="B653" s="24"/>
       <c r="C653" s="24"/>
@@ -18411,7 +18438,7 @@
       <c r="W653" s="2"/>
       <c r="X653" s="2"/>
     </row>
-    <row r="654" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A654" s="24"/>
       <c r="B654" s="24"/>
       <c r="C654" s="24"/>
@@ -18437,7 +18464,7 @@
       <c r="W654" s="2"/>
       <c r="X654" s="2"/>
     </row>
-    <row r="655" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A655" s="24"/>
       <c r="B655" s="24"/>
       <c r="C655" s="24"/>
@@ -18463,7 +18490,7 @@
       <c r="W655" s="2"/>
       <c r="X655" s="2"/>
     </row>
-    <row r="656" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A656" s="24"/>
       <c r="B656" s="24"/>
       <c r="C656" s="24"/>
@@ -18489,7 +18516,7 @@
       <c r="W656" s="2"/>
       <c r="X656" s="2"/>
     </row>
-    <row r="657" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A657" s="24"/>
       <c r="B657" s="24"/>
       <c r="C657" s="24"/>
@@ -18515,7 +18542,7 @@
       <c r="W657" s="2"/>
       <c r="X657" s="2"/>
     </row>
-    <row r="658" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A658" s="24"/>
       <c r="B658" s="24"/>
       <c r="C658" s="24"/>
@@ -18541,7 +18568,7 @@
       <c r="W658" s="2"/>
       <c r="X658" s="2"/>
     </row>
-    <row r="659" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A659" s="24"/>
       <c r="B659" s="24"/>
       <c r="C659" s="24"/>
@@ -18567,7 +18594,7 @@
       <c r="W659" s="2"/>
       <c r="X659" s="2"/>
     </row>
-    <row r="660" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A660" s="24"/>
       <c r="B660" s="24"/>
       <c r="C660" s="24"/>
@@ -18593,7 +18620,7 @@
       <c r="W660" s="2"/>
       <c r="X660" s="2"/>
     </row>
-    <row r="661" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A661" s="24"/>
       <c r="B661" s="24"/>
       <c r="C661" s="24"/>
@@ -18619,7 +18646,7 @@
       <c r="W661" s="2"/>
       <c r="X661" s="2"/>
     </row>
-    <row r="662" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A662" s="24"/>
       <c r="B662" s="24"/>
       <c r="C662" s="24"/>
@@ -18645,7 +18672,7 @@
       <c r="W662" s="2"/>
       <c r="X662" s="2"/>
     </row>
-    <row r="663" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A663" s="24"/>
       <c r="B663" s="24"/>
       <c r="C663" s="24"/>
@@ -18671,7 +18698,7 @@
       <c r="W663" s="2"/>
       <c r="X663" s="2"/>
     </row>
-    <row r="664" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A664" s="24"/>
       <c r="B664" s="24"/>
       <c r="C664" s="24"/>
@@ -18697,7 +18724,7 @@
       <c r="W664" s="2"/>
       <c r="X664" s="2"/>
     </row>
-    <row r="665" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A665" s="24"/>
       <c r="B665" s="24"/>
       <c r="C665" s="24"/>
@@ -18723,7 +18750,7 @@
       <c r="W665" s="2"/>
       <c r="X665" s="2"/>
     </row>
-    <row r="666" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A666" s="24"/>
       <c r="B666" s="24"/>
       <c r="C666" s="24"/>
@@ -18749,7 +18776,7 @@
       <c r="W666" s="2"/>
       <c r="X666" s="2"/>
     </row>
-    <row r="667" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A667" s="24"/>
       <c r="B667" s="24"/>
       <c r="C667" s="24"/>
@@ -18775,7 +18802,7 @@
       <c r="W667" s="2"/>
       <c r="X667" s="2"/>
     </row>
-    <row r="668" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A668" s="24"/>
       <c r="B668" s="24"/>
       <c r="C668" s="24"/>
@@ -18801,7 +18828,7 @@
       <c r="W668" s="2"/>
       <c r="X668" s="2"/>
     </row>
-    <row r="669" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A669" s="24"/>
       <c r="B669" s="24"/>
       <c r="C669" s="24"/>
@@ -18827,7 +18854,7 @@
       <c r="W669" s="2"/>
       <c r="X669" s="2"/>
     </row>
-    <row r="670" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A670" s="24"/>
       <c r="B670" s="24"/>
       <c r="C670" s="24"/>
@@ -18853,7 +18880,7 @@
       <c r="W670" s="2"/>
       <c r="X670" s="2"/>
     </row>
-    <row r="671" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A671" s="24"/>
       <c r="B671" s="24"/>
       <c r="C671" s="24"/>
@@ -18879,7 +18906,7 @@
       <c r="W671" s="2"/>
       <c r="X671" s="2"/>
     </row>
-    <row r="672" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A672" s="24"/>
       <c r="B672" s="24"/>
       <c r="C672" s="24"/>
@@ -18905,7 +18932,7 @@
       <c r="W672" s="2"/>
       <c r="X672" s="2"/>
     </row>
-    <row r="673" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A673" s="24"/>
       <c r="B673" s="24"/>
       <c r="C673" s="24"/>
@@ -18931,7 +18958,7 @@
       <c r="W673" s="2"/>
       <c r="X673" s="2"/>
     </row>
-    <row r="674" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A674" s="24"/>
       <c r="B674" s="24"/>
       <c r="C674" s="24"/>
@@ -18957,7 +18984,7 @@
       <c r="W674" s="2"/>
       <c r="X674" s="2"/>
     </row>
-    <row r="675" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A675" s="24"/>
       <c r="B675" s="24"/>
       <c r="C675" s="24"/>
@@ -18983,7 +19010,7 @@
       <c r="W675" s="2"/>
       <c r="X675" s="2"/>
     </row>
-    <row r="676" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A676" s="24"/>
       <c r="B676" s="24"/>
       <c r="C676" s="24"/>
@@ -19009,7 +19036,7 @@
       <c r="W676" s="2"/>
       <c r="X676" s="2"/>
     </row>
-    <row r="677" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A677" s="24"/>
       <c r="B677" s="24"/>
       <c r="C677" s="24"/>
@@ -19035,7 +19062,7 @@
       <c r="W677" s="2"/>
       <c r="X677" s="2"/>
     </row>
-    <row r="678" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A678" s="24"/>
       <c r="B678" s="24"/>
       <c r="C678" s="24"/>
@@ -19061,7 +19088,7 @@
       <c r="W678" s="2"/>
       <c r="X678" s="2"/>
     </row>
-    <row r="679" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A679" s="24"/>
       <c r="B679" s="24"/>
       <c r="C679" s="24"/>
@@ -19087,7 +19114,7 @@
       <c r="W679" s="2"/>
       <c r="X679" s="2"/>
     </row>
-    <row r="680" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A680" s="24"/>
       <c r="B680" s="24"/>
       <c r="C680" s="24"/>
@@ -19113,7 +19140,7 @@
       <c r="W680" s="2"/>
       <c r="X680" s="2"/>
     </row>
-    <row r="681" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A681" s="24"/>
       <c r="B681" s="24"/>
       <c r="C681" s="24"/>
@@ -19139,7 +19166,7 @@
       <c r="W681" s="2"/>
       <c r="X681" s="2"/>
     </row>
-    <row r="682" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A682" s="24"/>
       <c r="B682" s="24"/>
       <c r="C682" s="24"/>
@@ -19165,7 +19192,7 @@
       <c r="W682" s="2"/>
       <c r="X682" s="2"/>
     </row>
-    <row r="683" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A683" s="24"/>
       <c r="B683" s="24"/>
       <c r="C683" s="24"/>
@@ -19191,7 +19218,7 @@
       <c r="W683" s="2"/>
       <c r="X683" s="2"/>
     </row>
-    <row r="684" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A684" s="24"/>
       <c r="B684" s="24"/>
       <c r="C684" s="24"/>
@@ -19217,7 +19244,7 @@
       <c r="W684" s="2"/>
       <c r="X684" s="2"/>
     </row>
-    <row r="685" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A685" s="24"/>
       <c r="B685" s="24"/>
       <c r="C685" s="24"/>
@@ -19243,7 +19270,7 @@
       <c r="W685" s="2"/>
       <c r="X685" s="2"/>
     </row>
-    <row r="686" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A686" s="24"/>
       <c r="B686" s="24"/>
       <c r="C686" s="24"/>
@@ -19269,7 +19296,7 @@
       <c r="W686" s="2"/>
       <c r="X686" s="2"/>
     </row>
-    <row r="687" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A687" s="24"/>
       <c r="B687" s="24"/>
       <c r="C687" s="24"/>
@@ -19295,7 +19322,7 @@
       <c r="W687" s="2"/>
       <c r="X687" s="2"/>
     </row>
-    <row r="688" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A688" s="24"/>
       <c r="B688" s="24"/>
       <c r="C688" s="24"/>
@@ -19321,7 +19348,7 @@
       <c r="W688" s="2"/>
       <c r="X688" s="2"/>
     </row>
-    <row r="689" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A689" s="24"/>
       <c r="B689" s="24"/>
       <c r="C689" s="24"/>
@@ -19347,7 +19374,7 @@
       <c r="W689" s="2"/>
       <c r="X689" s="2"/>
     </row>
-    <row r="690" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A690" s="24"/>
       <c r="B690" s="24"/>
       <c r="C690" s="24"/>
@@ -19373,7 +19400,7 @@
       <c r="W690" s="2"/>
       <c r="X690" s="2"/>
     </row>
-    <row r="691" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A691" s="24"/>
       <c r="B691" s="24"/>
       <c r="C691" s="24"/>
@@ -19399,7 +19426,7 @@
       <c r="W691" s="2"/>
       <c r="X691" s="2"/>
     </row>
-    <row r="692" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A692" s="24"/>
       <c r="B692" s="24"/>
       <c r="C692" s="24"/>
@@ -19425,7 +19452,7 @@
       <c r="W692" s="2"/>
       <c r="X692" s="2"/>
     </row>
-    <row r="693" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A693" s="24"/>
       <c r="B693" s="24"/>
       <c r="C693" s="24"/>
@@ -19451,7 +19478,7 @@
       <c r="W693" s="2"/>
       <c r="X693" s="2"/>
     </row>
-    <row r="694" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A694" s="24"/>
       <c r="B694" s="24"/>
       <c r="C694" s="24"/>
@@ -19477,7 +19504,7 @@
       <c r="W694" s="2"/>
       <c r="X694" s="2"/>
     </row>
-    <row r="695" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A695" s="24"/>
       <c r="B695" s="24"/>
       <c r="C695" s="24"/>
@@ -19503,7 +19530,7 @@
       <c r="W695" s="2"/>
       <c r="X695" s="2"/>
     </row>
-    <row r="696" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A696" s="24"/>
       <c r="B696" s="24"/>
       <c r="C696" s="24"/>
@@ -19529,7 +19556,7 @@
       <c r="W696" s="2"/>
       <c r="X696" s="2"/>
     </row>
-    <row r="697" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A697" s="24"/>
       <c r="B697" s="24"/>
       <c r="C697" s="24"/>
@@ -19555,7 +19582,7 @@
       <c r="W697" s="2"/>
       <c r="X697" s="2"/>
     </row>
-    <row r="698" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A698" s="24"/>
       <c r="B698" s="24"/>
       <c r="C698" s="24"/>
@@ -19581,7 +19608,7 @@
       <c r="W698" s="2"/>
       <c r="X698" s="2"/>
     </row>
-    <row r="699" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A699" s="24"/>
       <c r="B699" s="24"/>
       <c r="C699" s="24"/>
@@ -19607,7 +19634,7 @@
       <c r="W699" s="2"/>
       <c r="X699" s="2"/>
     </row>
-    <row r="700" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A700" s="24"/>
       <c r="B700" s="24"/>
       <c r="C700" s="24"/>
@@ -19633,7 +19660,7 @@
       <c r="W700" s="2"/>
       <c r="X700" s="2"/>
     </row>
-    <row r="701" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A701" s="24"/>
       <c r="B701" s="24"/>
       <c r="C701" s="24"/>
@@ -19659,7 +19686,7 @@
       <c r="W701" s="2"/>
       <c r="X701" s="2"/>
     </row>
-    <row r="702" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A702" s="24"/>
       <c r="B702" s="24"/>
       <c r="C702" s="24"/>
@@ -19685,7 +19712,7 @@
       <c r="W702" s="2"/>
       <c r="X702" s="2"/>
     </row>
-    <row r="703" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A703" s="24"/>
       <c r="B703" s="24"/>
       <c r="C703" s="24"/>
@@ -19711,7 +19738,7 @@
       <c r="W703" s="2"/>
       <c r="X703" s="2"/>
     </row>
-    <row r="704" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A704" s="24"/>
       <c r="B704" s="24"/>
       <c r="C704" s="24"/>
@@ -19737,7 +19764,7 @@
       <c r="W704" s="2"/>
       <c r="X704" s="2"/>
     </row>
-    <row r="705" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A705" s="24"/>
       <c r="B705" s="24"/>
       <c r="C705" s="24"/>
@@ -19763,7 +19790,7 @@
       <c r="W705" s="2"/>
       <c r="X705" s="2"/>
     </row>
-    <row r="706" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A706" s="24"/>
       <c r="B706" s="24"/>
       <c r="C706" s="24"/>
@@ -19789,7 +19816,7 @@
       <c r="W706" s="2"/>
       <c r="X706" s="2"/>
     </row>
-    <row r="707" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A707" s="24"/>
       <c r="B707" s="24"/>
       <c r="C707" s="24"/>
@@ -19815,7 +19842,7 @@
       <c r="W707" s="2"/>
       <c r="X707" s="2"/>
     </row>
-    <row r="708" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A708" s="24"/>
       <c r="B708" s="24"/>
       <c r="C708" s="24"/>
@@ -19841,7 +19868,7 @@
       <c r="W708" s="2"/>
       <c r="X708" s="2"/>
     </row>
-    <row r="709" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A709" s="24"/>
       <c r="B709" s="24"/>
       <c r="C709" s="24"/>
@@ -19867,7 +19894,7 @@
       <c r="W709" s="2"/>
       <c r="X709" s="2"/>
     </row>
-    <row r="710" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A710" s="24"/>
       <c r="B710" s="24"/>
       <c r="C710" s="24"/>
@@ -19893,7 +19920,7 @@
       <c r="W710" s="2"/>
       <c r="X710" s="2"/>
     </row>
-    <row r="711" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A711" s="24"/>
       <c r="B711" s="24"/>
       <c r="C711" s="24"/>
@@ -19919,7 +19946,7 @@
       <c r="W711" s="2"/>
       <c r="X711" s="2"/>
     </row>
-    <row r="712" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A712" s="24"/>
       <c r="B712" s="24"/>
       <c r="C712" s="24"/>
@@ -19945,7 +19972,7 @@
       <c r="W712" s="2"/>
       <c r="X712" s="2"/>
     </row>
-    <row r="713" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A713" s="24"/>
       <c r="B713" s="24"/>
       <c r="C713" s="24"/>
@@ -19971,7 +19998,7 @@
       <c r="W713" s="2"/>
       <c r="X713" s="2"/>
     </row>
-    <row r="714" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A714" s="24"/>
       <c r="B714" s="24"/>
       <c r="C714" s="24"/>
@@ -19997,7 +20024,7 @@
       <c r="W714" s="2"/>
       <c r="X714" s="2"/>
     </row>
-    <row r="715" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A715" s="24"/>
       <c r="B715" s="24"/>
       <c r="C715" s="24"/>
@@ -20023,7 +20050,7 @@
       <c r="W715" s="2"/>
       <c r="X715" s="2"/>
     </row>
-    <row r="716" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A716" s="24"/>
       <c r="B716" s="24"/>
       <c r="C716" s="24"/>
@@ -20049,7 +20076,7 @@
       <c r="W716" s="2"/>
       <c r="X716" s="2"/>
     </row>
-    <row r="717" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A717" s="24"/>
       <c r="B717" s="24"/>
       <c r="C717" s="24"/>
@@ -20075,7 +20102,7 @@
       <c r="W717" s="2"/>
       <c r="X717" s="2"/>
     </row>
-    <row r="718" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A718" s="24"/>
       <c r="B718" s="24"/>
       <c r="C718" s="24"/>
@@ -20101,7 +20128,7 @@
       <c r="W718" s="2"/>
       <c r="X718" s="2"/>
     </row>
-    <row r="719" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A719" s="24"/>
       <c r="B719" s="24"/>
       <c r="C719" s="24"/>
@@ -20127,7 +20154,7 @@
       <c r="W719" s="2"/>
       <c r="X719" s="2"/>
     </row>
-    <row r="720" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A720" s="24"/>
       <c r="B720" s="24"/>
       <c r="C720" s="24"/>
@@ -20153,7 +20180,7 @@
       <c r="W720" s="2"/>
       <c r="X720" s="2"/>
     </row>
-    <row r="721" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A721" s="24"/>
       <c r="B721" s="24"/>
       <c r="C721" s="24"/>
@@ -20179,7 +20206,7 @@
       <c r="W721" s="2"/>
       <c r="X721" s="2"/>
     </row>
-    <row r="722" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A722" s="24"/>
       <c r="B722" s="24"/>
       <c r="C722" s="24"/>
@@ -20205,7 +20232,7 @@
       <c r="W722" s="2"/>
       <c r="X722" s="2"/>
     </row>
-    <row r="723" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A723" s="24"/>
       <c r="B723" s="24"/>
       <c r="C723" s="24"/>
@@ -20231,7 +20258,7 @@
       <c r="W723" s="2"/>
       <c r="X723" s="2"/>
     </row>
-    <row r="724" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A724" s="24"/>
       <c r="B724" s="24"/>
       <c r="C724" s="24"/>
@@ -20257,7 +20284,7 @@
       <c r="W724" s="2"/>
       <c r="X724" s="2"/>
     </row>
-    <row r="725" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A725" s="24"/>
       <c r="B725" s="24"/>
       <c r="C725" s="24"/>
@@ -20283,7 +20310,7 @@
       <c r="W725" s="2"/>
       <c r="X725" s="2"/>
     </row>
-    <row r="726" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A726" s="24"/>
       <c r="B726" s="24"/>
       <c r="C726" s="24"/>
@@ -20309,7 +20336,7 @@
       <c r="W726" s="2"/>
       <c r="X726" s="2"/>
     </row>
-    <row r="727" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A727" s="24"/>
       <c r="B727" s="24"/>
       <c r="C727" s="24"/>
@@ -20335,7 +20362,7 @@
       <c r="W727" s="2"/>
       <c r="X727" s="2"/>
     </row>
-    <row r="728" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A728" s="24"/>
       <c r="B728" s="24"/>
       <c r="C728" s="24"/>
@@ -20361,7 +20388,7 @@
       <c r="W728" s="2"/>
       <c r="X728" s="2"/>
     </row>
-    <row r="729" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A729" s="24"/>
       <c r="B729" s="24"/>
       <c r="C729" s="24"/>
@@ -20387,7 +20414,7 @@
       <c r="W729" s="2"/>
       <c r="X729" s="2"/>
     </row>
-    <row r="730" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A730" s="24"/>
       <c r="B730" s="24"/>
       <c r="C730" s="24"/>
@@ -20413,7 +20440,7 @@
       <c r="W730" s="2"/>
       <c r="X730" s="2"/>
     </row>
-    <row r="731" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A731" s="24"/>
       <c r="B731" s="24"/>
       <c r="C731" s="24"/>
@@ -20439,7 +20466,7 @@
       <c r="W731" s="2"/>
       <c r="X731" s="2"/>
     </row>
-    <row r="732" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A732" s="24"/>
       <c r="B732" s="24"/>
       <c r="C732" s="24"/>
@@ -20465,7 +20492,7 @@
       <c r="W732" s="2"/>
       <c r="X732" s="2"/>
     </row>
-    <row r="733" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A733" s="24"/>
       <c r="B733" s="24"/>
       <c r="C733" s="24"/>
@@ -20491,7 +20518,7 @@
       <c r="W733" s="2"/>
       <c r="X733" s="2"/>
     </row>
-    <row r="734" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A734" s="24"/>
       <c r="B734" s="24"/>
       <c r="C734" s="24"/>
@@ -20517,7 +20544,7 @@
       <c r="W734" s="2"/>
       <c r="X734" s="2"/>
     </row>
-    <row r="735" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A735" s="24"/>
       <c r="B735" s="24"/>
       <c r="C735" s="24"/>
@@ -20543,7 +20570,7 @@
       <c r="W735" s="2"/>
       <c r="X735" s="2"/>
     </row>
-    <row r="736" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A736" s="24"/>
       <c r="B736" s="24"/>
       <c r="C736" s="24"/>
@@ -20569,7 +20596,7 @@
       <c r="W736" s="2"/>
       <c r="X736" s="2"/>
     </row>
-    <row r="737" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A737" s="24"/>
       <c r="B737" s="24"/>
       <c r="C737" s="24"/>
@@ -20595,7 +20622,7 @@
       <c r="W737" s="2"/>
       <c r="X737" s="2"/>
     </row>
-    <row r="738" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A738" s="24"/>
       <c r="B738" s="24"/>
       <c r="C738" s="24"/>
@@ -20621,7 +20648,7 @@
       <c r="W738" s="2"/>
       <c r="X738" s="2"/>
     </row>
-    <row r="739" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A739" s="24"/>
       <c r="B739" s="24"/>
       <c r="C739" s="24"/>
@@ -20647,7 +20674,7 @@
       <c r="W739" s="2"/>
       <c r="X739" s="2"/>
     </row>
-    <row r="740" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A740" s="24"/>
       <c r="B740" s="24"/>
       <c r="C740" s="24"/>
@@ -20673,7 +20700,7 @@
       <c r="W740" s="2"/>
       <c r="X740" s="2"/>
     </row>
-    <row r="741" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A741" s="24"/>
       <c r="B741" s="24"/>
       <c r="C741" s="24"/>
@@ -20699,7 +20726,7 @@
       <c r="W741" s="2"/>
       <c r="X741" s="2"/>
     </row>
-    <row r="742" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A742" s="24"/>
       <c r="B742" s="24"/>
       <c r="C742" s="24"/>
@@ -20725,7 +20752,7 @@
       <c r="W742" s="2"/>
       <c r="X742" s="2"/>
     </row>
-    <row r="743" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A743" s="24"/>
       <c r="B743" s="24"/>
       <c r="C743" s="24"/>
@@ -20751,7 +20778,7 @@
       <c r="W743" s="2"/>
       <c r="X743" s="2"/>
     </row>
-    <row r="744" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A744" s="24"/>
       <c r="B744" s="24"/>
       <c r="C744" s="24"/>
@@ -20777,7 +20804,7 @@
       <c r="W744" s="2"/>
       <c r="X744" s="2"/>
     </row>
-    <row r="745" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A745" s="24"/>
       <c r="B745" s="24"/>
       <c r="C745" s="24"/>
@@ -20803,7 +20830,7 @@
       <c r="W745" s="2"/>
       <c r="X745" s="2"/>
     </row>
-    <row r="746" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A746" s="24"/>
       <c r="B746" s="24"/>
       <c r="C746" s="24"/>
@@ -20829,7 +20856,7 @@
       <c r="W746" s="2"/>
       <c r="X746" s="2"/>
     </row>
-    <row r="747" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A747" s="24"/>
       <c r="B747" s="24"/>
       <c r="C747" s="24"/>
@@ -20855,7 +20882,7 @@
       <c r="W747" s="2"/>
       <c r="X747" s="2"/>
     </row>
-    <row r="748" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A748" s="24"/>
       <c r="B748" s="24"/>
       <c r="C748" s="24"/>
@@ -20881,7 +20908,7 @@
       <c r="W748" s="2"/>
       <c r="X748" s="2"/>
     </row>
-    <row r="749" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A749" s="24"/>
       <c r="B749" s="24"/>
       <c r="C749" s="24"/>
@@ -20907,7 +20934,7 @@
       <c r="W749" s="2"/>
       <c r="X749" s="2"/>
     </row>
-    <row r="750" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A750" s="24"/>
       <c r="B750" s="24"/>
       <c r="C750" s="24"/>
@@ -20933,7 +20960,7 @@
       <c r="W750" s="2"/>
       <c r="X750" s="2"/>
     </row>
-    <row r="751" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A751" s="24"/>
       <c r="B751" s="24"/>
       <c r="C751" s="24"/>
@@ -20959,7 +20986,7 @@
       <c r="W751" s="2"/>
       <c r="X751" s="2"/>
     </row>
-    <row r="752" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A752" s="24"/>
       <c r="B752" s="24"/>
       <c r="C752" s="24"/>
@@ -20985,7 +21012,7 @@
       <c r="W752" s="2"/>
       <c r="X752" s="2"/>
     </row>
-    <row r="753" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A753" s="24"/>
       <c r="B753" s="24"/>
       <c r="C753" s="24"/>
@@ -21011,7 +21038,7 @@
       <c r="W753" s="2"/>
       <c r="X753" s="2"/>
     </row>
-    <row r="754" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A754" s="24"/>
       <c r="B754" s="24"/>
       <c r="C754" s="24"/>
@@ -21037,7 +21064,7 @@
       <c r="W754" s="2"/>
       <c r="X754" s="2"/>
     </row>
-    <row r="755" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A755" s="24"/>
       <c r="B755" s="24"/>
       <c r="C755" s="24"/>
@@ -21063,7 +21090,7 @@
       <c r="W755" s="2"/>
       <c r="X755" s="2"/>
     </row>
-    <row r="756" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A756" s="24"/>
       <c r="B756" s="24"/>
       <c r="C756" s="24"/>
@@ -21089,7 +21116,7 @@
       <c r="W756" s="2"/>
       <c r="X756" s="2"/>
     </row>
-    <row r="757" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A757" s="24"/>
       <c r="B757" s="24"/>
       <c r="C757" s="24"/>
@@ -21115,7 +21142,7 @@
       <c r="W757" s="2"/>
       <c r="X757" s="2"/>
     </row>
-    <row r="758" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A758" s="24"/>
       <c r="B758" s="24"/>
       <c r="C758" s="24"/>
@@ -21141,7 +21168,7 @@
       <c r="W758" s="2"/>
       <c r="X758" s="2"/>
     </row>
-    <row r="759" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A759" s="24"/>
       <c r="B759" s="24"/>
       <c r="C759" s="24"/>
@@ -21167,7 +21194,7 @@
       <c r="W759" s="2"/>
       <c r="X759" s="2"/>
     </row>
-    <row r="760" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A760" s="24"/>
       <c r="B760" s="24"/>
       <c r="C760" s="24"/>
@@ -21193,7 +21220,7 @@
       <c r="W760" s="2"/>
       <c r="X760" s="2"/>
     </row>
-    <row r="761" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A761" s="24"/>
       <c r="B761" s="24"/>
       <c r="C761" s="24"/>
@@ -21219,7 +21246,7 @@
       <c r="W761" s="2"/>
       <c r="X761" s="2"/>
     </row>
-    <row r="762" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A762" s="24"/>
       <c r="B762" s="24"/>
       <c r="C762" s="24"/>
@@ -21245,7 +21272,7 @@
       <c r="W762" s="2"/>
       <c r="X762" s="2"/>
     </row>
-    <row r="763" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A763" s="24"/>
       <c r="B763" s="24"/>
       <c r="C763" s="24"/>
@@ -21271,7 +21298,7 @@
       <c r="W763" s="2"/>
       <c r="X763" s="2"/>
     </row>
-    <row r="764" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A764" s="24"/>
       <c r="B764" s="24"/>
       <c r="C764" s="24"/>
@@ -21297,7 +21324,7 @@
       <c r="W764" s="2"/>
       <c r="X764" s="2"/>
     </row>
-    <row r="765" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A765" s="24"/>
       <c r="B765" s="24"/>
       <c r="C765" s="24"/>
@@ -21323,7 +21350,7 @@
       <c r="W765" s="2"/>
       <c r="X765" s="2"/>
     </row>
-    <row r="766" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A766" s="24"/>
       <c r="B766" s="24"/>
       <c r="C766" s="24"/>
@@ -21349,7 +21376,7 @@
       <c r="W766" s="2"/>
       <c r="X766" s="2"/>
     </row>
-    <row r="767" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A767" s="24"/>
       <c r="B767" s="24"/>
       <c r="C767" s="24"/>
@@ -21375,7 +21402,7 @@
       <c r="W767" s="2"/>
       <c r="X767" s="2"/>
     </row>
-    <row r="768" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A768" s="24"/>
       <c r="B768" s="24"/>
       <c r="C768" s="24"/>
@@ -21401,7 +21428,7 @@
       <c r="W768" s="2"/>
       <c r="X768" s="2"/>
     </row>
-    <row r="769" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A769" s="24"/>
       <c r="B769" s="24"/>
       <c r="C769" s="24"/>
@@ -21427,7 +21454,7 @@
       <c r="W769" s="2"/>
       <c r="X769" s="2"/>
     </row>
-    <row r="770" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A770" s="24"/>
       <c r="B770" s="24"/>
       <c r="C770" s="24"/>
@@ -21453,7 +21480,7 @@
       <c r="W770" s="2"/>
       <c r="X770" s="2"/>
     </row>
-    <row r="771" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A771" s="24"/>
       <c r="B771" s="24"/>
       <c r="C771" s="24"/>
@@ -21479,7 +21506,7 @@
       <c r="W771" s="2"/>
       <c r="X771" s="2"/>
     </row>
-    <row r="772" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A772" s="24"/>
       <c r="B772" s="24"/>
       <c r="C772" s="24"/>
@@ -21505,7 +21532,7 @@
       <c r="W772" s="2"/>
       <c r="X772" s="2"/>
     </row>
-    <row r="773" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A773" s="24"/>
       <c r="B773" s="24"/>
       <c r="C773" s="24"/>
@@ -21531,7 +21558,7 @@
       <c r="W773" s="2"/>
       <c r="X773" s="2"/>
     </row>
-    <row r="774" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A774" s="24"/>
       <c r="B774" s="24"/>
       <c r="C774" s="24"/>
@@ -21557,7 +21584,7 @@
       <c r="W774" s="2"/>
       <c r="X774" s="2"/>
     </row>
-    <row r="775" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A775" s="24"/>
       <c r="B775" s="24"/>
       <c r="C775" s="24"/>
@@ -21583,7 +21610,7 @@
       <c r="W775" s="2"/>
       <c r="X775" s="2"/>
     </row>
-    <row r="776" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A776" s="24"/>
       <c r="B776" s="24"/>
       <c r="C776" s="24"/>
@@ -21609,7 +21636,7 @@
       <c r="W776" s="2"/>
       <c r="X776" s="2"/>
     </row>
-    <row r="777" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A777" s="24"/>
       <c r="B777" s="24"/>
       <c r="C777" s="24"/>
@@ -21635,7 +21662,7 @@
       <c r="W777" s="2"/>
       <c r="X777" s="2"/>
     </row>
-    <row r="778" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A778" s="24"/>
       <c r="B778" s="24"/>
       <c r="C778" s="24"/>
@@ -21661,7 +21688,7 @@
       <c r="W778" s="2"/>
       <c r="X778" s="2"/>
     </row>
-    <row r="779" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A779" s="24"/>
       <c r="B779" s="24"/>
       <c r="C779" s="24"/>
@@ -21687,7 +21714,7 @@
       <c r="W779" s="2"/>
       <c r="X779" s="2"/>
     </row>
-    <row r="780" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A780" s="24"/>
       <c r="B780" s="24"/>
       <c r="C780" s="24"/>
@@ -21713,7 +21740,7 @@
       <c r="W780" s="2"/>
       <c r="X780" s="2"/>
     </row>
-    <row r="781" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A781" s="24"/>
       <c r="B781" s="24"/>
       <c r="C781" s="24"/>
@@ -21739,7 +21766,7 @@
       <c r="W781" s="2"/>
       <c r="X781" s="2"/>
     </row>
-    <row r="782" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A782" s="24"/>
       <c r="B782" s="24"/>
       <c r="C782" s="24"/>
@@ -21765,7 +21792,7 @@
       <c r="W782" s="2"/>
       <c r="X782" s="2"/>
     </row>
-    <row r="783" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A783" s="24"/>
       <c r="B783" s="24"/>
       <c r="C783" s="24"/>
@@ -21791,7 +21818,7 @@
       <c r="W783" s="2"/>
       <c r="X783" s="2"/>
     </row>
-    <row r="784" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A784" s="24"/>
       <c r="B784" s="24"/>
       <c r="C784" s="24"/>
@@ -21817,7 +21844,7 @@
       <c r="W784" s="2"/>
       <c r="X784" s="2"/>
     </row>
-    <row r="785" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A785" s="24"/>
       <c r="B785" s="24"/>
       <c r="C785" s="24"/>
@@ -21843,7 +21870,7 @@
       <c r="W785" s="2"/>
       <c r="X785" s="2"/>
     </row>
-    <row r="786" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A786" s="24"/>
       <c r="B786" s="24"/>
       <c r="C786" s="24"/>
@@ -21869,7 +21896,7 @@
       <c r="W786" s="2"/>
       <c r="X786" s="2"/>
     </row>
-    <row r="787" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A787" s="24"/>
       <c r="B787" s="24"/>
       <c r="C787" s="24"/>
@@ -21895,7 +21922,7 @@
       <c r="W787" s="2"/>
       <c r="X787" s="2"/>
     </row>
-    <row r="788" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A788" s="24"/>
       <c r="B788" s="24"/>
       <c r="C788" s="24"/>
@@ -21921,7 +21948,7 @@
       <c r="W788" s="2"/>
       <c r="X788" s="2"/>
     </row>
-    <row r="789" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A789" s="24"/>
       <c r="B789" s="24"/>
       <c r="C789" s="24"/>
@@ -21947,7 +21974,7 @@
       <c r="W789" s="2"/>
       <c r="X789" s="2"/>
     </row>
-    <row r="790" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A790" s="24"/>
       <c r="B790" s="24"/>
       <c r="C790" s="24"/>
@@ -21973,7 +22000,7 @@
       <c r="W790" s="2"/>
       <c r="X790" s="2"/>
     </row>
-    <row r="791" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="791" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A791" s="24"/>
       <c r="B791" s="24"/>
       <c r="C791" s="24"/>
@@ -21999,7 +22026,7 @@
       <c r="W791" s="2"/>
       <c r="X791" s="2"/>
     </row>
-    <row r="792" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="792" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A792" s="24"/>
       <c r="B792" s="24"/>
       <c r="C792" s="24"/>
@@ -22025,7 +22052,7 @@
       <c r="W792" s="2"/>
       <c r="X792" s="2"/>
     </row>
-    <row r="793" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A793" s="24"/>
       <c r="B793" s="24"/>
       <c r="C793" s="24"/>
@@ -22051,7 +22078,7 @@
       <c r="W793" s="2"/>
       <c r="X793" s="2"/>
     </row>
-    <row r="794" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="794" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A794" s="24"/>
       <c r="B794" s="24"/>
       <c r="C794" s="24"/>
@@ -22077,7 +22104,7 @@
       <c r="W794" s="2"/>
       <c r="X794" s="2"/>
     </row>
-    <row r="795" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A795" s="24"/>
       <c r="B795" s="24"/>
       <c r="C795" s="24"/>
@@ -22103,7 +22130,7 @@
       <c r="W795" s="2"/>
       <c r="X795" s="2"/>
     </row>
-    <row r="796" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="796" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A796" s="24"/>
       <c r="B796" s="24"/>
       <c r="C796" s="24"/>
@@ -22129,7 +22156,7 @@
       <c r="W796" s="2"/>
       <c r="X796" s="2"/>
     </row>
-    <row r="797" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A797" s="24"/>
       <c r="B797" s="24"/>
       <c r="C797" s="24"/>
@@ -22155,7 +22182,7 @@
       <c r="W797" s="2"/>
       <c r="X797" s="2"/>
     </row>
-    <row r="798" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="798" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A798" s="24"/>
       <c r="B798" s="24"/>
       <c r="C798" s="24"/>
@@ -22181,7 +22208,7 @@
       <c r="W798" s="2"/>
       <c r="X798" s="2"/>
     </row>
-    <row r="799" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="799" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A799" s="24"/>
       <c r="B799" s="24"/>
       <c r="C799" s="24"/>
@@ -22207,7 +22234,7 @@
       <c r="W799" s="2"/>
       <c r="X799" s="2"/>
     </row>
-    <row r="800" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="800" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A800" s="24"/>
       <c r="B800" s="24"/>
       <c r="C800" s="24"/>
@@ -22233,7 +22260,7 @@
       <c r="W800" s="2"/>
       <c r="X800" s="2"/>
     </row>
-    <row r="801" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="801" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A801" s="24"/>
       <c r="B801" s="24"/>
       <c r="C801" s="24"/>
@@ -22259,7 +22286,7 @@
       <c r="W801" s="2"/>
       <c r="X801" s="2"/>
     </row>
-    <row r="802" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="802" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A802" s="24"/>
       <c r="B802" s="24"/>
       <c r="C802" s="24"/>
@@ -22285,7 +22312,7 @@
       <c r="W802" s="2"/>
       <c r="X802" s="2"/>
     </row>
-    <row r="803" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="803" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A803" s="24"/>
       <c r="B803" s="24"/>
       <c r="C803" s="24"/>
@@ -22311,7 +22338,7 @@
       <c r="W803" s="2"/>
       <c r="X803" s="2"/>
     </row>
-    <row r="804" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="804" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A804" s="24"/>
       <c r="B804" s="24"/>
       <c r="C804" s="24"/>
@@ -22337,7 +22364,7 @@
       <c r="W804" s="2"/>
       <c r="X804" s="2"/>
     </row>
-    <row r="805" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="805" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A805" s="24"/>
       <c r="B805" s="24"/>
       <c r="C805" s="24"/>
@@ -22363,7 +22390,7 @@
       <c r="W805" s="2"/>
       <c r="X805" s="2"/>
     </row>
-    <row r="806" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="806" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A806" s="24"/>
       <c r="B806" s="24"/>
       <c r="C806" s="24"/>
@@ -22389,7 +22416,7 @@
       <c r="W806" s="2"/>
       <c r="X806" s="2"/>
     </row>
-    <row r="807" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="807" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A807" s="24"/>
       <c r="B807" s="24"/>
       <c r="C807" s="24"/>
@@ -22415,7 +22442,7 @@
       <c r="W807" s="2"/>
       <c r="X807" s="2"/>
     </row>
-    <row r="808" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="808" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A808" s="24"/>
       <c r="B808" s="24"/>
       <c r="C808" s="24"/>
@@ -22441,7 +22468,7 @@
       <c r="W808" s="2"/>
       <c r="X808" s="2"/>
     </row>
-    <row r="809" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="809" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A809" s="24"/>
       <c r="B809" s="24"/>
       <c r="C809" s="24"/>
@@ -22467,7 +22494,7 @@
       <c r="W809" s="2"/>
       <c r="X809" s="2"/>
     </row>
-    <row r="810" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="810" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A810" s="24"/>
       <c r="B810" s="24"/>
       <c r="C810" s="24"/>
@@ -22493,7 +22520,7 @@
       <c r="W810" s="2"/>
       <c r="X810" s="2"/>
     </row>
-    <row r="811" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="811" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A811" s="24"/>
       <c r="B811" s="24"/>
       <c r="C811" s="24"/>
@@ -22519,7 +22546,7 @@
       <c r="W811" s="2"/>
       <c r="X811" s="2"/>
     </row>
-    <row r="812" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="812" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A812" s="24"/>
       <c r="B812" s="24"/>
       <c r="C812" s="24"/>
@@ -22545,7 +22572,7 @@
       <c r="W812" s="2"/>
       <c r="X812" s="2"/>
     </row>
-    <row r="813" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="813" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A813" s="24"/>
       <c r="B813" s="24"/>
       <c r="C813" s="24"/>
@@ -22571,7 +22598,7 @@
       <c r="W813" s="2"/>
       <c r="X813" s="2"/>
     </row>
-    <row r="814" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="814" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A814" s="24"/>
       <c r="B814" s="24"/>
       <c r="C814" s="24"/>
@@ -22597,7 +22624,7 @@
       <c r="W814" s="2"/>
       <c r="X814" s="2"/>
     </row>
-    <row r="815" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="815" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A815" s="24"/>
       <c r="B815" s="24"/>
       <c r="C815" s="24"/>
@@ -22623,7 +22650,7 @@
       <c r="W815" s="2"/>
       <c r="X815" s="2"/>
     </row>
-    <row r="816" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="816" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A816" s="24"/>
       <c r="B816" s="24"/>
       <c r="C816" s="24"/>
@@ -22649,7 +22676,7 @@
       <c r="W816" s="2"/>
       <c r="X816" s="2"/>
     </row>
-    <row r="817" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="817" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A817" s="24"/>
       <c r="B817" s="24"/>
       <c r="C817" s="24"/>
@@ -22675,7 +22702,7 @@
       <c r="W817" s="2"/>
       <c r="X817" s="2"/>
     </row>
-    <row r="818" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="818" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A818" s="24"/>
       <c r="B818" s="24"/>
       <c r="C818" s="24"/>
@@ -22701,7 +22728,7 @@
       <c r="W818" s="2"/>
       <c r="X818" s="2"/>
     </row>
-    <row r="819" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="819" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A819" s="24"/>
       <c r="B819" s="24"/>
       <c r="C819" s="24"/>
@@ -22727,7 +22754,7 @@
       <c r="W819" s="2"/>
       <c r="X819" s="2"/>
     </row>
-    <row r="820" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="820" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A820" s="24"/>
       <c r="B820" s="24"/>
       <c r="C820" s="24"/>
@@ -22753,7 +22780,7 @@
       <c r="W820" s="2"/>
       <c r="X820" s="2"/>
     </row>
-    <row r="821" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="821" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A821" s="24"/>
       <c r="B821" s="24"/>
       <c r="C821" s="24"/>
@@ -22779,7 +22806,7 @@
       <c r="W821" s="2"/>
       <c r="X821" s="2"/>
     </row>
-    <row r="822" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="822" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A822" s="24"/>
       <c r="B822" s="24"/>
       <c r="C822" s="24"/>
@@ -22805,7 +22832,7 @@
       <c r="W822" s="2"/>
       <c r="X822" s="2"/>
     </row>
-    <row r="823" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="823" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A823" s="24"/>
       <c r="B823" s="24"/>
       <c r="C823" s="24"/>
@@ -22831,7 +22858,7 @@
       <c r="W823" s="2"/>
       <c r="X823" s="2"/>
     </row>
-    <row r="824" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="824" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A824" s="24"/>
       <c r="B824" s="24"/>
       <c r="C824" s="24"/>
@@ -22857,7 +22884,7 @@
       <c r="W824" s="2"/>
       <c r="X824" s="2"/>
     </row>
-    <row r="825" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="825" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A825" s="24"/>
       <c r="B825" s="24"/>
       <c r="C825" s="24"/>
@@ -22883,7 +22910,7 @@
       <c r="W825" s="2"/>
       <c r="X825" s="2"/>
     </row>
-    <row r="826" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="826" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A826" s="24"/>
       <c r="B826" s="24"/>
       <c r="C826" s="24"/>
@@ -22909,7 +22936,7 @@
       <c r="W826" s="2"/>
       <c r="X826" s="2"/>
     </row>
-    <row r="827" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="827" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A827" s="24"/>
       <c r="B827" s="24"/>
       <c r="C827" s="24"/>
@@ -22935,7 +22962,7 @@
       <c r="W827" s="2"/>
       <c r="X827" s="2"/>
     </row>
-    <row r="828" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="828" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A828" s="24"/>
       <c r="B828" s="24"/>
       <c r="C828" s="24"/>
@@ -22961,7 +22988,7 @@
       <c r="W828" s="2"/>
       <c r="X828" s="2"/>
     </row>
-    <row r="829" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="829" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A829" s="24"/>
       <c r="B829" s="24"/>
       <c r="C829" s="24"/>
@@ -22987,7 +23014,7 @@
       <c r="W829" s="2"/>
       <c r="X829" s="2"/>
     </row>
-    <row r="830" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="830" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A830" s="24"/>
       <c r="B830" s="24"/>
       <c r="C830" s="24"/>
@@ -23013,7 +23040,7 @@
       <c r="W830" s="2"/>
       <c r="X830" s="2"/>
     </row>
-    <row r="831" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="831" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A831" s="24"/>
       <c r="B831" s="24"/>
       <c r="C831" s="24"/>
@@ -23039,7 +23066,7 @@
       <c r="W831" s="2"/>
       <c r="X831" s="2"/>
     </row>
-    <row r="832" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="832" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A832" s="24"/>
       <c r="B832" s="24"/>
       <c r="C832" s="24"/>
@@ -23065,7 +23092,7 @@
       <c r="W832" s="2"/>
       <c r="X832" s="2"/>
     </row>
-    <row r="833" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="833" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A833" s="24"/>
       <c r="B833" s="24"/>
       <c r="C833" s="24"/>
@@ -23091,7 +23118,7 @@
       <c r="W833" s="2"/>
       <c r="X833" s="2"/>
     </row>
-    <row r="834" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="834" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A834" s="24"/>
       <c r="B834" s="24"/>
       <c r="C834" s="24"/>
@@ -23117,7 +23144,7 @@
       <c r="W834" s="2"/>
       <c r="X834" s="2"/>
     </row>
-    <row r="835" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="835" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A835" s="24"/>
       <c r="B835" s="24"/>
       <c r="C835" s="24"/>
@@ -23143,7 +23170,7 @@
       <c r="W835" s="2"/>
       <c r="X835" s="2"/>
     </row>
-    <row r="836" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="836" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A836" s="24"/>
       <c r="B836" s="24"/>
       <c r="C836" s="24"/>
@@ -23169,7 +23196,7 @@
       <c r="W836" s="2"/>
       <c r="X836" s="2"/>
     </row>
-    <row r="837" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="837" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A837" s="24"/>
       <c r="B837" s="24"/>
       <c r="C837" s="24"/>
@@ -23195,7 +23222,7 @@
       <c r="W837" s="2"/>
       <c r="X837" s="2"/>
     </row>
-    <row r="838" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="838" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A838" s="24"/>
       <c r="B838" s="24"/>
       <c r="C838" s="24"/>
@@ -23221,7 +23248,7 @@
       <c r="W838" s="2"/>
       <c r="X838" s="2"/>
     </row>
-    <row r="839" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="839" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A839" s="24"/>
       <c r="B839" s="24"/>
       <c r="C839" s="24"/>
@@ -23247,7 +23274,7 @@
       <c r="W839" s="2"/>
       <c r="X839" s="2"/>
     </row>
-    <row r="840" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="840" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A840" s="24"/>
       <c r="B840" s="24"/>
       <c r="C840" s="24"/>
@@ -23273,7 +23300,7 @@
       <c r="W840" s="2"/>
       <c r="X840" s="2"/>
     </row>
-    <row r="841" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="841" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A841" s="24"/>
       <c r="B841" s="24"/>
       <c r="C841" s="24"/>
@@ -23299,7 +23326,7 @@
       <c r="W841" s="2"/>
       <c r="X841" s="2"/>
     </row>
-    <row r="842" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="842" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A842" s="24"/>
       <c r="B842" s="24"/>
       <c r="C842" s="24"/>
@@ -23325,7 +23352,7 @@
       <c r="W842" s="2"/>
       <c r="X842" s="2"/>
     </row>
-    <row r="843" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="843" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A843" s="24"/>
       <c r="B843" s="24"/>
       <c r="C843" s="24"/>
@@ -23351,7 +23378,7 @@
       <c r="W843" s="2"/>
       <c r="X843" s="2"/>
     </row>
-    <row r="844" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="844" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A844" s="24"/>
       <c r="B844" s="24"/>
       <c r="C844" s="24"/>
@@ -23377,7 +23404,7 @@
       <c r="W844" s="2"/>
       <c r="X844" s="2"/>
     </row>
-    <row r="845" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="845" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A845" s="24"/>
       <c r="B845" s="24"/>
       <c r="C845" s="24"/>
@@ -23403,7 +23430,7 @@
       <c r="W845" s="2"/>
       <c r="X845" s="2"/>
     </row>
-    <row r="846" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="846" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A846" s="24"/>
       <c r="B846" s="24"/>
       <c r="C846" s="24"/>
@@ -23429,7 +23456,7 @@
       <c r="W846" s="2"/>
       <c r="X846" s="2"/>
     </row>
-    <row r="847" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="847" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A847" s="24"/>
       <c r="B847" s="24"/>
       <c r="C847" s="24"/>
@@ -23455,7 +23482,7 @@
       <c r="W847" s="2"/>
       <c r="X847" s="2"/>
     </row>
-    <row r="848" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="848" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A848" s="24"/>
       <c r="B848" s="24"/>
       <c r="C848" s="24"/>
@@ -23481,7 +23508,7 @@
       <c r="W848" s="2"/>
       <c r="X848" s="2"/>
     </row>
-    <row r="849" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="849" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A849" s="24"/>
       <c r="B849" s="24"/>
       <c r="C849" s="24"/>
@@ -23507,7 +23534,7 @@
       <c r="W849" s="2"/>
       <c r="X849" s="2"/>
     </row>
-    <row r="850" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="850" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A850" s="24"/>
       <c r="B850" s="24"/>
       <c r="C850" s="24"/>
@@ -23533,7 +23560,7 @@
       <c r="W850" s="2"/>
       <c r="X850" s="2"/>
     </row>
-    <row r="851" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="851" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A851" s="24"/>
       <c r="B851" s="24"/>
       <c r="C851" s="24"/>
@@ -23559,7 +23586,7 @@
       <c r="W851" s="2"/>
       <c r="X851" s="2"/>
     </row>
-    <row r="852" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="852" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A852" s="24"/>
       <c r="B852" s="24"/>
       <c r="C852" s="24"/>
@@ -23585,7 +23612,7 @@
       <c r="W852" s="2"/>
       <c r="X852" s="2"/>
     </row>
-    <row r="853" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="853" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A853" s="24"/>
       <c r="B853" s="24"/>
       <c r="C853" s="24"/>
@@ -23611,7 +23638,7 @@
       <c r="W853" s="2"/>
       <c r="X853" s="2"/>
     </row>
-    <row r="854" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="854" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A854" s="24"/>
       <c r="B854" s="24"/>
       <c r="C854" s="24"/>
@@ -23637,7 +23664,7 @@
       <c r="W854" s="2"/>
       <c r="X854" s="2"/>
     </row>
-    <row r="855" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="855" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A855" s="24"/>
       <c r="B855" s="24"/>
       <c r="C855" s="24"/>
@@ -23663,7 +23690,7 @@
       <c r="W855" s="2"/>
       <c r="X855" s="2"/>
     </row>
-    <row r="856" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="856" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A856" s="24"/>
       <c r="B856" s="24"/>
       <c r="C856" s="24"/>
@@ -23689,7 +23716,7 @@
       <c r="W856" s="2"/>
       <c r="X856" s="2"/>
     </row>
-    <row r="857" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="857" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A857" s="24"/>
       <c r="B857" s="24"/>
       <c r="C857" s="24"/>
@@ -23715,7 +23742,7 @@
       <c r="W857" s="2"/>
       <c r="X857" s="2"/>
     </row>
-    <row r="858" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="858" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A858" s="24"/>
       <c r="B858" s="24"/>
       <c r="C858" s="24"/>
@@ -23741,7 +23768,7 @@
       <c r="W858" s="2"/>
       <c r="X858" s="2"/>
     </row>
-    <row r="859" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="859" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A859" s="24"/>
       <c r="B859" s="24"/>
       <c r="C859" s="24"/>
@@ -23767,7 +23794,7 @@
       <c r="W859" s="2"/>
       <c r="X859" s="2"/>
     </row>
-    <row r="860" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="860" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A860" s="24"/>
       <c r="B860" s="24"/>
       <c r="C860" s="24"/>
@@ -23793,7 +23820,7 @@
       <c r="W860" s="2"/>
       <c r="X860" s="2"/>
     </row>
-    <row r="861" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="861" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A861" s="24"/>
       <c r="B861" s="24"/>
       <c r="C861" s="24"/>
@@ -23819,7 +23846,7 @@
       <c r="W861" s="2"/>
       <c r="X861" s="2"/>
     </row>
-    <row r="862" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="862" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A862" s="24"/>
       <c r="B862" s="24"/>
       <c r="C862" s="24"/>
@@ -23845,7 +23872,7 @@
       <c r="W862" s="2"/>
       <c r="X862" s="2"/>
     </row>
-    <row r="863" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="863" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A863" s="24"/>
       <c r="B863" s="24"/>
       <c r="C863" s="24"/>
@@ -23871,7 +23898,7 @@
       <c r="W863" s="2"/>
       <c r="X863" s="2"/>
     </row>
-    <row r="864" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="864" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A864" s="24"/>
       <c r="B864" s="24"/>
       <c r="C864" s="24"/>
@@ -23897,7 +23924,7 @@
       <c r="W864" s="2"/>
       <c r="X864" s="2"/>
     </row>
-    <row r="865" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="865" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A865" s="24"/>
       <c r="B865" s="24"/>
       <c r="C865" s="24"/>
@@ -23923,7 +23950,7 @@
       <c r="W865" s="2"/>
       <c r="X865" s="2"/>
     </row>
-    <row r="866" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="866" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A866" s="24"/>
       <c r="B866" s="24"/>
       <c r="C866" s="24"/>
@@ -23949,7 +23976,7 @@
       <c r="W866" s="2"/>
       <c r="X866" s="2"/>
     </row>
-    <row r="867" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="867" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A867" s="24"/>
       <c r="B867" s="24"/>
       <c r="C867" s="24"/>
@@ -23975,7 +24002,7 @@
       <c r="W867" s="2"/>
       <c r="X867" s="2"/>
     </row>
-    <row r="868" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="868" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A868" s="24"/>
       <c r="B868" s="24"/>
       <c r="C868" s="24"/>
@@ -24001,7 +24028,7 @@
       <c r="W868" s="2"/>
       <c r="X868" s="2"/>
     </row>
-    <row r="869" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="869" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A869" s="24"/>
       <c r="B869" s="24"/>
       <c r="C869" s="24"/>
@@ -24027,7 +24054,7 @@
       <c r="W869" s="2"/>
       <c r="X869" s="2"/>
     </row>
-    <row r="870" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="870" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A870" s="24"/>
       <c r="B870" s="24"/>
       <c r="C870" s="24"/>
@@ -24053,7 +24080,7 @@
       <c r="W870" s="2"/>
       <c r="X870" s="2"/>
     </row>
-    <row r="871" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="871" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A871" s="24"/>
       <c r="B871" s="24"/>
       <c r="C871" s="24"/>
@@ -24079,7 +24106,7 @@
       <c r="W871" s="2"/>
       <c r="X871" s="2"/>
     </row>
-    <row r="872" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="872" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A872" s="24"/>
       <c r="B872" s="24"/>
       <c r="C872" s="24"/>
@@ -24105,7 +24132,7 @@
       <c r="W872" s="2"/>
       <c r="X872" s="2"/>
     </row>
-    <row r="873" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="873" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A873" s="24"/>
       <c r="B873" s="24"/>
       <c r="C873" s="24"/>
@@ -24131,7 +24158,7 @@
       <c r="W873" s="2"/>
       <c r="X873" s="2"/>
     </row>
-    <row r="874" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="874" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A874" s="24"/>
       <c r="B874" s="24"/>
       <c r="C874" s="24"/>
@@ -24157,7 +24184,7 @@
       <c r="W874" s="2"/>
       <c r="X874" s="2"/>
     </row>
-    <row r="875" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="875" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A875" s="24"/>
       <c r="B875" s="24"/>
       <c r="C875" s="24"/>
@@ -24183,7 +24210,7 @@
       <c r="W875" s="2"/>
       <c r="X875" s="2"/>
     </row>
-    <row r="876" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="876" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A876" s="24"/>
       <c r="B876" s="24"/>
       <c r="C876" s="24"/>
@@ -24209,7 +24236,7 @@
       <c r="W876" s="2"/>
       <c r="X876" s="2"/>
     </row>
-    <row r="877" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="877" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A877" s="24"/>
       <c r="B877" s="24"/>
       <c r="C877" s="24"/>
@@ -24235,7 +24262,7 @@
       <c r="W877" s="2"/>
       <c r="X877" s="2"/>
     </row>
-    <row r="878" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="878" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A878" s="24"/>
       <c r="B878" s="24"/>
       <c r="C878" s="24"/>
@@ -24261,7 +24288,7 @@
       <c r="W878" s="2"/>
       <c r="X878" s="2"/>
     </row>
-    <row r="879" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="879" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A879" s="24"/>
       <c r="B879" s="24"/>
       <c r="C879" s="24"/>
@@ -24287,7 +24314,7 @@
       <c r="W879" s="2"/>
       <c r="X879" s="2"/>
     </row>
-    <row r="880" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="880" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A880" s="24"/>
       <c r="B880" s="24"/>
       <c r="C880" s="24"/>
@@ -24313,7 +24340,7 @@
       <c r="W880" s="2"/>
       <c r="X880" s="2"/>
     </row>
-    <row r="881" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="881" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A881" s="24"/>
       <c r="B881" s="24"/>
       <c r="C881" s="24"/>
@@ -24339,7 +24366,7 @@
       <c r="W881" s="2"/>
       <c r="X881" s="2"/>
     </row>
-    <row r="882" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="882" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A882" s="24"/>
       <c r="B882" s="24"/>
       <c r="C882" s="24"/>
@@ -24365,7 +24392,7 @@
       <c r="W882" s="2"/>
       <c r="X882" s="2"/>
     </row>
-    <row r="883" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="883" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A883" s="24"/>
       <c r="B883" s="24"/>
       <c r="C883" s="24"/>
@@ -24391,7 +24418,7 @@
       <c r="W883" s="2"/>
       <c r="X883" s="2"/>
     </row>
-    <row r="884" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="884" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A884" s="24"/>
       <c r="B884" s="24"/>
       <c r="C884" s="24"/>
@@ -24417,7 +24444,7 @@
       <c r="W884" s="2"/>
       <c r="X884" s="2"/>
     </row>
-    <row r="885" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="885" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A885" s="24"/>
       <c r="B885" s="24"/>
       <c r="C885" s="24"/>
@@ -24443,7 +24470,7 @@
       <c r="W885" s="2"/>
       <c r="X885" s="2"/>
     </row>
-    <row r="886" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="886" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A886" s="24"/>
       <c r="B886" s="24"/>
       <c r="C886" s="24"/>
@@ -24469,7 +24496,7 @@
       <c r="W886" s="2"/>
       <c r="X886" s="2"/>
     </row>
-    <row r="887" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="887" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A887" s="24"/>
       <c r="B887" s="24"/>
       <c r="C887" s="24"/>
@@ -24495,7 +24522,7 @@
       <c r="W887" s="2"/>
       <c r="X887" s="2"/>
     </row>
-    <row r="888" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="888" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A888" s="24"/>
       <c r="B888" s="24"/>
       <c r="C888" s="24"/>
@@ -24521,7 +24548,7 @@
       <c r="W888" s="2"/>
       <c r="X888" s="2"/>
     </row>
-    <row r="889" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="889" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A889" s="24"/>
       <c r="B889" s="24"/>
       <c r="C889" s="24"/>
@@ -24547,7 +24574,7 @@
       <c r="W889" s="2"/>
       <c r="X889" s="2"/>
     </row>
-    <row r="890" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="890" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A890" s="24"/>
       <c r="B890" s="24"/>
       <c r="C890" s="24"/>
@@ -24573,7 +24600,7 @@
       <c r="W890" s="2"/>
       <c r="X890" s="2"/>
     </row>
-    <row r="891" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="891" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A891" s="24"/>
       <c r="B891" s="24"/>
       <c r="C891" s="24"/>
@@ -24599,7 +24626,7 @@
       <c r="W891" s="2"/>
       <c r="X891" s="2"/>
     </row>
-    <row r="892" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="892" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A892" s="24"/>
       <c r="B892" s="24"/>
       <c r="C892" s="24"/>
@@ -24625,7 +24652,7 @@
       <c r="W892" s="2"/>
       <c r="X892" s="2"/>
     </row>
-    <row r="893" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="893" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A893" s="24"/>
       <c r="B893" s="24"/>
       <c r="C893" s="24"/>
@@ -24651,7 +24678,7 @@
       <c r="W893" s="2"/>
       <c r="X893" s="2"/>
     </row>
-    <row r="894" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="894" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A894" s="24"/>
       <c r="B894" s="24"/>
       <c r="C894" s="24"/>
@@ -24677,7 +24704,7 @@
       <c r="W894" s="2"/>
       <c r="X894" s="2"/>
     </row>
-    <row r="895" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="895" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A895" s="24"/>
       <c r="B895" s="24"/>
       <c r="C895" s="24"/>
@@ -24703,7 +24730,7 @@
       <c r="W895" s="2"/>
       <c r="X895" s="2"/>
     </row>
-    <row r="896" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="896" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A896" s="24"/>
       <c r="B896" s="24"/>
       <c r="C896" s="24"/>
@@ -24729,7 +24756,7 @@
       <c r="W896" s="2"/>
       <c r="X896" s="2"/>
     </row>
-    <row r="897" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="897" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A897" s="24"/>
       <c r="B897" s="24"/>
       <c r="C897" s="24"/>
@@ -24755,7 +24782,7 @@
       <c r="W897" s="2"/>
       <c r="X897" s="2"/>
     </row>
-    <row r="898" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="898" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A898" s="24"/>
       <c r="B898" s="24"/>
       <c r="C898" s="24"/>
@@ -24781,7 +24808,7 @@
       <c r="W898" s="2"/>
       <c r="X898" s="2"/>
     </row>
-    <row r="899" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="899" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A899" s="24"/>
       <c r="B899" s="24"/>
       <c r="C899" s="24"/>
@@ -24807,7 +24834,7 @@
       <c r="W899" s="2"/>
       <c r="X899" s="2"/>
     </row>
-    <row r="900" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="900" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A900" s="24"/>
       <c r="B900" s="24"/>
       <c r="C900" s="24"/>
@@ -24833,7 +24860,7 @@
       <c r="W900" s="2"/>
       <c r="X900" s="2"/>
     </row>
-    <row r="901" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="901" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A901" s="24"/>
       <c r="B901" s="24"/>
       <c r="C901" s="24"/>
@@ -24859,7 +24886,7 @@
       <c r="W901" s="2"/>
       <c r="X901" s="2"/>
     </row>
-    <row r="902" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="902" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A902" s="24"/>
       <c r="B902" s="24"/>
       <c r="C902" s="24"/>
@@ -24885,7 +24912,7 @@
       <c r="W902" s="2"/>
       <c r="X902" s="2"/>
     </row>
-    <row r="903" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="903" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A903" s="24"/>
       <c r="B903" s="24"/>
       <c r="C903" s="24"/>
@@ -24911,7 +24938,7 @@
       <c r="W903" s="2"/>
       <c r="X903" s="2"/>
     </row>
-    <row r="904" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="904" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A904" s="24"/>
       <c r="B904" s="24"/>
       <c r="C904" s="24"/>
@@ -24937,7 +24964,7 @@
       <c r="W904" s="2"/>
       <c r="X904" s="2"/>
     </row>
-    <row r="905" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="905" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A905" s="24"/>
       <c r="B905" s="24"/>
       <c r="C905" s="24"/>
@@ -24963,7 +24990,7 @@
       <c r="W905" s="2"/>
       <c r="X905" s="2"/>
     </row>
-    <row r="906" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="906" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A906" s="24"/>
       <c r="B906" s="24"/>
       <c r="C906" s="24"/>
@@ -24989,7 +25016,7 @@
       <c r="W906" s="2"/>
       <c r="X906" s="2"/>
     </row>
-    <row r="907" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="907" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A907" s="24"/>
       <c r="B907" s="24"/>
       <c r="C907" s="24"/>
@@ -25015,7 +25042,7 @@
       <c r="W907" s="2"/>
       <c r="X907" s="2"/>
     </row>
-    <row r="908" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="908" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A908" s="24"/>
       <c r="B908" s="24"/>
       <c r="C908" s="24"/>
@@ -25041,7 +25068,7 @@
       <c r="W908" s="2"/>
       <c r="X908" s="2"/>
     </row>
-    <row r="909" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="909" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A909" s="24"/>
       <c r="B909" s="24"/>
       <c r="C909" s="24"/>
@@ -25067,7 +25094,7 @@
       <c r="W909" s="2"/>
       <c r="X909" s="2"/>
     </row>
-    <row r="910" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="910" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A910" s="24"/>
       <c r="B910" s="24"/>
       <c r="C910" s="24"/>
@@ -25093,7 +25120,7 @@
       <c r="W910" s="2"/>
       <c r="X910" s="2"/>
     </row>
-    <row r="911" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="911" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A911" s="24"/>
       <c r="B911" s="24"/>
       <c r="C911" s="24"/>
@@ -25119,7 +25146,7 @@
       <c r="W911" s="2"/>
       <c r="X911" s="2"/>
     </row>
-    <row r="912" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="912" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A912" s="24"/>
       <c r="B912" s="24"/>
       <c r="C912" s="24"/>
@@ -25145,7 +25172,7 @@
       <c r="W912" s="2"/>
       <c r="X912" s="2"/>
     </row>
-    <row r="913" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="913" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A913" s="24"/>
       <c r="B913" s="24"/>
       <c r="C913" s="24"/>
@@ -25171,7 +25198,7 @@
       <c r="W913" s="2"/>
       <c r="X913" s="2"/>
     </row>
-    <row r="914" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="914" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A914" s="24"/>
       <c r="B914" s="24"/>
       <c r="C914" s="24"/>
@@ -25197,7 +25224,7 @@
       <c r="W914" s="2"/>
       <c r="X914" s="2"/>
     </row>
-    <row r="915" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="915" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A915" s="24"/>
       <c r="B915" s="24"/>
       <c r="C915" s="24"/>
@@ -25223,7 +25250,7 @@
       <c r="W915" s="2"/>
       <c r="X915" s="2"/>
     </row>
-    <row r="916" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="916" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A916" s="24"/>
       <c r="B916" s="24"/>
       <c r="C916" s="24"/>
@@ -25249,7 +25276,7 @@
       <c r="W916" s="2"/>
       <c r="X916" s="2"/>
     </row>
-    <row r="917" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="917" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A917" s="24"/>
       <c r="B917" s="24"/>
       <c r="C917" s="24"/>
@@ -25275,7 +25302,7 @@
       <c r="W917" s="2"/>
       <c r="X917" s="2"/>
     </row>
-    <row r="918" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="918" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A918" s="24"/>
       <c r="B918" s="24"/>
       <c r="C918" s="24"/>
@@ -25301,7 +25328,7 @@
       <c r="W918" s="2"/>
       <c r="X918" s="2"/>
     </row>
-    <row r="919" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="919" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A919" s="24"/>
       <c r="B919" s="24"/>
       <c r="C919" s="24"/>
@@ -25327,7 +25354,7 @@
       <c r="W919" s="2"/>
       <c r="X919" s="2"/>
     </row>
-    <row r="920" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="920" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A920" s="24"/>
       <c r="B920" s="24"/>
       <c r="C920" s="24"/>
@@ -25353,7 +25380,7 @@
       <c r="W920" s="2"/>
       <c r="X920" s="2"/>
     </row>
-    <row r="921" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="921" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A921" s="24"/>
       <c r="B921" s="24"/>
       <c r="C921" s="24"/>
@@ -25379,7 +25406,7 @@
       <c r="W921" s="2"/>
       <c r="X921" s="2"/>
     </row>
-    <row r="922" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="922" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A922" s="24"/>
       <c r="B922" s="24"/>
       <c r="C922" s="24"/>
@@ -25405,7 +25432,7 @@
       <c r="W922" s="2"/>
       <c r="X922" s="2"/>
     </row>
-    <row r="923" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="923" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A923" s="24"/>
       <c r="B923" s="24"/>
       <c r="C923" s="24"/>
@@ -25431,7 +25458,7 @@
       <c r="W923" s="2"/>
       <c r="X923" s="2"/>
     </row>
-    <row r="924" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="924" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A924" s="24"/>
       <c r="B924" s="24"/>
       <c r="C924" s="24"/>
@@ -25457,7 +25484,7 @@
       <c r="W924" s="2"/>
       <c r="X924" s="2"/>
     </row>
-    <row r="925" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="925" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A925" s="24"/>
       <c r="B925" s="24"/>
       <c r="C925" s="24"/>
@@ -25483,7 +25510,7 @@
       <c r="W925" s="2"/>
       <c r="X925" s="2"/>
     </row>
-    <row r="926" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="926" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A926" s="24"/>
       <c r="B926" s="24"/>
       <c r="C926" s="24"/>
@@ -25509,7 +25536,7 @@
       <c r="W926" s="2"/>
       <c r="X926" s="2"/>
     </row>
-    <row r="927" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="927" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A927" s="24"/>
       <c r="B927" s="24"/>
       <c r="C927" s="24"/>
@@ -25535,7 +25562,7 @@
       <c r="W927" s="2"/>
       <c r="X927" s="2"/>
     </row>
-    <row r="928" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="928" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A928" s="24"/>
       <c r="B928" s="24"/>
       <c r="C928" s="24"/>
@@ -25561,7 +25588,7 @@
       <c r="W928" s="2"/>
       <c r="X928" s="2"/>
     </row>
-    <row r="929" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="929" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A929" s="24"/>
       <c r="B929" s="24"/>
       <c r="C929" s="24"/>
@@ -25587,7 +25614,7 @@
       <c r="W929" s="2"/>
       <c r="X929" s="2"/>
     </row>
-    <row r="930" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="930" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A930" s="24"/>
       <c r="B930" s="24"/>
       <c r="C930" s="24"/>
@@ -25613,7 +25640,7 @@
       <c r="W930" s="2"/>
       <c r="X930" s="2"/>
     </row>
-    <row r="931" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="931" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A931" s="24"/>
       <c r="B931" s="24"/>
       <c r="C931" s="24"/>
@@ -25639,7 +25666,7 @@
       <c r="W931" s="2"/>
       <c r="X931" s="2"/>
     </row>
-    <row r="932" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="932" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A932" s="24"/>
       <c r="B932" s="24"/>
       <c r="C932" s="24"/>
@@ -25665,7 +25692,7 @@
       <c r="W932" s="2"/>
       <c r="X932" s="2"/>
     </row>
-    <row r="933" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="933" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A933" s="24"/>
       <c r="B933" s="24"/>
       <c r="C933" s="24"/>
@@ -25691,7 +25718,7 @@
       <c r="W933" s="2"/>
       <c r="X933" s="2"/>
     </row>
-    <row r="934" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="934" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A934" s="24"/>
       <c r="B934" s="24"/>
       <c r="C934" s="24"/>
@@ -25717,7 +25744,7 @@
       <c r="W934" s="2"/>
       <c r="X934" s="2"/>
     </row>
-    <row r="935" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="935" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A935" s="24"/>
       <c r="B935" s="24"/>
       <c r="C935" s="24"/>
@@ -25743,7 +25770,7 @@
       <c r="W935" s="2"/>
       <c r="X935" s="2"/>
     </row>
-    <row r="936" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="936" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A936" s="24"/>
       <c r="B936" s="24"/>
       <c r="C936" s="24"/>
@@ -25769,7 +25796,7 @@
       <c r="W936" s="2"/>
       <c r="X936" s="2"/>
     </row>
-    <row r="937" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="937" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A937" s="24"/>
       <c r="B937" s="24"/>
       <c r="C937" s="24"/>
@@ -25795,7 +25822,7 @@
       <c r="W937" s="2"/>
       <c r="X937" s="2"/>
     </row>
-    <row r="938" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="938" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A938" s="24"/>
       <c r="B938" s="24"/>
       <c r="C938" s="24"/>
@@ -25821,7 +25848,7 @@
       <c r="W938" s="2"/>
       <c r="X938" s="2"/>
     </row>
-    <row r="939" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="939" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A939" s="24"/>
       <c r="B939" s="24"/>
       <c r="C939" s="24"/>
@@ -25847,7 +25874,7 @@
       <c r="W939" s="2"/>
       <c r="X939" s="2"/>
     </row>
-    <row r="940" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="940" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A940" s="24"/>
       <c r="B940" s="24"/>
       <c r="C940" s="24"/>
@@ -25873,7 +25900,7 @@
       <c r="W940" s="2"/>
       <c r="X940" s="2"/>
     </row>
-    <row r="941" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="941" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A941" s="24"/>
       <c r="B941" s="24"/>
       <c r="C941" s="24"/>
@@ -25899,7 +25926,7 @@
       <c r="W941" s="2"/>
       <c r="X941" s="2"/>
     </row>
-    <row r="942" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="942" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A942" s="24"/>
       <c r="B942" s="24"/>
       <c r="C942" s="24"/>
@@ -25925,7 +25952,7 @@
       <c r="W942" s="2"/>
       <c r="X942" s="2"/>
     </row>
-    <row r="943" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="943" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A943" s="24"/>
       <c r="B943" s="24"/>
       <c r="C943" s="24"/>
@@ -25951,7 +25978,7 @@
       <c r="W943" s="2"/>
       <c r="X943" s="2"/>
     </row>
-    <row r="944" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="944" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A944" s="24"/>
       <c r="B944" s="24"/>
       <c r="C944" s="24"/>
@@ -25977,7 +26004,7 @@
       <c r="W944" s="2"/>
       <c r="X944" s="2"/>
     </row>
-    <row r="945" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="945" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A945" s="24"/>
       <c r="B945" s="24"/>
       <c r="C945" s="24"/>
@@ -26003,7 +26030,7 @@
       <c r="W945" s="2"/>
       <c r="X945" s="2"/>
     </row>
-    <row r="946" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="946" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A946" s="24"/>
       <c r="B946" s="24"/>
       <c r="C946" s="24"/>
@@ -26029,7 +26056,7 @@
       <c r="W946" s="2"/>
       <c r="X946" s="2"/>
     </row>
-    <row r="947" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="947" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A947" s="24"/>
       <c r="B947" s="24"/>
       <c r="C947" s="24"/>
@@ -26055,7 +26082,7 @@
       <c r="W947" s="2"/>
       <c r="X947" s="2"/>
     </row>
-    <row r="948" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="948" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A948" s="24"/>
       <c r="B948" s="24"/>
       <c r="C948" s="24"/>
@@ -26081,7 +26108,7 @@
       <c r="W948" s="2"/>
       <c r="X948" s="2"/>
     </row>
-    <row r="949" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="949" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A949" s="24"/>
       <c r="B949" s="24"/>
       <c r="C949" s="24"/>
@@ -26107,7 +26134,7 @@
       <c r="W949" s="2"/>
       <c r="X949" s="2"/>
     </row>
-    <row r="950" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="950" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A950" s="24"/>
       <c r="B950" s="24"/>
       <c r="C950" s="24"/>
@@ -26133,7 +26160,7 @@
       <c r="W950" s="2"/>
       <c r="X950" s="2"/>
     </row>
-    <row r="951" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="951" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A951" s="24"/>
       <c r="B951" s="24"/>
       <c r="C951" s="24"/>
@@ -26159,7 +26186,7 @@
       <c r="W951" s="2"/>
       <c r="X951" s="2"/>
     </row>
-    <row r="952" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="952" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A952" s="24"/>
       <c r="B952" s="24"/>
       <c r="C952" s="24"/>
@@ -26185,7 +26212,7 @@
       <c r="W952" s="2"/>
       <c r="X952" s="2"/>
     </row>
-    <row r="953" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="953" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A953" s="24"/>
       <c r="B953" s="24"/>
       <c r="C953" s="24"/>
@@ -26211,7 +26238,7 @@
       <c r="W953" s="2"/>
       <c r="X953" s="2"/>
     </row>
-    <row r="954" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="954" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A954" s="24"/>
       <c r="B954" s="24"/>
       <c r="C954" s="24"/>
@@ -26237,7 +26264,7 @@
       <c r="W954" s="2"/>
       <c r="X954" s="2"/>
     </row>
-    <row r="955" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="955" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A955" s="24"/>
       <c r="B955" s="24"/>
       <c r="C955" s="24"/>
@@ -26263,7 +26290,7 @@
       <c r="W955" s="2"/>
       <c r="X955" s="2"/>
     </row>
-    <row r="956" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="956" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A956" s="24"/>
       <c r="B956" s="24"/>
       <c r="C956" s="24"/>
@@ -26289,7 +26316,7 @@
       <c r="W956" s="2"/>
       <c r="X956" s="2"/>
     </row>
-    <row r="957" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="957" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A957" s="24"/>
       <c r="B957" s="24"/>
       <c r="C957" s="24"/>
@@ -26315,7 +26342,7 @@
       <c r="W957" s="2"/>
       <c r="X957" s="2"/>
     </row>
-    <row r="958" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="958" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A958" s="24"/>
       <c r="B958" s="24"/>
       <c r="C958" s="24"/>
@@ -26341,7 +26368,7 @@
       <c r="W958" s="2"/>
       <c r="X958" s="2"/>
     </row>
-    <row r="959" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="959" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A959" s="24"/>
       <c r="B959" s="24"/>
       <c r="C959" s="24"/>
@@ -26367,7 +26394,7 @@
       <c r="W959" s="2"/>
       <c r="X959" s="2"/>
     </row>
-    <row r="960" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="960" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A960" s="24"/>
       <c r="B960" s="24"/>
       <c r="C960" s="24"/>
@@ -26393,7 +26420,7 @@
       <c r="W960" s="2"/>
       <c r="X960" s="2"/>
     </row>
-    <row r="961" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="961" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A961" s="24"/>
       <c r="B961" s="24"/>
       <c r="C961" s="24"/>
@@ -26419,7 +26446,7 @@
       <c r="W961" s="2"/>
       <c r="X961" s="2"/>
     </row>
-    <row r="962" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="962" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A962" s="24"/>
       <c r="B962" s="24"/>
       <c r="C962" s="24"/>
@@ -26445,7 +26472,7 @@
       <c r="W962" s="2"/>
       <c r="X962" s="2"/>
     </row>
-    <row r="963" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="963" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A963" s="24"/>
       <c r="B963" s="24"/>
       <c r="C963" s="24"/>
@@ -26471,7 +26498,7 @@
       <c r="W963" s="2"/>
       <c r="X963" s="2"/>
     </row>
-    <row r="964" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="964" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A964" s="24"/>
       <c r="B964" s="24"/>
       <c r="C964" s="24"/>
@@ -26497,7 +26524,7 @@
       <c r="W964" s="2"/>
       <c r="X964" s="2"/>
     </row>
-    <row r="965" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="965" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A965" s="24"/>
       <c r="B965" s="24"/>
       <c r="C965" s="24"/>
@@ -26523,7 +26550,7 @@
       <c r="W965" s="2"/>
       <c r="X965" s="2"/>
     </row>
-    <row r="966" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="966" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A966" s="24"/>
       <c r="B966" s="24"/>
       <c r="C966" s="24"/>
@@ -26549,7 +26576,7 @@
       <c r="W966" s="2"/>
       <c r="X966" s="2"/>
     </row>
-    <row r="967" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="967" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A967" s="24"/>
       <c r="B967" s="24"/>
       <c r="C967" s="24"/>
@@ -26575,7 +26602,7 @@
       <c r="W967" s="2"/>
       <c r="X967" s="2"/>
     </row>
-    <row r="968" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="968" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A968" s="24"/>
       <c r="B968" s="24"/>
       <c r="C968" s="24"/>
@@ -26601,7 +26628,7 @@
       <c r="W968" s="2"/>
       <c r="X968" s="2"/>
     </row>
-    <row r="969" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="969" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A969" s="24"/>
       <c r="B969" s="24"/>
       <c r="C969" s="24"/>
@@ -26627,7 +26654,7 @@
       <c r="W969" s="2"/>
       <c r="X969" s="2"/>
     </row>
-    <row r="970" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="970" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A970" s="24"/>
       <c r="B970" s="24"/>
       <c r="C970" s="24"/>
@@ -26653,7 +26680,7 @@
       <c r="W970" s="2"/>
       <c r="X970" s="2"/>
     </row>
-    <row r="971" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="971" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A971" s="24"/>
       <c r="B971" s="24"/>
       <c r="C971" s="24"/>
@@ -26679,7 +26706,7 @@
       <c r="W971" s="2"/>
       <c r="X971" s="2"/>
     </row>
-    <row r="972" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="972" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A972" s="24"/>
       <c r="B972" s="24"/>
       <c r="C972" s="24"/>
@@ -26705,7 +26732,7 @@
       <c r="W972" s="2"/>
       <c r="X972" s="2"/>
     </row>
-    <row r="973" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="973" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A973" s="24"/>
       <c r="B973" s="24"/>
       <c r="C973" s="24"/>
@@ -26731,7 +26758,7 @@
       <c r="W973" s="2"/>
       <c r="X973" s="2"/>
     </row>
-    <row r="974" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="974" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A974" s="24"/>
       <c r="B974" s="24"/>
       <c r="C974" s="24"/>
@@ -26757,7 +26784,7 @@
       <c r="W974" s="2"/>
       <c r="X974" s="2"/>
     </row>
-    <row r="975" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="975" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A975" s="24"/>
       <c r="B975" s="24"/>
       <c r="C975" s="24"/>
@@ -26783,7 +26810,7 @@
       <c r="W975" s="2"/>
       <c r="X975" s="2"/>
     </row>
-    <row r="976" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="976" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A976" s="24"/>
       <c r="B976" s="24"/>
       <c r="C976" s="24"/>
@@ -26809,7 +26836,7 @@
       <c r="W976" s="2"/>
       <c r="X976" s="2"/>
     </row>
-    <row r="977" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="977" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A977" s="24"/>
       <c r="B977" s="24"/>
       <c r="C977" s="24"/>
@@ -26835,7 +26862,7 @@
       <c r="W977" s="2"/>
       <c r="X977" s="2"/>
     </row>
-    <row r="978" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="978" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A978" s="24"/>
       <c r="B978" s="24"/>
       <c r="C978" s="24"/>
@@ -26861,7 +26888,7 @@
       <c r="W978" s="2"/>
       <c r="X978" s="2"/>
     </row>
-    <row r="979" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="979" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A979" s="24"/>
       <c r="B979" s="24"/>
       <c r="C979" s="24"/>
@@ -26887,7 +26914,7 @@
       <c r="W979" s="2"/>
       <c r="X979" s="2"/>
     </row>
-    <row r="980" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="980" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A980" s="24"/>
       <c r="B980" s="24"/>
       <c r="C980" s="24"/>
@@ -26913,7 +26940,7 @@
       <c r="W980" s="2"/>
       <c r="X980" s="2"/>
     </row>
-    <row r="981" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="981" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A981" s="24"/>
       <c r="B981" s="24"/>
       <c r="C981" s="24"/>
@@ -26939,7 +26966,7 @@
       <c r="W981" s="2"/>
       <c r="X981" s="2"/>
     </row>
-    <row r="982" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="982" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A982" s="24"/>
       <c r="B982" s="24"/>
       <c r="C982" s="24"/>
@@ -26965,7 +26992,7 @@
       <c r="W982" s="2"/>
       <c r="X982" s="2"/>
     </row>
-    <row r="983" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="983" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A983" s="24"/>
       <c r="B983" s="24"/>
       <c r="C983" s="24"/>
@@ -26991,7 +27018,7 @@
       <c r="W983" s="2"/>
       <c r="X983" s="2"/>
     </row>
-    <row r="984" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="984" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A984" s="24"/>
       <c r="B984" s="24"/>
       <c r="C984" s="24"/>
@@ -27017,7 +27044,7 @@
       <c r="W984" s="2"/>
       <c r="X984" s="2"/>
     </row>
-    <row r="985" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="985" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A985" s="24"/>
       <c r="B985" s="24"/>
       <c r="C985" s="24"/>
@@ -27043,7 +27070,7 @@
       <c r="W985" s="2"/>
       <c r="X985" s="2"/>
     </row>
-    <row r="986" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="986" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A986" s="24"/>
       <c r="B986" s="24"/>
       <c r="C986" s="24"/>
@@ -27069,7 +27096,7 @@
       <c r="W986" s="2"/>
       <c r="X986" s="2"/>
     </row>
-    <row r="987" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="987" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A987" s="24"/>
       <c r="B987" s="24"/>
       <c r="C987" s="24"/>
@@ -27095,7 +27122,7 @@
       <c r="W987" s="2"/>
       <c r="X987" s="2"/>
     </row>
-    <row r="988" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="988" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A988" s="24"/>
       <c r="B988" s="24"/>
       <c r="C988" s="24"/>
@@ -27121,7 +27148,7 @@
       <c r="W988" s="2"/>
       <c r="X988" s="2"/>
     </row>
-    <row r="989" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="989" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A989" s="24"/>
       <c r="B989" s="24"/>
       <c r="C989" s="24"/>
@@ -27147,7 +27174,7 @@
       <c r="W989" s="2"/>
       <c r="X989" s="2"/>
     </row>
-    <row r="990" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="990" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A990" s="24"/>
       <c r="B990" s="24"/>
       <c r="C990" s="24"/>
@@ -27173,7 +27200,7 @@
       <c r="W990" s="2"/>
       <c r="X990" s="2"/>
     </row>
-    <row r="991" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="991" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A991" s="24"/>
       <c r="B991" s="24"/>
       <c r="C991" s="24"/>
@@ -27199,7 +27226,7 @@
       <c r="W991" s="2"/>
       <c r="X991" s="2"/>
     </row>
-    <row r="992" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="992" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A992" s="24"/>
       <c r="B992" s="24"/>
       <c r="C992" s="24"/>
@@ -27225,7 +27252,7 @@
       <c r="W992" s="2"/>
       <c r="X992" s="2"/>
     </row>
-    <row r="993" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="993" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A993" s="24"/>
       <c r="B993" s="24"/>
       <c r="C993" s="24"/>
@@ -27251,7 +27278,7 @@
       <c r="W993" s="2"/>
       <c r="X993" s="2"/>
     </row>
-    <row r="994" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="994" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A994" s="24"/>
       <c r="B994" s="24"/>
       <c r="C994" s="24"/>
@@ -27277,7 +27304,7 @@
       <c r="W994" s="2"/>
       <c r="X994" s="2"/>
     </row>
-    <row r="995" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="995" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A995" s="24"/>
       <c r="B995" s="24"/>
       <c r="C995" s="24"/>
@@ -27303,7 +27330,7 @@
       <c r="W995" s="2"/>
       <c r="X995" s="2"/>
     </row>
-    <row r="996" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="996" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A996" s="24"/>
       <c r="B996" s="24"/>
       <c r="C996" s="24"/>
@@ -27329,7 +27356,7 @@
       <c r="W996" s="2"/>
       <c r="X996" s="2"/>
     </row>
-    <row r="997" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="997" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A997" s="24"/>
       <c r="B997" s="24"/>
       <c r="C997" s="24"/>
@@ -27355,7 +27382,7 @@
       <c r="W997" s="2"/>
       <c r="X997" s="2"/>
     </row>
-    <row r="998" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="998" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A998" s="24"/>
       <c r="B998" s="24"/>
       <c r="C998" s="24"/>
@@ -27381,7 +27408,7 @@
       <c r="W998" s="2"/>
       <c r="X998" s="2"/>
     </row>
-    <row r="999" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="999" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A999" s="24"/>
       <c r="B999" s="24"/>
       <c r="C999" s="24"/>
@@ -27407,7 +27434,7 @@
       <c r="W999" s="2"/>
       <c r="X999" s="2"/>
     </row>
-    <row r="1000" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="1000" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A1000" s="24"/>
       <c r="B1000" s="24"/>
       <c r="C1000" s="24"/>
@@ -27433,7 +27460,7 @@
       <c r="W1000" s="2"/>
       <c r="X1000" s="2"/>
     </row>
-    <row r="1001" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="1001" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A1001" s="24"/>
       <c r="B1001" s="24"/>
       <c r="C1001" s="24"/>
@@ -27459,7 +27486,7 @@
       <c r="W1001" s="2"/>
       <c r="X1001" s="2"/>
     </row>
-    <row r="1002" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="1002" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A1002" s="24"/>
       <c r="B1002" s="24"/>
       <c r="C1002" s="24"/>
@@ -27485,7 +27512,7 @@
       <c r="W1002" s="2"/>
       <c r="X1002" s="2"/>
     </row>
-    <row r="1003" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="1003" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A1003" s="24"/>
       <c r="B1003" s="24"/>
       <c r="C1003" s="24"/>
@@ -27511,7 +27538,7 @@
       <c r="W1003" s="2"/>
       <c r="X1003" s="2"/>
     </row>
-    <row r="1004" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="1004" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A1004" s="24"/>
       <c r="B1004" s="24"/>
       <c r="C1004" s="24"/>
@@ -27537,7 +27564,7 @@
       <c r="W1004" s="2"/>
       <c r="X1004" s="2"/>
     </row>
-    <row r="1005" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="1005" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A1005" s="24"/>
       <c r="B1005" s="24"/>
       <c r="C1005" s="24"/>
@@ -27563,7 +27590,7 @@
       <c r="W1005" s="2"/>
       <c r="X1005" s="2"/>
     </row>
-    <row r="1006" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="1006" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A1006" s="24"/>
       <c r="B1006" s="24"/>
       <c r="C1006" s="24"/>
@@ -27589,7 +27616,7 @@
       <c r="W1006" s="2"/>
       <c r="X1006" s="2"/>
     </row>
-    <row r="1007" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="1007" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A1007" s="24"/>
       <c r="B1007" s="24"/>
       <c r="C1007" s="24"/>
@@ -27615,7 +27642,7 @@
       <c r="W1007" s="2"/>
       <c r="X1007" s="2"/>
     </row>
-    <row r="1008" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="1008" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A1008" s="24"/>
       <c r="B1008" s="24"/>
       <c r="C1008" s="24"/>
@@ -27641,7 +27668,7 @@
       <c r="W1008" s="2"/>
       <c r="X1008" s="2"/>
     </row>
-    <row r="1009" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="1009" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A1009" s="24"/>
       <c r="B1009" s="24"/>
       <c r="C1009" s="24"/>
@@ -27667,7 +27694,7 @@
       <c r="W1009" s="2"/>
       <c r="X1009" s="2"/>
     </row>
-    <row r="1010" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="1010" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A1010" s="24"/>
       <c r="B1010" s="24"/>
       <c r="C1010" s="24"/>
@@ -27693,7 +27720,7 @@
       <c r="W1010" s="2"/>
       <c r="X1010" s="2"/>
     </row>
-    <row r="1011" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="1011" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A1011" s="24"/>
       <c r="B1011" s="24"/>
       <c r="C1011" s="24"/>
@@ -27719,7 +27746,7 @@
       <c r="W1011" s="2"/>
       <c r="X1011" s="2"/>
     </row>
-    <row r="1012" spans="1:24" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="1012" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A1012" s="24"/>
       <c r="B1012" s="24"/>
       <c r="C1012" s="24"/>
@@ -27747,6 +27774,16 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="A3:A9"/>
+    <mergeCell ref="B3:B7"/>
+    <mergeCell ref="A10:A14"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="A15:A17"/>
+    <mergeCell ref="A18:A25"/>
+    <mergeCell ref="A32:A35"/>
+    <mergeCell ref="A36:A40"/>
+    <mergeCell ref="A41:A43"/>
     <mergeCell ref="B36:B38"/>
     <mergeCell ref="B41:B42"/>
     <mergeCell ref="B19:B21"/>
@@ -27756,16 +27793,6 @@
     <mergeCell ref="A29:A31"/>
     <mergeCell ref="B29:B31"/>
     <mergeCell ref="B32:B34"/>
-    <mergeCell ref="A15:A17"/>
-    <mergeCell ref="A18:A25"/>
-    <mergeCell ref="A32:A35"/>
-    <mergeCell ref="A36:A40"/>
-    <mergeCell ref="A41:A43"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="A3:A9"/>
-    <mergeCell ref="B3:B7"/>
-    <mergeCell ref="A10:A14"/>
-    <mergeCell ref="B10:B13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
